--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -17,13 +17,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +51,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,1107 +437,1107 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№ з/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Дата і номер розпорядження/ рішення/припису</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Дата одержання розпорядження/ рішення/припису</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Назва лікарських засобів та перелік серій лікарських засобів, зазначених у розпорядженні/ рішенні/приписі</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Результати перевірки щодо наявності зазначених лікарських засобів</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Вжиті заходи у разі виявлення зазначених лікарських засобів</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Дата і номер листа-повідомлення територіальному органу</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Підпис уповноваженої особи</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>№ 164-001.2/002.0/17-26 від 01.04.2026</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 20 мг; по 10 таблеток у блістері; по 3 блістери у картонній коробці, Серія № FD253720C, Гетеро Лабз Лімітед, Індія</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>№ 164-001.2/002.0/17-26 від 01.04.2026</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 20 мг; по 10 таблеток у блістері; по 9 блістерів у картонній коробці, Серія № FD253721A, Гетеро Лабз Лімітед, Індія</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>№ 165-001.2/002.0/17-26 від 01.04.2026</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 10 мг; по 10 таблеток у блістері; по 9 блістерів у картонній коробці, Серія № FD252942A, Гетеро Лабз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>№ 165-001.2/002.0/17-26 від 01.04.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>01.04.2026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 10 мг; по 10 таблеток у блістері; по 3 блістери у картонній коробці, Серія № FD253931B, Гетеро Лабз Лімітед, Індія</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>№ 165-001.2/002.0/17-26 від 01.04.2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>№ 166-001.2/002.0/17-26 від 01.04.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 10 мг; по 10 таблеток у блістері; по 9 блістерів у картонній коробці, Серія № FD252942A, Гетеро Лабз Лімітед, Індія</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>№ 166-001.2/002.0/17-26 від 01.04.2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 40 мг, по 10 таблеток у блістері, по 3 блістери у картонній коробці, Серія № FD255985С, Гетеро Лабз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>№ 167-001.2/002.0/17-26 від 01.04.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>01.04.2026</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 40 мг, по 10 таблеток у блістері, по 3 блістери у картонній коробці, Серія № FD255985С, Гетеро Лабз Лімітед, Індія</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>№ 167-001.2/002.0/17-26 від 01.04.2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>01.04.2026</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>ОКОМІСТИН®, краплі очні/вушні/для носа, розчин 0,01 % по 5 мл у флаконі полімерному з крапельницею; по 1 флакону в пачці, Серія № 10324, ПАТ "Фармак", Україна</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>№ 168-001.2/002.0/17-26 від 02.04.2026</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>PROLIA® (Denosumab) 60 mg/ml, розчин для ін`єкцій у попередньо наповненому шприці, Серія № 1174358A, Amgen Manufacturing Limited Пуерто-Рико, EE.UU; Amgen Technology Unlimited Company, Ірландія</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>№ 169-001.2/002.0/17-26 від 02.04.2026</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>JAXTERAN (Dimethylis fumaras) 120 mg, тверді кишковорозчинні капсули, по 7 капсул в блістері, по 2 блістери в упаковці, Серія № 23690003, SANOVEL ILAC SANAYI VETICARET AS, Туреччина</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>№ 170-001.2/002.0/17-26 від 02.04.2026</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>AZELAN (Azelaic acid) 150mg/g, гель, Серія № всі серії, LEO PHARMA MANUFACTURING (ITALY) S.R.L, Італія</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>№ 171-001.2/002.0/17-26 від 02.04.2026</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>PROLIA® (Denosumab) 60 mg/ml, розчин для ін`єкцій у попередньо наповненому шприці, Серія № 2749920, 9053760, 6637000, Amgen Manufacturing Limited Пуерто-Рико, EE.UU; Amgen Technology Unlimited Company, Ірландія</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>MOXIFLOXACIN EBERTH 400 mg/250 ml, розчин для інфузій, Серія № 24G453, 24K216, 24K217, 24K220, 24K221, 24K225, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>02.04.2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>VORICONAZOL EBERTH 200 mg, порошок для приготування розчину для інфузій у флаконі, Серія № 24J152, 24J154, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>02.04.2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>CEFAZOLIN DR. EBERTH 2 g, порошок для приготування розчину для ін'єкцій/інфузій у флаконі, Серія № 241255, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>CEFОTAXIM EBERTH 0.5 g, порошок для приготування розчину для ін'єкцій у флаконі, Серія № 240923, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>02.04.2026</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>CEFTAZIDIM DR. EBERTH 500 mg, порошок для приготування розчину для ін'єкцій, у флаконі, Серія № 240559, 240560, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>02.04.2026</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>CEFTAZIDIM DR. EBERTH 2 g, порошок для приготування розчину для ін’єкцій та інфузій, у флаконі, Серія № 240606, 240610, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CEFTAZIDIM DR. EBERTH 500 mg, порошок для приготування розчину для ін'єкцій, у флаконі, Серія № 240559, 240560, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CEFTRIAXON EBERTH 1 g, порошок для приготування розчину для ін'єкцій у флаконі, Серія № 240441, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CEFTRIAXON EBERTH 1 g, порошок для приготування розчину для ін'єкцій у флаконі, Серія № 240441, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>CEFTRIAXON EBERTH 2 g, порошок для приготування розчину для інфузій у флаконі, Серія № 240445, 240447, 240448, 240449, 240450, 240451, 240452, 240501, 240502, 240503, 240504, 240505, 240506, 240805, 240806, 240807, 240808, 240809, 240810, 240812, 240811, 240813, 240814, 240831, 240832, 240833, 240834, 240835, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CEFTRIAXON EBERTH 2 g, порошок для приготування розчину для інфузій у флаконі, Серія № 240445, 240447, 240448, 240449, 240450, 240451, 240452, 240501, 240502, 240503, 240504, 240505, 240506, 240805, 240806, 240807, 240808, 240809, 240810, 240812, 240811, 240813, 240814, 240831, 240832, 240833, 240834, 240835, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>LEVOFLOXACIN DR. EBERTH, 5 mg/ml, розчин для інфузій, Серія № 11024, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>№ 173-001.2/002.0/17-26 від 02.04.2026</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>02.04.2026</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CEFОTAXIM EBERTH 0.5 g, порошок для приготування розчину для ін'єкцій у флаконі, Серія № 240923, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>02.04.2026</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LEVOFLOXACIN DR. EBERTH, 5 mg/ml, розчин для інфузій, Серія № 11024, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>02.04.2026</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>MOXIFLOXACIN EBERTH 400 mg/250 ml, розчин для інфузій, Серія № 24G453, 24K216, 24K217, 24K220, 24K221, 24K225, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>№ 172-001.2/002.0/17-26 від 02.04.2026</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>02.04.2026</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VORICONAZOL EBERTH 200 mg, порошок для приготування розчину для інфузій у флаконі, Серія № 24J152, 24J154, Dr. Friedrich Eberth Arzneimittel GmbH, Німеччина</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>№ 173-001.2/002.0/17-26 від 02.04.2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>02.04.2026</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>КEFADIM (Ceftazidime pentahydrate) 1g, порошок для приготування розчину для ін’єкцій, Серія № 111485C, 111626C, 111750C, 112056C, ANTIBIOTICOS DO BRASIL LTDA, Бразилія</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>№ 174-001.2/002.0/17-26 від 03.04.2026</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>03.04.2026</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>SAIZEN (Somatropin)8 mg/ml, розчин для інфузій, Серія № BA088217, Merck Serono S.P.A., Італія</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>№ 175-001.2/002.0/17-26 від 03.04.2026</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>03.04.2026</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>MOUNJARO (Tirzepatide), парентеральний розчин малого об’єму, Серія № D880730, D856831, D840678, ELI LILLY S.A, Ірландія</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>№ 176-001.2/002.0/17-26 від 03.04.2026</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>03.04.2026</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>РИПРОНАТ, розчин для ін`єкцій, 100 мг/мл; по 5 мл в ампулі; по 5 ампул в контурній чарунковій упаковці; по 2 контурні чарункові упаковки в картонній коробці, Серія № 2404611, К.О. Ромфарм Компані С.Р.Л., Румунiя</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>№ 178-001.2/002.0/17-26 від 06.04.2026</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>MAGNESIUM SULFATE у воді для ін'єкцій, USP, 4 г/100 мл, внутрішньовенний пакет, Серія № AH250162, Amneal Pharmaceuticais Pvt. Ltd., Індія</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>№ 179-001.2/002.0/17-26 від 06.04.2026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>АСКОРІЛ ЕКСПЕКТОРАНТ, сироп; по 100 мл у пластикових флаконах; по 1 флакону разом з мірним ковпачком у картонній упаковці, Серія № всі серії, Гленмарк Фармасьютикалз Лтд., Індія</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>№ 180-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>СПИРТ ЕТИЛОВИЙ 96%, розчин для зовнішнього застосування 96 % по 100 мл у флаконах, Серія № 010425, ПрАТ "Біолік", Україна</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>№ 181-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>КУРОСУРФ® (CUROSURF) 80 mg, суспензія для ендотрахеального введення, 80 мг/мл, по 1,5 мл у флаконі; по 1 флакону в картонній коробці, Серія № 1211286, CHIESI FARMACEUTICI S.P.A., Італія</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>№ 182-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>INUPRIN FORTE (Inosinum pranobexum) 100 mg/ml, сироп 100 мл, Серія № 01051714, 02051714, 03051714, 04051714, 05051714, 06051714, 07051714, 08051714, 09051714, 01061714, 02061714, 03061714, 04061714, 05061714, 06061714, 07061714, 08061714, 09061714, 10061714, 11061714, 01071714, 02071714, Mako Pharma Sp. z o.o., Medicofarma S.A.n, Польща</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>№ 183-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>ФАРМАСЕПТИЛ, розчин для зовнішнього застосування 70 %, по 100 мл у флаконах, Серія № 011125, ТОВ "МЕДЛЕВ", Україна</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>№ 184-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники; по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № TW864, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>№ 186-001.3/002.0/17-26 від 10.04.2026</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>10.04.2026</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>СТРЕПСІЛС® З МЕНТОЛОМ ТА ЕВКАЛІПТОМ, льодяники, по 12 льодяників у блістері, по 2 блістери в картонній коробці, Серія № VB598, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>№ 187-001.3/002.0/17-26 від 10.04.2026</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>10.04.2026</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Dysport®500 (Clostridium Botulinum type Atoxin), 500 unit/vial, Серія № Р31330, з маркуванням виробника IPSEN BIOPHARM LTD/UK, -</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>№ 188-001.2/002.0/17-26 від 13.04.2026</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>13.04.2026</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>OXALIPLATIN EUGIA (Oxaliplatinum), 5mg/ml, концентрат для розчину для інфузій, 1 флакон 20 мл, Серія № 1OX25010B, APL Swift Services (Malta) Ltd., Мальта</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>№ 189-001.2/002.0/17-26 від 13.04.2026</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>13.04.2026</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>TAGRISSO (Osimertinib), 80 mg, таблетки № 30 у флаконі, Серія № HT3877, AstraZeneca AB, -</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>№ 190-001.2/002.0/17-26 від 13.04.2026</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>13.04.2026</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>АКЛАСТА/ACLASTA (Zoledronic acid), розчин для інфузій, 5 мг/100 мл; по 1 флакону в коробці з картону, Серія № NU1096, NX9351, Fresenius Kabi Austria GmbH, -</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>№ 191-001.2/002.0/17-26 від 13.04.2026</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>13.04.2026</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>OZEMPIC (Semaglutide), 1 mg, розчин для ін'єкцій у попередньо заповненій шприц-ручці, у картонній коробці з 1 ручкою та 4 одноразовими голками (4 дози), Серія № MP5E511 (попередньо наповнена ручка), S7A925 (вторинна упаковка), з маркуванням виробника Bayer de Mexico, S.A. de C.V., -</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1539,6 +1539,62 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>№ 192-001.2/002.0/17-26 від 14.04.2026</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>ЛОТАР®, таблетки, вкриті плівковою оболонкою, по 100 мг; по 15 таблеток у блістері; по 2 блістери у картонній коробці, Серія № 1136055, АЛКАЛОЇД АД Скоп'є, Республіка Північна Македонія</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>№ 192-001.2/002.0/17-26 від 14.04.2026</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>ЛОТАР®, таблетки, вкриті плівковою оболонкою, по 100 мг; по 15 таблеток у блістері; по 2 блістери у картонній коробці, Серія № 1136056, АЛКАЛОЇД АД Скоп'є, Республіка Північна Македонія</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>№ 181-001.2/002.0/17-26 від 07.04.2026</t>
+          <t>№ 180-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>КУРОСУРФ® (CUROSURF) 80 mg, суспензія для ендотрахеального введення, 80 мг/мл, по 1,5 мл у флаконі; по 1 флакону в картонній коробці, Серія № 1211286, CHIESI FARMACEUTICI S.P.A., Італія</t>
+          <t>СПИРТ ЕТИЛОВИЙ 96%, розчин для зовнішнього застосування 96 %, по 100 мл у флаконах, Серія № 020925, ПрАТ "Біолік", Україна</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>№ 182-001.2/002.0/17-26 від 07.04.2026</t>
+          <t>№ 181-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>INUPRIN FORTE (Inosinum pranobexum) 100 mg/ml, сироп 100 мл, Серія № 01051714, 02051714, 03051714, 04051714, 05051714, 06051714, 07051714, 08051714, 09051714, 01061714, 02061714, 03061714, 04061714, 05061714, 06061714, 07061714, 08061714, 09061714, 10061714, 11061714, 01071714, 02071714, Mako Pharma Sp. z o.o., Medicofarma S.A.n, Польща</t>
+          <t>КУРОСУРФ® (CUROSURF) 80 mg, суспензія для ендотрахеального введення, 80 мг/мл, по 1,5 мл у флаконі; по 1 флакону в картонній коробці, Серія № 1211286, CHIESI FARMACEUTICI S.P.A., Італія</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>№ 183-001.2/002.0/17-26 від 07.04.2026</t>
+          <t>№ 182-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ФАРМАСЕПТИЛ, розчин для зовнішнього застосування 70 %, по 100 мл у флаконах, Серія № 011125, ТОВ "МЕДЛЕВ", Україна</t>
+          <t>INUPRIN FORTE (Inosinum pranobexum) 100 mg/ml, сироп 100 мл, Серія № 01051714, 02051714, 03051714, 04051714, 05051714, 06051714, 07051714, 08051714, 09051714, 01061714, 02061714, 03061714, 04061714, 05061714, 06061714, 07061714, 08061714, 09061714, 10061714, 11061714, 01071714, 02071714, Mako Pharma Sp. z o.o., Medicofarma S.A.n, Польща</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>№ 184-001.2/002.0/17-26 від 07.04.2026</t>
+          <t>№ 183-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники; по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № TW864, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+          <t>ФАРМАСЕПТИЛ, розчин для зовнішнього застосування 70 %, по 100 мл у флаконах, Серія № 011125, ТОВ "МЕДЛЕВ", Україна</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1377,17 +1377,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>№ 186-001.3/002.0/17-26 від 10.04.2026</t>
+          <t>№ 184-001.2/002.0/17-26 від 07.04.2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10.04.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>СТРЕПСІЛС® З МЕНТОЛОМ ТА ЕВКАЛІПТОМ, льодяники, по 12 льодяників у блістері, по 2 блістери в картонній коробці, Серія № VB598, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники; по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № TW864, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>№ 187-001.3/002.0/17-26 від 10.04.2026</t>
+          <t>№ 186-001.3/002.0/17-26 від 10.04.2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Dysport®500 (Clostridium Botulinum type Atoxin), 500 unit/vial, Серія № Р31330, з маркуванням виробника IPSEN BIOPHARM LTD/UK, -</t>
+          <t>СТРЕПСІЛС® З МЕНТОЛОМ ТА ЕВКАЛІПТОМ, льодяники, по 12 льодяників у блістері, по 2 блістери в картонній коробці, Серія № VB598, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1433,17 +1433,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>№ 188-001.2/002.0/17-26 від 13.04.2026</t>
+          <t>№ 187-001.3/002.0/17-26 від 10.04.2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>13.04.2026</t>
+          <t>10.04.2026</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>OXALIPLATIN EUGIA (Oxaliplatinum), 5mg/ml, концентрат для розчину для інфузій, 1 флакон 20 мл, Серія № 1OX25010B, APL Swift Services (Malta) Ltd., Мальта</t>
+          <t>Dysport®500 (Clostridium Botulinum type Atoxin), 500 unit/vial, Серія № Р31330, з маркуванням виробника IPSEN BIOPHARM LTD/UK, -</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>№ 189-001.2/002.0/17-26 від 13.04.2026</t>
+          <t>№ 188-001.2/002.0/17-26 від 13.04.2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>TAGRISSO (Osimertinib), 80 mg, таблетки № 30 у флаконі, Серія № HT3877, AstraZeneca AB, -</t>
+          <t>OXALIPLATIN EUGIA (Oxaliplatinum), 5mg/ml, концентрат для розчину для інфузій, 1 флакон 20 мл, Серія № 1OX25010B, APL Swift Services (Malta) Ltd., Мальта</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>№ 190-001.2/002.0/17-26 від 13.04.2026</t>
+          <t>№ 189-001.2/002.0/17-26 від 13.04.2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>АКЛАСТА/ACLASTA (Zoledronic acid), розчин для інфузій, 5 мг/100 мл; по 1 флакону в коробці з картону, Серія № NU1096, NX9351, Fresenius Kabi Austria GmbH, -</t>
+          <t>TAGRISSO (Osimertinib), 80 mg, таблетки № 30 у флаконі, Серія № HT3877, AstraZeneca AB, -</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>№ 191-001.2/002.0/17-26 від 13.04.2026</t>
+          <t>№ 190-001.2/002.0/17-26 від 13.04.2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>OZEMPIC (Semaglutide), 1 mg, розчин для ін'єкцій у попередньо заповненій шприц-ручці, у картонній коробці з 1 ручкою та 4 одноразовими голками (4 дози), Серія № MP5E511 (попередньо наповнена ручка), S7A925 (вторинна упаковка), з маркуванням виробника Bayer de Mexico, S.A. de C.V., -</t>
+          <t>АКЛАСТА/ACLASTA (Zoledronic acid), розчин для інфузій, 5 мг/100 мл; по 1 флакону в коробці з картону, Серія № NU1096, NX9351, Fresenius Kabi Austria GmbH, -</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>№ 192-001.2/002.0/17-26 від 14.04.2026</t>
+          <t>№ 191-001.2/002.0/17-26 від 13.04.2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>14.04.2026</t>
+          <t>13.04.2026</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>ЛОТАР®, таблетки, вкриті плівковою оболонкою, по 100 мг; по 15 таблеток у блістері; по 2 блістери у картонній коробці, Серія № 1136055, АЛКАЛОЇД АД Скоп'є, Республіка Північна Македонія</t>
+          <t>OZEMPIC (Semaglutide), 1 mg, розчин для ін'єкцій у попередньо заповненій шприц-ручці, у картонній коробці з 1 ручкою та 4 одноразовими голками (4 дози), Серія № MP5E511 (попередньо наповнена ручка), S7A925 (вторинна упаковка), з маркуванням виробника Bayer de Mexico, S.A. de C.V., -</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>ЛОТАР®, таблетки, вкриті плівковою оболонкою, по 100 мг; по 15 таблеток у блістері; по 2 блістери у картонній коробці, Серія № 1136056, АЛКАЛОЇД АД Скоп'є, Республіка Північна Македонія</t>
+          <t>ЛОТАР®, таблетки, вкриті плівковою оболонкою, по 100 мг; по 15 таблеток у блістері; по 2 блістери у картонній коробці, Серія № 1136055, АЛКАЛОЇД АД Скоп'є, Республіка Північна Македонія</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1594,6 +1594,34 @@
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>№ 192-001.2/002.0/17-26 від 14.04.2026</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>ЛОТАР®, таблетки, вкриті плівковою оболонкою, по 100 мг; по 15 таблеток у блістері; по 2 блістери у картонній коробці, Серія № 1136056, АЛКАЛОЇД АД Скоп'є, Республіка Північна Македонія</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1623,6 +1623,62 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
     </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>№ 193-001.2/002.0/17-26 від 16.04.2026</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>всі серії лікарських засобів виробництва ЛЗ виробництва Zenzi Pharmaceutical Industries Pvt. Ltd., -, Zenzi Pharmaceutical Industries Pvt. Ltd., India</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>№ 194-001.2/002.0/17-26 від 16.04.2026</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>ARANESP 30 mkg, розчин для ін’єкцій, Серія № 1174101A, Амджен Європа Б.В., Нідерланди</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1679,6 +1679,62 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
     </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>№ 195-001.2/002.0/17-26 від 17.04.2026</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT®500 (Clostridium Botulinum type Atoxin), порошок для розчину для ін'єкцій, у флаконі, Серія № P09903, з маркуванням виробника Ipsen Biopharm LTD., Wrexcam, UK, -</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>№ 196-001.2/002.0/17-26 від 17.04.2026</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>17.04.2026</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>GASTROGRAFIN (Meglumine amidotrizas + Natrii amidotrizas ) 660 mg + 100 mg/ml, розчин для перорального та ректального застосування, 10 флаконів по 100 мл, Серія № всі серії, BERLIMED S.A. ,Poligono Industrial Santa Rosa, Madrid, Іспанія</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1735,6 +1735,146 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
     </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>№ 197-001.2/002.0/17-26 від 20.04.2026</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 20 мг; по 10 таблеток у блістері; по 9 блістерів у картонній коробці, Серія № FD253721A, Гетеро Лабз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>№ 197-001.2/002.0/17-26 від 20.04.2026</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 20 мг; по 10 таблеток у блістері; по 3 блістери у картонній коробці, Серія № FD253720C, Гетеро Лабз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>№ 198-001.3/002.0/17-26 від 20.04.2026</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 40 мг, по 10 таблеток у блістері, по 3 блістери у картонній коробці, Серія № FD255985С, Гетеро Лабз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>№ 199-001.2/002.0/17-26 від 20.04.2026</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 10 мг; по 10 таблеток у блістері; по 3 блістери у картонній коробці, Серія № FD253931B, Гетеро Лабз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>№ 200-001.2/002.0/17-26 від 20.04.2026</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>CISPLATIN (Cisplatin) 1mg/ml, концентрат для розчину для інфузій, 1 флакон, Серія № AZ0108, Тимоорган Фармаціе ГмбХ, Німеччина</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1875,6 +1875,258 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
     </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>№ 201-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>USYMRO® 45 mg and 90 mg, розчин для ін’єкцій, у попередньо заповненому шприці, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>№ 201-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>USYMRO® 130 mg, порошок для розчину для інфузій, у флаконі, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>№ 201-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>AVZIVI® 25 mg/ml, порошок для розчину для інфузій, у флаконі, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>№ 201-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>TOFIDENCE ® 20 mg/ml, порошок для розчину для інфузій, у флаконі, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>№ 201-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>GOTENFIA 50 mg and 100 mg, розчин для ін’єкцій, у попередньо заповненому шприці, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>№ 202-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>ДЕКАРИС, таблетки по 50 мг, по 2 таблетки у блістері; по 1 блістеру в картонній упаковці, Серія № всі серії, повний цикл виробництва готової продукції, пакування, контроль серії: Гедеон Ріхтер Румунія А.Т., Румунія; випуск серії, оформлення сертифікатів якості: ВАТ "Гедеон Ріхтер", Угорщина, Румунія/ Угорщина</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>№ 202-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>ДЕКАРИС, таблетки по 150 мг; по 1 таблетці у блістері; по 1 блістеру в картонній упаковці, Серія № всі серії, повний цикл виробництва готової продукції, пакування, контроль серії: Гедеон Ріхтер Румунія А.Т., Румунія; випуск серії, оформлення сертифікатів якості: ВАТ "Гедеон Ріхтер", Угорщина, Румунія/ Угорщина</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>№ 203-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>СТРЕПСІЛС® З МЕДОМ ТА ЛИМОНОМ, льодяники; по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № TV663, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>№ 204-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>СТРЕПСІЛС® З МЕДОМ ТА ЛИМОНОМ, льодяники по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № TY558, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>№ 200-001.2/002.0/17-26 від 20.04.2026</t>
+          <t>№ 199-001.2/002.0/17-26 від 20.04.2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CISPLATIN (Cisplatin) 1mg/ml, концентрат для розчину для інфузій, 1 флакон, Серія № AZ0108, Тимоорган Фармаціе ГмбХ, Німеччина</t>
+          <t>ЛІПІРАСТОР, таблетки, вкриті плівковою оболонкою, по 10 мг; по 10 таблеток у блістері; по 9 блістерів у картонній коробці, Серія № FD252942A, Гетеро Лабз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1881,17 +1881,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>№ 201-001.2/002.0/17-26 від 21.04.2026</t>
+          <t>№ 200-001.2/002.0/17-26 від 20.04.2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>21.04.2026</t>
+          <t>20.04.2026</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>USYMRO® 45 mg and 90 mg, розчин для ін’єкцій, у попередньо заповненому шприці, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+          <t>CISPLATIN (Cisplatin) 1mg/ml, концентрат для розчину для інфузій, 1 флакон, Серія № AZ0108, Тимоорган Фармаціе ГмбХ, Німеччина</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>USYMRO® 130 mg, порошок для розчину для інфузій, у флаконі, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+          <t>USYMRO® 45 mg and 90 mg, розчин для ін’єкцій, у попередньо заповненому шприці, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>AVZIVI® 25 mg/ml, порошок для розчину для інфузій, у флаконі, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+          <t>USYMRO® 130 mg, порошок для розчину для інфузій, у флаконі, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>TOFIDENCE ® 20 mg/ml, порошок для розчину для інфузій, у флаконі, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+          <t>AVZIVI® 25 mg/ml, порошок для розчину для інфузій, у флаконі, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>GOTENFIA 50 mg and 100 mg, розчин для ін’єкцій, у попередньо заповненому шприці, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
+          <t>TOFIDENCE ® 20 mg/ml, порошок для розчину для інфузій, у флаконі, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>№ 202-001.2/002.0/17-26 від 21.04.2026</t>
+          <t>№ 201-001.2/002.0/17-26 від 21.04.2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>ДЕКАРИС, таблетки по 50 мг, по 2 таблетки у блістері; по 1 блістеру в картонній упаковці, Серія № всі серії, повний цикл виробництва готової продукції, пакування, контроль серії: Гедеон Ріхтер Румунія А.Т., Румунія; випуск серії, оформлення сертифікатів якості: ВАТ "Гедеон Ріхтер", Угорщина, Румунія/ Угорщина</t>
+          <t>GOTENFIA 50 mg and 100 mg, розчин для ін’єкцій, у попередньо заповненому шприці, Серія № всі серії, Bio-Thera Solutions Ltd., Китай</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>ДЕКАРИС, таблетки по 150 мг; по 1 таблетці у блістері; по 1 блістеру в картонній упаковці, Серія № всі серії, повний цикл виробництва готової продукції, пакування, контроль серії: Гедеон Ріхтер Румунія А.Т., Румунія; випуск серії, оформлення сертифікатів якості: ВАТ "Гедеон Ріхтер", Угорщина, Румунія/ Угорщина</t>
+          <t>ДЕКАРИС, таблетки по 50 мг, по 2 таблетки у блістері; по 1 блістеру в картонній упаковці, Серія № всі серії, повний цикл виробництва готової продукції, пакування, контроль серії: Гедеон Ріхтер Румунія А.Т., Румунія; випуск серії, оформлення сертифікатів якості: ВАТ "Гедеон Ріхтер", Угорщина, Румунія/ Угорщина</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>№ 203-001.2/002.0/17-26 від 21.04.2026</t>
+          <t>№ 202-001.2/002.0/17-26 від 21.04.2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>СТРЕПСІЛС® З МЕДОМ ТА ЛИМОНОМ, льодяники; по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № TV663, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
+          <t>ДЕКАРИС, таблетки по 150 мг; по 1 таблетці у блістері; по 1 блістеру в картонній упаковці, Серія № всі серії, повний цикл виробництва готової продукції, пакування, контроль серії: Гедеон Ріхтер Румунія А.Т., Румунія; випуск серії, оформлення сертифікатів якості: ВАТ "Гедеон Ріхтер", Угорщина, Румунія/ Угорщина</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>№ 204-001.2/002.0/17-26 від 21.04.2026</t>
+          <t>№ 203-001.2/002.0/17-26 від 21.04.2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>СТРЕПСІЛС® З МЕДОМ ТА ЛИМОНОМ, льодяники по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № TY558, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+          <t>СТРЕПСІЛС® З МЕДОМ ТА ЛИМОНОМ, льодяники; по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № TV663, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2126,6 +2126,34 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>№ 204-001.2/002.0/17-26 від 21.04.2026</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>СТРЕПСІЛС® З МЕДОМ ТА ЛИМОНОМ, льодяники по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № TY558, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2155,6 +2155,118 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
     </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>№ 205-001.2/002.0/17-26 від 22.04.2026</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>AKNEMYCIN PLUS (Erythromycin), 40 mg/g and 0,25 mg/g, розчин для шкіри, Серія № 541193, 51316X2, Almirall Hermal GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>№ 206-001.2/002.0/17-26 від 22.04.2026</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>VENDAL RETARD (Morphini hydrochloridum) 10 mg, таблетки з пролонгованою дією, вкриті плівковою оболонкою, № 30 у блістері, Серія № H01295 (bulk No GG00037), G.L. Pharma GmbH, Австрія</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>№ 207-001.2/002.0/17-26 від 22.04.2026</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>RYBELSUS® (Semaglutide), 3 mg; 7 mg; 14 mg, таблетки № 100 у флаконі, Серія № N087035, з маркуванням виробника NOVO NORDISK MEXICO, S.A. DE C.V., -</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>№ 208-001.2/002.0/17-26 від 22.04.2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>22.04.2026</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Vyvanse® (Lisdexamfetamine dimesylate) 30 mg; 50 mg; 70 mg, капсули, флакон № 28 у картонній коробці, Серія № 317426D, 3077743, з маркуванням виробника Takeda Mexico, S.A. de CV.,, -</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2267,6 +2267,34 @@
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
     </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>№ 209-001.2/002.0/17-26 від 23.04.2026</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>23.04.2026</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>UROGRAFINA (Meglumine amidotrizoate/Sodium amidotrizoate), 660 mg/100 mg/ml, -, Серія № всі серії, BERLIMED S.A., Poligono Industrial Santa Rosa, Madrid, Іспанія</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2295,6 +2295,258 @@
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
     </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>№ 210-001.2/002.0/17-26 від 24.04.2026</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>THOMPSON CHILDREN`S CHEWABLE, жувальні таблетки, Серія № всі серії, Nutraceutical International Corp, Thompson, -</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>№ 210-001.2/002.0/17-26 від 24.04.2026</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>SOLARY VITEX, капсули, Серія № всі серії, Nutraceutical International Corp, Thompson, -</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>№ 210-001.2/002.0/17-26 від 24.04.2026</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>SOLARY QUERCETIN, капсули, Серія № всі серії, Nutraceutical International Corp, Thompson, -</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>№ 210-001.2/002.0/17-26 від 24.04.2026</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>SOLARY SAW PALMETTO 580 mg, капсули, Серія № всі серії, Nutraceutical International Corp, Thompson, -</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>№ 210-001.2/002.0/17-26 від 24.04.2026</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>SOLARY CALCIUM, жувальні таблетки, Серія № всі серії, Nutraceutical International Corp, Thompson, -</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>№ 210-001.2/002.0/17-26 від 24.04.2026</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>SOLARY LODINE, капсули, Серія № всі серії, Nutraceutical International Corp, Thompson, -</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>№ 210-001.2/002.0/17-26 від 24.04.2026</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>THOMPSON B COMPLEX, таблетки, Серія № всі серії, Nutraceutical International Corp, Thompson, -</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>№ 210-001.2/002.0/17-26 від 24.04.2026</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>THOMPSON DHEA 50 mg, капсули, Серія № всі серії, Nutraceutical International Corp, Thompson, -</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>№ 210-001.2/002.0/17-26 від 24.04.2026</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>24.04.2026</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>THOMPSON CHROMIUM, таблетки, Серія № всі серії, Nutraceutical International Corp, Thompson, -</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2547,6 +2547,594 @@
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
     </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25303, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25304, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25305, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25306, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25308, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25307, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25309, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25310, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25311, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25313, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25312, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25314, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25315, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25317, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25316, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25318, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25319, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25321, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25320, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25323, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25322, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3135,6 +3135,118 @@
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr"/>
     </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25325, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25324, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25327, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>№ 211-001.2/002.0/17-26 від 27.04.2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>27.04.2026</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>ДОЛОКСЕН, таблетки, вкриті плівковою оболонкою; по 10 таблеток у блістері; по 10 блістерів у картонній коробці, Серія № ET25328, Галфа Лабораторіз Лтд. Юніт 1, Індія</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3247,6 +3247,426 @@
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
     </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>№ 212-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>МЕФЕНАМІНОВА КИСЛОТА, таблетки по 500 мг, по 10 таблеток у блістері, по 2 блістери в пачці, Серія № 100925, ТОВ "Фармацевтична компанія "ФарКоС", Україна</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>№ 213-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>МЕФЕНАМІНОВА КИСЛОТА, таблетки по 500 мг, по 10 таблеток у блістері, по 2 блістери в пачці, Серія № 070425, ТОВ "Фармацевтична компанія "ФарКоС", Україна</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>№ 215-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>№ 216-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Tirzepatide, mounjaro® 15mg KwikPen® 15mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D938367, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>№ 216-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Tirzepatide, mounjaro® 15mg KwikPen® 15mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D949932, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>№ 216-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Tirzepatide, mounjaro® 10mg KwikPen® 10mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D894804, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>№ 216-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Tirzepatide, mounjaro® 10mg KwikPen® 10mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D949702, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>№ 216-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Tirzepatide, mounjaro® 10mg KwikPen® 10mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D918099, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>№ 218-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>MIFMIS KIT, (200mg+200mg), Mifepristone and Misoprostol Tablets 1+4 Tablets Kit, Серія № Produkt A: с. T29Y03; Produkt B: с. T30Y10; Master Batch: STL28Y04, Shree Venkatesh Inretnational Limited (A WHO-OMP Certified Company) Blok №. 311, Kosamba Pardi Road, Village: Nandav, Taluka: Mangrol. Dist: Surat -394125, Gujarat, INDIA</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>№ 219-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>ZIRABEV, 400mg/16ml Infuzyonluk Cozelti, Steril Bevacizumab lntravenoz kullan?m icindir, 1 flakon, Серія № LW9883, Pharmacia&amp;Upjohn Company, LLC 7000 Portage Road, Kalamazoo, ABD</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>№ 220-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>MOLNUVIR, 200mg MOLNUPIRAVIR TABLETS-200mg № 40, Серія № GT2072, SACRED LEAVES Pvt. Ltd, Property No. 74, Ground Floor Gali No. 1, Govindpuri, New Delhi-110019, INDIA</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>№ 221-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Ozempic®, 1mg, raztopina za injiciranje v napolnjenem injekcijskem peresniku semaglutide za subkutano uporabo 1?3-ml injekcijski peresnik sn 4 igle za enkranto uporabo (4 odmerki), Серія № SN 1946823642072, Lot RT6LL67, Novo Nordisk A/S, Novo Alle, DK-2880 Bagsvaerd, Danska</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>№ 222-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>TEN – ALFA, Tenofovir Alafenamide Tablets IP 25 mg, 30  Tablets, Серія № T-210004, LEOWIN HEALTHCARE LLP, MFG. AT: P-2 BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>№ 222-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>DACFOS PLUS+, TABLETS, Sofosbuvir and Daclatasvir Tablets 400 mg/60 mg, 28 tablets, Серія № D-M2002, LEOWIN HEALTHCARE LLP, MFG. AT: P-2 BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>№ 222-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>VELOVIR, Velpatasvir Sofosbuvir Tablets 100mg/400mg, 28 tablets, Серія № V-99003, LEOWIN HEALTHCARE LLP, MFG. AT: P-2 BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>№ 215-001.2/002.0/17-26 від 28.04.2026</t>
+          <t>№ 214-001.2/002.0/17-26 від 28.04.2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
+          <t>МЕФЕНАМІНОВА КИСЛОТА, таблетки по 500 мг по 10 таблеток у блістері, по 2 блістери в пачці, Серія № 151224, ТОВ "Фармацевтична компанія "ФарКоС", Україна</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>№ 216-001.2/002.0/17-26 від 28.04.2026</t>
+          <t>№ 215-001.2/002.0/17-26 від 28.04.2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Tirzepatide, mounjaro® 15mg KwikPen® 15mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D938367, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Tirzepatide, mounjaro® 15mg KwikPen® 15mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D949932, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+          <t>Tirzepatide, mounjaro® 15mg KwikPen® 15mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D938367, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Tirzepatide, mounjaro® 10mg KwikPen® 10mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D894804, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+          <t>Tirzepatide, mounjaro® 15mg KwikPen® 15mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D949932, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Tirzepatide, mounjaro® 10mg KwikPen® 10mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D949702, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+          <t>Tirzepatide, mounjaro® 10mg KwikPen® 10mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D894804, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Tirzepatide, mounjaro® 10mg KwikPen® 10mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D918099, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
+          <t>Tirzepatide, mounjaro® 10mg KwikPen® 10mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D949702, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>№ 218-001.2/002.0/17-26 від 28.04.2026</t>
+          <t>№ 216-001.2/002.0/17-26 від 28.04.2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>MIFMIS KIT, (200mg+200mg), Mifepristone and Misoprostol Tablets 1+4 Tablets Kit, Серія № Produkt A: с. T29Y03; Produkt B: с. T30Y10; Master Batch: STL28Y04, Shree Venkatesh Inretnational Limited (A WHO-OMP Certified Company) Blok №. 311, Kosamba Pardi Road, Village: Nandav, Taluka: Mangrol. Dist: Surat -394125, Gujarat, INDIA</t>
+          <t>Tirzepatide, mounjaro® 10mg KwikPen® 10mg/0.6ml in multiple-dose prefilled pen, 1 pen containing, 2.4 ml solution that can be administered (4 doses), Серія № D918099, Eli Lilly Italia SpA Via Antonio Gramsci 731/733 Sesto Fiorentino FI 50019, Italy</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>№ 219-001.2/002.0/17-26 від 28.04.2026</t>
+          <t>№ 217-001.2/002.0/17-26 від 28.04.2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>ZIRABEV, 400mg/16ml Infuzyonluk Cozelti, Steril Bevacizumab lntravenoz kullan?m icindir, 1 flakon, Серія № LW9883, Pharmacia&amp;Upjohn Company, LLC 7000 Portage Road, Kalamazoo, ABD</t>
+          <t>Altuzan, 400mg/16ml konsantre infuzyon cozeltisi, bevacizumab, 1 adet flakon, Серія № 30037241, Roche Mustahzarlari Sanayi A.S., Maslak/Sariyer, lstanbul</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>№ 220-001.2/002.0/17-26 від 28.04.2026</t>
+          <t>№ 218-001.2/002.0/17-26 від 28.04.2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>MOLNUVIR, 200mg MOLNUPIRAVIR TABLETS-200mg № 40, Серія № GT2072, SACRED LEAVES Pvt. Ltd, Property No. 74, Ground Floor Gali No. 1, Govindpuri, New Delhi-110019, INDIA</t>
+          <t>MIFMIS KIT, (200mg+200mg), Mifepristone and Misoprostol Tablets 1+4 Tablets Kit, Серія № Produkt A: с. T29Y03; Produkt B: с. T30Y10; Master Batch: STL28Y04, Shree Venkatesh Inretnational Limited (A WHO-OMP Certified Company) Blok №. 311, Kosamba Pardi Road, Village: Nandav, Taluka: Mangrol. Dist: Surat -394125, Gujarat, INDIA</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>№ 221-001.2/002.0/17-26 від 28.04.2026</t>
+          <t>№ 219-001.2/002.0/17-26 від 28.04.2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, raztopina za injiciranje v napolnjenem injekcijskem peresniku semaglutide za subkutano uporabo 1?3-ml injekcijski peresnik sn 4 igle za enkranto uporabo (4 odmerki), Серія № SN 1946823642072, Lot RT6LL67, Novo Nordisk A/S, Novo Alle, DK-2880 Bagsvaerd, Danska</t>
+          <t>ZIRABEV, 400mg/16ml Infuzyonluk Cozelti, Steril Bevacizumab lntravenoz kullan?m icindir, 1 flakon, Серія № LW9883, Pharmacia&amp;Upjohn Company, LLC 7000 Portage Road, Kalamazoo, ABD</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>№ 222-001.2/002.0/17-26 від 28.04.2026</t>
+          <t>№ 220-001.2/002.0/17-26 від 28.04.2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>TEN – ALFA, Tenofovir Alafenamide Tablets IP 25 mg, 30  Tablets, Серія № T-210004, LEOWIN HEALTHCARE LLP, MFG. AT: P-2 BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+          <t>MOLNUVIR, 200mg MOLNUPIRAVIR TABLETS-200mg № 40, Серія № GT2072, SACRED LEAVES Pvt. Ltd, Property No. 74, Ground Floor Gali No. 1, Govindpuri, New Delhi-110019, INDIA</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>№ 222-001.2/002.0/17-26 від 28.04.2026</t>
+          <t>№ 221-001.2/002.0/17-26 від 28.04.2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>DACFOS PLUS+, TABLETS, Sofosbuvir and Daclatasvir Tablets 400 mg/60 mg, 28 tablets, Серія № D-M2002, LEOWIN HEALTHCARE LLP, MFG. AT: P-2 BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+          <t>Ozempic®, 1mg, raztopina za injiciranje v napolnjenem injekcijskem peresniku semaglutide za subkutano uporabo 1?3-ml injekcijski peresnik sn 4 igle za enkranto uporabo (4 odmerki), Серія № SN 1946823642072, Lot RT6LL67, Novo Nordisk A/S, Novo Alle, DK-2880 Bagsvaerd, Danska</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>VELOVIR, Velpatasvir Sofosbuvir Tablets 100mg/400mg, 28 tablets, Серія № V-99003, LEOWIN HEALTHCARE LLP, MFG. AT: P-2 BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+          <t>TEN – ALFA, Tenofovir Alafenamide Tablets IP 25 mg, 30  Tablets, Серія № T-210004, LEOWIN HEALTHCARE LLP, MFG. AT: P-2 BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -3666,6 +3666,62 @@
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>№ 222-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>DACFOS PLUS+, TABLETS, Sofosbuvir and Daclatasvir Tablets 400 mg/60 mg, 28 tablets, Серія № D-M2002, LEOWIN HEALTHCARE LLP, MFG. AT: P-2 BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>№ 222-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>VELOVIR, Velpatasvir Sofosbuvir Tablets 100mg/400mg, 28 tablets, Серія № V-99003, LEOWIN HEALTHCARE LLP, MFG. AT: P-2 BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3723,6 +3723,62 @@
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
     </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>№ 222-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>VELOVIR, Velpatasvir &amp; Sofosbuvir tablets 100mg/400 mg N28, Серія № V-99003, LEOWIN, HEALTHCARE LLP MFG. AT.: P-2, BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391776, GUJARAT, INDIA</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>№ 222-001.2/002.0/17-26 від 28.04.2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>TEN-ALFA, Tenofovir alafenamide tablets IP 25 mg №30, Серія № Т-210004, Manufactured &amp; Marketed By: LEOWIN HEALTHCARE LLP MFG. AT: P-2, BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3779,6 +3779,62 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
     </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>№ 223-001.2/002.0/17-26 від 29.04.2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>5-Frotu® 1000mg/20ml, 5-Fluorourasil 1000mg/20ml 1 flakon, Серія № 50958810, компанії Onko Ilac San. ve Tic. A.S. GOSB 1700. Sk. No: 1703 Cayirova / Kocaeli, Туреччина</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>№ 224-001.2/002.0/17-26 від 29.04.2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>29.04.2026</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>МOLNUVIR 200mg, Molnupiravir tablets-200mg N40, Серія № GT2072, Kwality Pharmaceuticals Ltd. Nag Kalan, Majitha Road, Amritsar, INDIA</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3835,6 +3835,34 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
     </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>№ 225-001.2/002.0/17-26 від 30.04.2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>30.04.2026</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>DACFOS PLUS+ TABLETS, Sofosbuvir and Daclatasvir Tablets 400 mg/60 mg N28, Серія № D-142002, LEOVIN HEALTHCARE LLP MFG. AT.: P-2, BIO-TECH PARK, MANJUSAR, SAVLI, INDUSTRIAL ESTATE, VADODARA-391775, GUJARAT, INDIA</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3863,6 +3863,146 @@
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr"/>
     </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>№ 226-001.2/002.0/17-26 від 05.05.2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>СТРЕПСІЛС® З МЕНТОЛОМ ТА ЕВКАЛІПТОМ, льодяники, по 12 льодяників у блістері, по 2 блістери в картонній коробці, Серія № VE421, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>№ 227-001.2/002.0/17-26 від 05.05.2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>ГЛОДУ НАСТОЙКА, настойка для перорального застосування по 100 мл у флаконах полімерних, Серія № 591025, ПП "Кілафф", Україна</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>№ 228-001.2/002.0/17-26 від 05.05.2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА КИСЛОТА, розчин для зовнішнього застосування, спиртовий 1 % по 40 мл у флаконах скляних, укупорених пробками і кришками;, Серія № 320725, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>№ 229-001.2/002.0/17-26 від 05.05.2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>СОФОРИ ЯПОНСЬКОЇ НАСТОЙКА, настойка, по 40 мл у флаконах полімерних, Серія № 040424, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>№ 230-001.2/002.0/17-26 від 05.05.2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>ЗОНІК, капсули тверді по 25 мг; по 14 капсул у блістері; по 2   блістери в картонній упаковці, Серія № 1008141, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4003,6 +4003,34 @@
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
     </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>№ 231-001.2/002.0/17-26 від 06.05.2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>06.05.2026</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>пмс-БУСУЛЬФАН / pms-BUSULFAN, розчин для ін'єкцій, 6 мг/мл, по 10 мл у флаконі;  по 8 флаконів у коробці, Серія № 660609, Фармасайнс Інк., Канада</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4031,6 +4031,90 @@
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr"/>
     </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>№ 232-001.2/002.0/17-26 від 07.05.2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>07.05.2026</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>АВЕЦИН-Н, розчин для інфузій, 400 мг/250 мл, по 250 мл у флаконі;  по 10 флаконів у коробці, Серія № А010624, Нерозфасований продукт, первинна упаковка, вторинна упаковка, контроль: ВІОСЕР С.А. ПАРЕНТЕРАЛ СОЛЮШНС ІНДАСТРІ, Греція Контроль, випуск серії: ТОВ "ФАРМАСЕЛ", Україна, Греція/ Україна</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>№ 233-001.2/002.0/17-26 від 07.05.2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>07.05.2026</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>ГАРДАСИЛ / GARDASIL® ВАКЦИНА ПРОТИ ВІРУСУ ПАПІЛОМИ ЛЮДИНИ (ТИПІВ 6, 11, 16, 18) КВАДРИВАЛЕНТНА РЕКОМБІНАНТНА, суспензія для ін’єкцій; 1 або 10 флаконів (по 0,5 мл (1 доза)) у картонній коробці; 1 або 6 попередньо наповнених шприців (по 0,5 мл (1 доза)) у комплекті з 1 голкою у контурній комірковій упаковці в картонній коробці, Серія № Z003787, MERCK SHARP &amp; DOHME LLC та MSD Ireland (Carlow), -</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>№ 233-001.2/002.0/17-26 від 07.05.2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>07.05.2026</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>ГАРДАСИЛ® 9 ВАКЦИНА ПРОТИ ВІРУСУ ПАПІЛОМИ ЛЮДИНИ 9-ВАЛЕНТНА (РЕКОМБІНАНТНА, АДСОРБОВАНА), суспензія для ін'єкцій, по 0,5 мл (1 доза); по 0,5 мл суспензії у попередньо наповненому шприці (скло) з обмежувачем ходу поршня (силіконізований бромбутиловий еластомер із покриттям FluroTec) та ковпачком (синтетична ізопрен-бромбутилова суміш). По 1 поп, Серія № W036325, 800-672, XG663784, XG66374, W036351, MERCK SHARP &amp; DOHME LLC та MSD Ireland (Carlow), -</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4115,6 +4115,146 @@
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
     </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>№ 234-001.2/002.0/17-26 від 08.05.2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>КУРОСУРФ® (CUROSURF) 80 mg/ml, суспензія для ендотрахеального введення, 80 мг/мл; по 1,5 мл у флаконі; по 1 флакону в картонній коробці, Серія № 1223993, 1222945, 1226966, 1204364, CHIESI FARMACEUTICI S.P.A., -</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>№ 235-001.2/002.0/17-26 від 08.05.2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>всі серії лікарських засобів виробництва ЛЗ виробництва Navesta Pharmaceuticals Pvt Ltd., -, Серія № всі серії, Navesta Pharmaceuticals Pvt Ltd., Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>№ 236-001.2/002.0/17-26 від 08.05.2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>SAIZEN (Somatropin)8 mg/ml (20 MG / 2.5mL), стерилізовані парентеральні розчини малого об'єму, Серія № AB003660, з маркуванням виробника AstraZeneca AB MERCK S/A (ESTRADA DOS BANDEIRANTES, Бразилія</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>№ 237-001.2/002.0/17-26 від 08.05.2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>DEPO MEDROL (Methylprednisolone Acetate) 40mg/1ml, супензія для ін'єкцій, Серія № LX9826, NL5172, ML7753, з маркуванням виробника  PFIZER MANUFACTURING BELGIUM, Бельгія</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>№ 238-001.2/002.0/17-26 від 08.05.2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>08.05.2026</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>DURATESTON (30 + 60 + 100 + 60) mg, cтерилізовані gарентеральні розчини малого об'єму, Серія № 900124, з маркуванням виробника ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4255,6 +4255,62 @@
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr"/>
     </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>№ 239-001.2/002.0/17-26 від 12.05.2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>12.05.2026</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники; по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ТR056, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>№ 240-001.2/002.0/17-26 від 12.05.2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>12.05.2026</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>СТРЕПСІЛС® ОРИГІНАЛЬНИЙ, льодяники; по 12 льодяників у блістері, по 2 блістери в картонній коробці, Серія № VC784, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4311,6 +4311,62 @@
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr"/>
     </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>№ 241-001.2/002.0/17-26 від 13.05.2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>ЛОРНОЛІОФ РОМФАРМ, порошок для розчину для ін'єкцій по 8 мг, по 1 флакону з порошком та 1 ампулі з 2 мл розчинника (вода для ін'єкцій) в наборі у контурній чарунковій упаковці, по 5 наборів у картонній пачці, Серія № 2514091, К.Т.РОМФАРМ КОМПАНІ С.Р.Л., Румунія</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>№ 241-001.2/002.0/17-26 від 13.05.2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>ЛОРНОЛІОФ РОМФАРМ, порошок для розчину для ін'єкцій по 8 мг, по 1 флакону з порошком та 1 ампулі з 2 мл розчинника (вода для ін'єкцій) в наборі у контурній чарунковій упаковці, по 5 наборів у картонній пачці, Серія № 2517362, К.Т.Ромфарм Компані С.Р.Л., Румунія</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4367,6 +4367,34 @@
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr"/>
     </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>№ 242-001.2/002.0/17-26 від 13.05.2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>всі серії ЛЗ виробництва Technophage Investigacao E Desenvolvimento Em Biotecnologia S.A., -, Серія № всі серії, Technophage Investigacao E Desenvolvimento Em Biotecnologia S.A., Португалія</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4395,6 +4395,90 @@
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
     </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>№ 243-001.2/002.0/17-26 від 14.05.2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг; по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці, Серія № ECM25002B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>№ 244-001.2/002.0/17-26 від 14.05.2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>НІМЕЛГАН, гранули для оральної суспензії, по 100 мг; по 30 саше у коробці з картону, Серія № 070324, ТОВ "АСТРАФАРМ", Україна</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>№ 245-001.2/002.0/17-26 від 14.05.2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4479,6 +4479,118 @@
       <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr"/>
     </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>№ 246-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Baclofen-neuraxpharm®, 25mg, Tabletten, 100 Tabletten, Серія № 230012, NEURAXPHARM Arzneimittel GmbH Elisabeth-Selbert-Str. 23 40764, Langenfeld</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>№ 247-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 42726A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>№ 247-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 20914A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>№ 248-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Naratriptan – 1A Pharma®, bei Migrane 2,5 mg Filmtabletten, 2 Filmtabletten № 1, Серія № PT5595, Lek S.A. Ul. Podlipie 16 Strykow 95-010, Polen</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4591,6 +4591,34 @@
       <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr"/>
     </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>№ 249-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Duloxetin Glenmark, 30 mg magensaftresistente Hartkapseln, 28 magensaftresistente Hartkapseln, Серія № 40784, Towa Pharmaceutical Europe, S.L. C/ de Sant Marti, 75-97 Martorelles, 08107 Barcelona, Spanien</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4619,6 +4619,650 @@
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr"/>
     </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 60 Film Kapli Tablet, Серія № 25371012, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 3 Film Kapli Tablet, Серія № 25371015, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>ANDAZOL®, 200mg/10ml Suspansiyon, % 2 suspansiyon 60 ml, Серія № 25020011, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152" ht="40" customHeight="1">
+      <c r="A152" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>NUROFEN® JUNIOR, ERDBEER, 40 mg/ml SUSPENSION ZUM EINNEHMEN 100ml, Серія № AHC903, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153" ht="40" customHeight="1">
+      <c r="A153" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>NUROFEN® IMMEDIA, 400 mg Filmtabletten, 12 Filmtabletten, Серія № TE404, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154" ht="40" customHeight="1">
+      <c r="A154" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>NUROFEN®, 400MG WEICHKAPSELN, 20 Weichkapseln, Серія № TY059, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155" ht="40" customHeight="1">
+      <c r="A155" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>NUROFEN® Immedia, 200 mg, 10 Weichkapseln, Серія № TK473, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156" ht="40" customHeight="1">
+      <c r="A156" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>NUROFEN® JUNIOR, ORANGE, 40 mg/ml SUSPENSION ZUM EINNEHMEN, 100ml, Серія № AHB068, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157" ht="40" customHeight="1">
+      <c r="A157" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>TYLOL®HOT DAY, 12 poset, Серія № 270630, NOBEL ILAC SANAYII VE TICARET A.S. Sancaklar 81100, DUZCE</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158" ht="40" customHeight="1">
+      <c r="A158" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Tadalafil beta, 5 mg 84 Filmtabletten, Серія № 2405018050, betapharm Arzneimittel GmbH Kobelweg 95, 86156, Augsburg</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159" ht="40" customHeight="1">
+      <c r="A159" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Soldesam, 0,2% gocce orali, soluzione Flacone da 10 ml, Серія № 260128, laboratorio farmacologico milanese s.r.l. via monterosso, 273 21042, caronno pertusella (va)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160" ht="40" customHeight="1">
+      <c r="A160" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Tolperison-HCI dura®, 50 mg Filmtabletten, 96 Filmtabletten, Серія № TN47017H, Mylan Germany GmbH Lutticher Stra?e 5 53842, Troisdorf</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161" ht="40" customHeight="1">
+      <c r="A161" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953167, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162" ht="40" customHeight="1">
+      <c r="A162" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D937842, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163" ht="40" customHeight="1">
+      <c r="A163" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Espumisan®, Emulsion 40 mg/ml, 32 ml Emulsion zum Einnehmen, Серія № 51001A, BERLIN-CHEMIE AG Glienicker Weg 125, 12489 Berlin, Deutschland</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164" ht="40" customHeight="1">
+      <c r="A164" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Ben-u-ron® Saft, 40 mg/ml Sirup, 100 ml Sirup Zum Einnehmen, Серія № 306L241, Medinfar Manufacturing S.A. Parque Industrial Armando Martins Tavares Rua Outeiro da Armada No 5 Condeixa-а-Nova 3150-194 Sebal, Portugal</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165" ht="40" customHeight="1">
+      <c r="A165" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Lymphomyosot®N, 100 ml Mischung, Серія № 09982, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166" ht="40" customHeight="1">
+      <c r="A166" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Femoston® conti, 1mg/5mg Filmtabletten, 84 (3x28) Filmtabletten Zum Einnehmen, Серія № 375648, Abbott Biologicals B.V. C.J. van Houtenlaan 36 1381 CP Weesp, Niederlande</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167" ht="40" customHeight="1">
+      <c r="A167" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 08900, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 10944, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169" ht="40" customHeight="1">
+      <c r="A169" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5V443, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170" ht="40" customHeight="1">
+      <c r="A170" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171" ht="40" customHeight="1">
+      <c r="A171" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T599, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>№ 248-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 247-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Naratriptan – 1A Pharma®, bei Migrane 2,5 mg Filmtabletten, 2 Filmtabletten № 1, Серія № PT5595, Lek S.A. Ul. Podlipie 16 Strykow 95-010, Polen</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 13850A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>№ 249-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 248-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Duloxetin Glenmark, 30 mg magensaftresistente Hartkapseln, 28 magensaftresistente Hartkapseln, Серія № 40784, Towa Pharmaceutical Europe, S.L. C/ de Sant Marti, 75-97 Martorelles, 08107 Barcelona, Spanien</t>
+          <t>Naratriptan – 1A Pharma®, bei Migrane 2,5 mg Filmtabletten, 2 Filmtabletten № 1, Серія № PT5595, Lek S.A. Ul. Podlipie 16 Strykow 95-010, Polen</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 249-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 60 Film Kapli Tablet, Серія № 25371012, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>Duloxetin Glenmark, 30 mg magensaftresistente Hartkapseln, 28 magensaftresistente Hartkapseln, Серія № 40784, Towa Pharmaceutical Europe, S.L. C/ de Sant Marti, 75-97 Martorelles, 08107 Barcelona, Spanien</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 3 Film Kapli Tablet, Серія № 25371015, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 60 Film Kapli Tablet, Серія № 25371012, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 200mg/10ml Suspansiyon, % 2 suspansiyon 60 ml, Серія № 25020011, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 3 Film Kapli Tablet, Серія № 25371015, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® JUNIOR, ERDBEER, 40 mg/ml SUSPENSION ZUM EINNEHMEN 100ml, Серія № AHC903, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>ANDAZOL®, 200mg/10ml Suspansiyon, % 2 suspansiyon 60 ml, Серія № 25020011, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® IMMEDIA, 400 mg Filmtabletten, 12 Filmtabletten, Серія № TE404, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® JUNIOR, ERDBEER, 40 mg/ml SUSPENSION ZUM EINNEHMEN 100ml, Серія № AHC903, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN®, 400MG WEICHKAPSELN, 20 Weichkapseln, Серія № TY059, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® IMMEDIA, 400 mg Filmtabletten, 12 Filmtabletten, Серія № TE404, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® Immedia, 200 mg, 10 Weichkapseln, Серія № TK473, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN®, 400MG WEICHKAPSELN, 20 Weichkapseln, Серія № TY059, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® JUNIOR, ORANGE, 40 mg/ml SUSPENSION ZUM EINNEHMEN, 100ml, Серія № AHB068, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® Immedia, 200 mg, 10 Weichkapseln, Серія № TK473, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>TYLOL®HOT DAY, 12 poset, Серія № 270630, NOBEL ILAC SANAYII VE TICARET A.S. Sancaklar 81100, DUZCE</t>
+          <t>NUROFEN® JUNIOR, ORANGE, 40 mg/ml SUSPENSION ZUM EINNEHMEN, 100ml, Серія № AHB068, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Tadalafil beta, 5 mg 84 Filmtabletten, Серія № 2405018050, betapharm Arzneimittel GmbH Kobelweg 95, 86156, Augsburg</t>
+          <t>TYLOL®HOT DAY, 12 poset, Серія № 270630, NOBEL ILAC SANAYII VE TICARET A.S. Sancaklar 81100, DUZCE</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Soldesam, 0,2% gocce orali, soluzione Flacone da 10 ml, Серія № 260128, laboratorio farmacologico milanese s.r.l. via monterosso, 273 21042, caronno pertusella (va)</t>
+          <t>Tadalafil beta, 5 mg 84 Filmtabletten, Серія № 2405018050, betapharm Arzneimittel GmbH Kobelweg 95, 86156, Augsburg</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Tolperison-HCI dura®, 50 mg Filmtabletten, 96 Filmtabletten, Серія № TN47017H, Mylan Germany GmbH Lutticher Stra?e 5 53842, Troisdorf</t>
+          <t>Soldesam, 0,2% gocce orali, soluzione Flacone da 10 ml, Серія № 260128, laboratorio farmacologico milanese s.r.l. via monterosso, 273 21042, caronno pertusella (va)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953167, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Tolperison-HCI dura®, 50 mg Filmtabletten, 96 Filmtabletten, Серія № TN47017H, Mylan Germany GmbH Lutticher Stra?e 5 53842, Troisdorf</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D937842, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Escitalopram A?Z, 20 mg Filmtabletten, 100 Filmtabletten, Серія № 16515423, Merckle GmbH Ludwig-Merckle-Str. 3 89143, Blaubeuren</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Espumisan®, Emulsion 40 mg/ml, 32 ml Emulsion zum Einnehmen, Серія № 51001A, BERLIN-CHEMIE AG Glienicker Weg 125, 12489 Berlin, Deutschland</t>
+          <t>Ezetimib Arasto, 10 mg Tabletten, 50 Tabletten, Серія № 26046T5, Laboratorios Medicamentos Internacionales S.A. Calle Solana 26 28850 Torrejon de Ardoz (Madrid), Spanien</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Ben-u-ron® Saft, 40 mg/ml Sirup, 100 ml Sirup Zum Einnehmen, Серія № 306L241, Medinfar Manufacturing S.A. Parque Industrial Armando Martins Tavares Rua Outeiro da Armada No 5 Condeixa-а-Nova 3150-194 Sebal, Portugal</t>
+          <t>Sab simplex®, 69,19 mg/ml Suspension zum Einnehmen Simeticon, 30 ml, Серія № 01261, Delpharm Orleans 5, avenue de Concyr 45071 Orleans Cedex 2, Frankreich</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 100 ml Mischung, Серія № 09982, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953167, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Femoston® conti, 1mg/5mg Filmtabletten, 84 (3x28) Filmtabletten Zum Einnehmen, Серія № 375648, Abbott Biologicals B.V. C.J. van Houtenlaan 36 1381 CP Weesp, Niederlande</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D937842, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 08900, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953182, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 10944, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Mounjaro® KwikPen®, 10 mg/Dosis, Injektionslosung in einem Fertigpen 3 Pens (jeder Pen gibt 4 Dosen ad), Серія № D871349D, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5V443, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Espumisan®, Emulsion 40 mg/ml, 32 ml Emulsion zum Einnehmen, Серія № 51001A, BERLIN-CHEMIE AG Glienicker Weg 125, 12489 Berlin, Deutschland</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ben-u-ron® Saft, 40 mg/ml Sirup, 100 ml Sirup Zum Einnehmen, Серія № 306L241, Medinfar Manufacturing S.A. Parque Industrial Armando Martins Tavares Rua Outeiro da Armada No 5 Condeixa-а-Nova 3150-194 Sebal, Portugal</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T599, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Lymphomyosot®N, 100 ml Mischung, Серія № 09982, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -5262,6 +5262,174 @@
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172" ht="40" customHeight="1">
+      <c r="A172" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Femoston® conti, 1mg/5mg Filmtabletten, 84 (3x28) Filmtabletten Zum Einnehmen, Серія № 375648, Abbott Biologicals B.V. C.J. van Houtenlaan 36 1381 CP Weesp, Niederlande</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173" ht="40" customHeight="1">
+      <c r="A173" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 08900, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174" ht="40" customHeight="1">
+      <c r="A174" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 10944, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5V443, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T599, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5431,6 +5431,34 @@
       <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr"/>
     </row>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>№ 258-001.2/002.0/17-26 від 18.05.2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>18.05.2026</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5459,6 +5459,34 @@
       <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr"/>
     </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>№ 259-001.2/002.0/17-26 від 21.05.2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>21.05.2026</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>ВАЛОКОРМІД, краплі оральні, по 25 мл у флаконах;, Серія № 11225, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5487,6 +5487,62 @@
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr"/>
     </row>
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>№ 260-001.2/002.0/17-26 від 22.05.2026</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>GENTEAL GEL, гель для очей, Серія № 2X11, EXCELVISION 27 RUE DE LA LOMBARDIER ANNONAY, 07100, FRENCH REPUBLIC, Франція</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>№ 261-001.2/002.0/17-26 від 22.05.2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>22.05.2026</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>HEROGEL, суспензія для перорального застосування, ПЕТ-пляшка 240 мл, Серія № 83300804, Heromycin pharma Co., Ltd., -</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5543,6 +5543,34 @@
       <c r="G181" s="2" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr"/>
     </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>№ 262-001.2/002.0/17-26 від 25.05.2026</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>25.05.2026</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>ЕЗОЛОНГ®-20, таблетки, вкриті плівковою оболонкою, по 20 мг; по 7 таблеток у блістері; по 2 блістери у картонній коробці, Серія № ЕЕР25008А1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr"/>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5571,6 +5571,34 @@
       <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr"/>
     </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>№ 263-001.2/002.0/17-26 від 26.05.2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>26.05.2026</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг, по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці;, Серія № ЕСМ25001В1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5599,6 +5599,286 @@
       <c r="G183" s="2" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr"/>
     </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>№ 264-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>MONSEL`S SOLUTION, розчин, Серія № 640911253, Premier Medical Products, -</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>№ 265-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>APALIN 250 mg Injection, 125 mg/1 mL, розчин для ін`єкцій по 2 мл в ампулі; по 10 ампул у картонній пачці, Серія № 242837T, Duopharma (M) Sdn. Bhd., Малайзія</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>№ 266-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>AMPICILLIN SODIUM, порошок для ін'єкцій, Серія № 315089, TP Drug Laboratories (1969) Co.,Ltd (Praram 2 Branch), -</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>№ 267-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>FLEBOGAMMA DIF 5%, 50 mg/ml, розчин для інфузій, 400 мл, Серія № G04K181561, Instituto Grifols, S.A facility in Parets del Valles, Barcelona, Іспанія</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>№ 268-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>DURATESTON, 30  mg, 60  mg, 100 mg, cтерилізовані парентеральні розчини малого об'єму, Серія № 945858, ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>АА PHARMA HYDROXYZINE CAPSULE, 10 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW6213A, AW6448A, AW8160A, AW8161A, AW8177A, Catalent Ontario Limited, Канада</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>№ 270-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>GLUMET XR 500 mg, таблетки № 10 у блістері, у картонній коробці № 100, Серія № 5028486, 5032332, 5032334, 2034104, 5034103, 5034100, 5036722, 5036724, 5036723, 5037167, 5036983, 5036984, 5038424, 5039549, 5040444, Pharmaniaga Manufacturing Berhad, Selangor, Малайзія</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>№ 271-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>PALIFREN LONG 150 mg ( Paliperidonum), пролонгована суспензія для ін’єкцій у попередньо наповненому шприці, Серія № 4201120, 4300099, 4201591, PHARMATHEN INTERNATIONAL S.A Rodopi, Evrou, Греція</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>№ 272-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>FOSFATO DISSODICO DE DEXAMETASONA, 4 MG/ML, парентеральні розчини малого об’єму, стерилізовані термінальним методом, № 50, Серія № 25091566, HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, Бразилія</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5879,6 +5879,34 @@
       <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr"/>
     </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>№ 273-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>SPHERICAL ADSORPTIVE CARBON (Black Tablets), № 336, Серія № TK24804, TK24Y18, TK24Y19, TK25115, TK25117, TK25209, TK25306, TK25307, TK25308, TK25908, TT24Y05, TT24Z13, TP24601, TP24607, TP25222, TP25804, KUREHA Corporation, -</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>№ 270-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>GLUMET XR 500 mg, таблетки № 10 у блістері, у картонній коробці № 100, Серія № 5028486, 5032332, 5032334, 2034104, 5034103, 5034100, 5036722, 5036724, 5036723, 5037167, 5036983, 5036984, 5038424, 5039549, 5040444, Pharmaniaga Manufacturing Berhad, Selangor, Малайзія</t>
+          <t>АА PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>№ 271-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 270-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>PALIFREN LONG 150 mg ( Paliperidonum), пролонгована суспензія для ін’єкцій у попередньо наповненому шприці, Серія № 4201120, 4300099, 4201591, PHARMATHEN INTERNATIONAL S.A Rodopi, Evrou, Греція</t>
+          <t>GLUMET XR 500 mg, таблетки № 10 у блістері, у картонній коробці № 100, Серія № 5028486, 5032332, 5032334, 2034104, 5034103, 5034100, 5036722, 5036724, 5036723, 5037167, 5036983, 5036984, 5038424, 5039549, 5040444, Pharmaniaga Manufacturing Berhad, Selangor, Малайзія</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>№ 272-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 271-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>FOSFATO DISSODICO DE DEXAMETASONA, 4 MG/ML, парентеральні розчини малого об’єму, стерилізовані термінальним методом, № 50, Серія № 25091566, HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, Бразилія</t>
+          <t>PALIFREN LONG 150 mg ( Paliperidonum), пролонгована суспензія для ін’єкцій у попередньо наповненому шприці, Серія № 4201120, 4300099, 4201591, PHARMATHEN INTERNATIONAL S.A Rodopi, Evrou, Греція</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>№ 273-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 272-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>SPHERICAL ADSORPTIVE CARBON (Black Tablets), № 336, Серія № TK24804, TK24Y18, TK24Y19, TK25115, TK25117, TK25209, TK25306, TK25307, TK25308, TK25908, TT24Y05, TT24Z13, TP24601, TP24607, TP25222, TP25804, KUREHA Corporation, -</t>
+          <t>FOSFATO DISSODICO DE DEXAMETASONA, 4 MG/ML, парентеральні розчини малого об’єму, стерилізовані термінальним методом, № 50, Серія № 25091566, HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, Бразилія</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -5906,6 +5906,34 @@
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>№ 273-001.2/002.0/17-26 від 27.05.2026</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>27.05.2026</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>SPHERICAL ADSORPTIVE CARBON (Black Tablets), № 336, Серія № TK24804, TK24Y18, TK24Y19, TK25115, TK25117, TK25209, TK25306, TK25307, TK25308, TK25908, TT24Y05, TT24Z13, TP24601, TP24607, TP25222, TP25804, KUREHA Corporation, -</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5935,6 +5935,34 @@
       <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr"/>
     </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>№ 275-001.2/002.0/17-26 від 01.06.2026</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>АБРОЛ®, таблетки по 30 мг; по 10 таблеток у блістері; по 2 блістери в упаковці, Серія № SAA5001, ТОВ "КУСУМ ФАРМ", Україна</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>№ 275-001.2/002.0/17-26 від 01.06.2026</t>
+          <t>№ 274-001.2/002.0/17-26 від 01.06.2026</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>АБРОЛ®, таблетки по 30 мг; по 10 таблеток у блістері; по 2 блістери в упаковці, Серія № SAA5001, ТОВ "КУСУМ ФАРМ", Україна</t>
+          <t>ЄВРОФАСТ КОМБІ, капсули м'які, 200 мг/500 мг, по 10 капсул у блістері; по 1 блістеру в картонній коробці, Серія № GX3010, Олів Хелскер, Індія</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -5962,6 +5962,174 @@
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>№ 274-001.2/002.0/17-26 від 01.06.2026</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>ЄВРОФАСТ КОМБІ, капсули м'які, 200 мг/500 мг, по 10 капсул у блістері; по 1 блістеру в картонній коробці, Серія № GX3009, Олів Хелскер, Індія</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>№ 275-001.2/002.0/17-26 від 01.06.2026</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>АБРОЛ®, таблетки по 30 мг; по 10 таблеток у блістері; по 2 блістери в упаковці, Серія № SAA5001, ТОВ "КУСУМ ФАРМ", Україна</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>№ 276-001.2/002.0/17-26 від 01.06.2026</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>ФЕНІБУТ, таблетки по 250 мг по 10 таблеток у блістері, по 2 блістери у коробці з картону, Серія № 070925, ТОВ "АСТРАФАРМ", Україна,</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>№ 277-001.2/002.0/17-26 від 01.06.2026</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг, по 10 таблеток у блістері; по 2 блістери в пачці з картону, Серія № 170226, ПАТ "Лубнифарм", Україна</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>№ 278-001.2/002.0/17-26 від 01.06.2026</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>OZEMPIC (Semaglutide), 0.25 mg-0.5 mg/doses, розчин для ін'єкцій у попередньо заповненій шприц-ручці, у картонній коробці з 1 ручкою та 6 одноразовими голками                       (6 доз), Серія № PP5K617, з маркуванням виробника Novo Nordisk A/S., -</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>№ 279-001.2/002.0/17-26 від 01.06.2026</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>01.06.2026</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>МЕТРОГІЛ®, гель для зовнішнього застосування, 10 мг/г, по 30 г у тубі з ламінованого пластику, по 1 тубі в картонній коробці, Серія № PGN6003, Юнік Фармасьютикал Лабораторіз (відділення фірми "Дж. Б. Кемікалз енд Фармасьютикалз Лтд."), Індія</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6131,6 +6131,34 @@
       <c r="G202" s="2" t="inlineStr"/>
       <c r="H202" s="2" t="inlineStr"/>
     </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>№ 280-001.2/002.0/17-26 від 02.06.2026</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>02.06.2026</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>ПЕРЕКИС - ВІШФА, розчин для зовнішнього застосування 3 %; по 100 мл у флаконах полімерних, Серія № 60825, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr"/>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6159,6 +6159,34 @@
       <c r="G203" s="2" t="inlineStr"/>
       <c r="H203" s="2" t="inlineStr"/>
     </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>№ 281-001.2/002.0/17-26 від 03.06.2026</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>03.06.2026</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>TRZ-10 (Tirzepatide (rDNA origin), контейнер із прозорого пластику, що містить два скляних флакони: TRZ-10, 10 mg/vial; WATER (bacteriostatic USP) 3ml/vial, Серія № всі серії, із маркуванням GENIK, Netherlands</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6187,6 +6187,34 @@
       <c r="G204" s="2" t="inlineStr"/>
       <c r="H204" s="2" t="inlineStr"/>
     </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>№ Проект від 05.06.2026</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>BAIRABRON® (Trimebutine and Simethicone) 200 mg/75 mg, таблетки № 24 у картонній коробці, Серія № 0418D25, 0513M25, 0514M25A, 0802G25, 0803G25, 0804G25, 1112N25A, Protein, S.A. de C.V., -</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>№ Проект від 05.06.2026</t>
+          <t>№ 282-001.2/002.0/17-26 від 05.06.2026</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -6214,6 +6214,90 @@
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr"/>
       <c r="H205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>№ 283-001.2/002.0/17-26 від 05.06.2026</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>ALDOMET 250 mg (Methyldopa), таблетки, вкриті оболонкою, Серія № P0019875, ASPEN SA OSD, Південно-Африканська Республіка</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>№ 284-001.2/002.0/17-26 від 05.06.2026</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>RIVIAL MV12, Ergocalciferol 5 mcg +Biotina 60 mcg + Acido Folico 400 mcg + Cianocobalamina 5 mcg + Riboflavina 5fosfato sodico 3.6 mg + Piridoxina clorhidrato 4.86 mg + Tiamina clorhidrato, 50 ліофілізованих ампул (лише для використання в лікарні), Серія № G/099, G/101, G/105, G/111, G/112, G/118, H/099, Н/105, H/111, H/112, I/112, LABORATORIOS SOLKOTAL S.A.,, Аргентина</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>№ Проект від 05.06.2026</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>05.06.2026</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>BAIRABRON® (Trimebutine and Simethicone) 200 mg/75 mg, таблетки № 24 у картонній коробці, Серія № 0418D25, 0513M25, 0514M25A, 0802G25, 0803G25, 0804G25, 1112N25A, Protein, S.A. de C.V., -</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H208"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6299,6 +6299,62 @@
       <c r="G208" s="2" t="inlineStr"/>
       <c r="H208" s="2" t="inlineStr"/>
     </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>№ 285-001.2/002.0/17-26 від 09.06.2026</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>КАРДАК, таблетки вкриті плівковою оболонкою, по 40 мг, по 10 таблеток у блістері, по 3 блістера у пачці з картону, Серія № SBM2500740B, Ауробіндо Фарма Лімітед, Формулейшин, Юніт-XV, Індія</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>№ 285-001.2/002.0/17-26 від 09.06.2026</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>КАРДАК, таблетки вкриті плівковою оболонкою, по 20 мг, по 10 таблеток у блістері, по 3 блістера у пачці з картону, Серія № SBM2500420F, Ауробіндо Фарма Лімітед, Формулейшин, Юніт-XV, Індія</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6355,6 +6355,34 @@
       <c r="G210" s="2" t="inlineStr"/>
       <c r="H210" s="2" t="inlineStr"/>
     </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>№ 286-001.2/002.0/17-26 від 09.06.2026</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>09.06.2026</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>ОФЛОКСАЦИН ШТУЛЬН ЮД, краплі очні, 3 мг/1 мл; по 0,5 мл у туб-крапельниці, що містить одну дозу очних крапель Офлоксацин Штульн ЮД.По 5 туб-крапельниць з'єднаних у блок; по 2 блоки (№10) в алюмінієвій упаковці у  картонній коробці, Серія № 24G041, Фарма Штульн ГмбХ, Німеччина</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:H212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6383,6 +6383,34 @@
       <c r="G211" s="2" t="inlineStr"/>
       <c r="H211" s="2" t="inlineStr"/>
     </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>№ 287-001.2/002.0/17-26 від 10.06.2026</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>10.06.2026</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>СПИРТ ЕТИЛОВИЙ 96%, розчин для зовнішнього застосування 96 %, по 100 мл у флаконах, Серія № 170725, ПрАТ "Біолік", Україна</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H212"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6411,6 +6411,202 @@
       <c r="G212" s="2" t="inlineStr"/>
       <c r="H212" s="2" t="inlineStr"/>
     </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>№ 288-001.2/002.0/17-26 від 11.06.2026</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>TEIKOPLANINA BRADEX, 200 mg, порошок та розчинник для розчину для ін'єкцій/інфузій або перорального розчину, Серія № 2457043, DEMO S.A. PHARMACEUTICAL INDUSTRY, Греція</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>№ 289-001.2/002.0/17-26 від 11.06.2026</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>CONVULEX, (Valproic acid) 50 mg/ml, сіроп для дітей, скляний флакон об'ємом 100 мл, Серія № M00651, G.L. Pharma GmbH Standort 1160 Wien, Австрія</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>№ 290-001.2/002.0/17-26 від 11.06.2026</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Re N ToxTM, clostridium botulinum toxin type A, 100 units, 1 vial, Серія № всі серії, Pharma Research BIO Co., Ltd., Republic of Korea</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>№ 291-001.2/002.0/17-26 від 11.06.2026</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>CARDIOPLEGIC SOLUTION IB, 500 ml, внутрішньосерцевий розчин, Серія № 2621440229, 2621440230, 2621440231, 2621440232, 2621440233, 2621440234, 2621440235, 2621440236, 2621440237, 2621440287, 2621440288, 2621440289, 2621440290, 2621440291, 2621440292, 2621440293,2621440294, 2621440295, 2622240318, 2622240319, 2622240320, 2622240321, 2622240322, 2622240323, 2622240324, 2622240325, 2622240326, 2622240327, 2622240328,2622240329, B. Braun Medical, S.A. Carretera de Terrassa, Іспанія</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>№ 291-001.2/002.0/17-26 від 11.06.2026</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>CARDIOPLEGIC SOLUTION (HB) WITHOUT POTASSIUM, 500 ml,, внутрішньосерцевий розчин, Серія № 2621340250, 2621340251, 2621340252, 2621340253, 2621340255, 2621340256, 2621340257, 2621340414, B. Braun Medical, S.A. Carretera de Terrassa, Іспанія</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>№ 291-001.2/002.0/17-26 від 11.06.2026</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>CARDIOPLEGIC SOLUTION (HB) WITH POTASSIUM, 500 ml, внутрішньосерцевий розчин, Серія № 2621340258, 2621340259, 2621340260, 2621340261, B. Braun Medical, S.A. Carretera de Terrassa, Іспанія</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>№ 292-001.2/002.0/17-26 від 11.06.2026</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>11.06.2026</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>СЕПТЕФРИЛ ВЕРДЕ ВІД БОЛЮ В ГОРЛІ, льодяники по 3 мг, зі смаком меду та апельсина; по 10 льодяників у блістері; по 2 блістери в пачці, Серія № 00001, контроль серії: ІНФАРМЕЙД, С.Л., Іспанія контроль серії (мікробіологічний): Лабораторіо Ечіварне, С.А., Іспанія виробництво готової продукції, первинне і вторинне пакування, випуск серії: ЛОЗІ'С ФАРМАСЬЮТІКАЛС С.Л., Іспанія, Іспанія</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6607,6 +6607,34 @@
       <c r="G219" s="2" t="inlineStr"/>
       <c r="H219" s="2" t="inlineStr"/>
     </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>№ 293-001.2/002.0/17-26 від 17.06.2026</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>17.06.2026</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>АСКОРІЛ ЕКСПЕКТОРАНТ, сироп; по 100 мл у пластикових флаконах; по 1 флакону разом з мірним ковпачком у картонній упаковці, Серія № 05251272A, Гленмарк Фармасьютикалз Лтд., Індія</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6635,6 +6635,62 @@
       <c r="G220" s="2" t="inlineStr"/>
       <c r="H220" s="2" t="inlineStr"/>
     </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>№ 294-001.2/002.0/17-26 від 19.06.2026</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>ALBUNATE® 20%, розчин для ін'єкцій, флакон у картонній коробці., Серія № P100542812, P100564605, P100622643, P100544607, з маркуванням виробника CSL Behring AG, -</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr"/>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>№ 294-001.2/002.0/17-26 від 19.06.2026</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>HIGLOBIN® 5 g, розчин для ін'єкцій, флакон у картонній коробці, Серія № P100687928, P100697335, P100583631, P100649549, P100592175, P100687928, P100658686, P100681628, P100697335, P100589056, P100707988, P100662582, P100566928, P100600969, P100641596, P100574249, P100626316, P100632461, P100549898, P100592194, P100626311, P100594944, P100551256, P100592166, P100582242, P100539704, P100624139, P100454993, CSL Behring AG., -</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr"/>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6691,6 +6691,90 @@
       <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr"/>
     </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>№ 295-001.2/002.0/17-26 від 19.06.2026</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>ДИКЛО-Ф, краплі очні, 0,1 %, по 5 мл у флаконі-крапельниці; по 1 флакону-крапельниці в пачці, Серія № N25338C, СЕНТІСС ФАРМА  ПВТ.ЛТД., Індія</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr"/>
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>№ 297-001.2/002.0/17-26 від 19.06.2026</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>JAKAVI 20 mg, таблетки № 50, Серія № AVT50, з маркуванням виробника Novartis, -</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr"/>
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>№ 297-001.2/002.0/17-26 від 19.06.2026</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>19.06.2026</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>JAKAVI 15 mg, таблетки № 56, Серія № SGL04, з маркуванням виробника Novartis, -</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr"/>
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6775,6 +6775,286 @@
       <c r="G225" s="2" t="inlineStr"/>
       <c r="H225" s="2" t="inlineStr"/>
     </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по 25 г у контейнерах; по 20 г або 25 г у тубах; по 20 г або по 25 г у тубі; по 1 тубі в пачці; по 20 г або по 25 г у тубах ламінатних; по 20 г або по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 060924, 010125, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по  25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 071024, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по 25 г у  тубі; по 1 тубі в пачці;, Серія № 081124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по 25 г у тубі; по 1 тубі в пачці;, Серія № 020325, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 060423, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 050524, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>№ 299-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>ГІДРОКОРТИЗОН, мазь 1 %; по  15 г у тубі; по 1 тубі в картонній пачці, Серія № 11257, ТОВ “Арпімед”, Республіка Вірменія</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>№ 299-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>ГІДРОКОРТИЗОН, мазь 1 %; по 10 г   у тубі; по 1 тубі в картонній пачці, Серія № 11255, ТОВ “Арпімед”, Республіка Вірменія</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>№ 300-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>ДІАГНОЛ®, порошок для орального розчину, 64 г/пакет по 73,69 г порошку у пакеті; по 4 пакети в пачці з картону, Серія № DMIR008780/2, АТ "Фармак", Україна</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>№ 301-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>ОВЕСТИН®, крем вагінальний, 1 мг/г; по 15 г у тубі; по 1 тубі у комплекті з аплікатором в пачці, Серія № 24Е001, Аспен Бад-Ольдесло ГмбХ. (виробник відповідальний за виробництво, первинне та вторинне пакування, контроль якості та випуск серії), Німеччина</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr"/>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H235"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7055,6 +7055,174 @@
       <c r="G235" s="2" t="inlineStr"/>
       <c r="H235" s="2" t="inlineStr"/>
     </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>№ 302-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>АСКОРІЛ, таблетки, по 10 таблеток у блістері; по 2 блістери в картонній упаковці, Серія № 10252263, Гленмарк Фармасьютикалз Лтд., Індія</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>№ 303-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>KEYTRUDA (pembrolizumab), 100mg/4mL, асептично оброблені парентеральні розчини малого об'єму, Серія № Y019149, з маркуванням виробника MERCK SHARP &amp; DOHME CORP., -</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr"/>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>№ 304-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>VECTIBIX 100 mg/5 mL (Panitumumab), флакон у картонній коробці, Серія № 2051100, 1166523, 1130818, 3377806, Amgen Manufacturing Limited, -</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>CLORAPREP 1 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 60, Серія № 3196393, 3325915, 3325918, 4021709, 4058230, 4058232, 4086014, 4086017, 4149178, 4155875, 4206632, 4210656, 4212800, 4233418, 4267729, 4270388, 4302021, 4302040, 4305711, 4324566, 4348098, 5026580, 5052205, 5081618, 5127264, 5133556, 5127263, 3261045, 3321422, 3346244, 4023071, 4058231, 4086024, 4151136, 4192080, 4212805, 4212806, 4233411, 4233411, 4270390, 4192033, 4212808, 4233414, 4267722, 4302029, 4325766, 4348096, 5026579, 5052200, 5133411, 3294918, 4206633, 4326463, BD Infection Prevention, Бельгія</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>CHLORAPREP FREPP 1,5 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 20, Серія № 3313882, 4020572, 4177103, 4264525, 3138975, 3227659, 3313884, 4169640, 4235732, 4295374, 5036189, 5037270, 5076598, 3138978, 4058927, 4085811, 4107060, 4138630, 4198196, 4198199, 4235722, 4264522, 4295373, 4330648, 5016735, 5037282, 5076588, 5114831, BD Infection Prevention, Бельгія</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr"/>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>№ 306-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>CRISCY (SOMATROPINE), асептично оброблені парентеральні розчини малого об'єму, Серія № 22030133, з маркуванням виробника CRISTALIA PRODUTOS QUIMICOS FARMACEUTICOS LTDA, -</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr"/>
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>№ 299-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>ГІДРОКОРТИЗОН, мазь 1 %; по  15 г у тубі; по 1 тубі в картонній пачці, Серія № 11257, ТОВ “Арпімед”, Республіка Вірменія</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г ламінатній тубі;  по 1 тубі в пачці, Серія № 131224, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>№ 299-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>ГІДРОКОРТИЗОН, мазь 1 %; по 10 г   у тубі; по 1 тубі в картонній пачці, Серія № 11255, ТОВ “Арпімед”, Республіка Вірменія</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній пачці, Серія № 070724, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>№ 300-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>ДІАГНОЛ®, порошок для орального розчину, 64 г/пакет по 73,69 г порошку у пакеті; по 4 пакети в пачці з картону, Серія № DMIR008780/2, АТ "Фармак", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 2% по 25 г у тубі, по 1 тубі у пачці, Серія № 040924, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>№ 301-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 299-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>ОВЕСТИН®, крем вагінальний, 1 мг/г; по 15 г у тубі; по 1 тубі у комплекті з аплікатором в пачці, Серія № 24Е001, Аспен Бад-Ольдесло ГмбХ. (виробник відповідальний за виробництво, первинне та вторинне пакування, контроль якості та випуск серії), Німеччина</t>
+          <t>ГІДРОКОРТИЗОН, мазь 1 %; по  15 г у тубі; по 1 тубі в картонній пачці, Серія № 11257, ТОВ “Арпімед”, Республіка Вірменія</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>№ 302-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 299-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>АСКОРІЛ, таблетки, по 10 таблеток у блістері; по 2 блістери в картонній упаковці, Серія № 10252263, Гленмарк Фармасьютикалз Лтд., Індія</t>
+          <t>ГІДРОКОРТИЗОН, мазь 1 %; по 10 г   у тубі; по 1 тубі в картонній пачці, Серія № 11255, ТОВ “Арпімед”, Республіка Вірменія</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>№ 303-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 300-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>KEYTRUDA (pembrolizumab), 100mg/4mL, асептично оброблені парентеральні розчини малого об'єму, Серія № Y019149, з маркуванням виробника MERCK SHARP &amp; DOHME CORP., -</t>
+          <t>ДІАГНОЛ®, порошок для орального розчину, 64 г/пакет по 73,69 г порошку у пакеті; по 4 пакети в пачці з картону, Серія № DMIR008780/2, АТ "Фармак", Україна</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>№ 304-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 301-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>VECTIBIX 100 mg/5 mL (Panitumumab), флакон у картонній коробці, Серія № 2051100, 1166523, 1130818, 3377806, Amgen Manufacturing Limited, -</t>
+          <t>ОВЕСТИН®, крем вагінальний, 1 мг/г; по 15 г у тубі; по 1 тубі у комплекті з аплікатором в пачці, Серія № 24Е001, Аспен Бад-Ольдесло ГмбХ. (виробник відповідальний за виробництво, первинне та вторинне пакування, контроль якості та випуск серії), Німеччина</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 302-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>CLORAPREP 1 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 60, Серія № 3196393, 3325915, 3325918, 4021709, 4058230, 4058232, 4086014, 4086017, 4149178, 4155875, 4206632, 4210656, 4212800, 4233418, 4267729, 4270388, 4302021, 4302040, 4305711, 4324566, 4348098, 5026580, 5052205, 5081618, 5127264, 5133556, 5127263, 3261045, 3321422, 3346244, 4023071, 4058231, 4086024, 4151136, 4192080, 4212805, 4212806, 4233411, 4233411, 4270390, 4192033, 4212808, 4233414, 4267722, 4302029, 4325766, 4348096, 5026579, 5052200, 5133411, 3294918, 4206633, 4326463, BD Infection Prevention, Бельгія</t>
+          <t>АСКОРІЛ, таблетки, по 10 таблеток у блістері; по 2 блістери в картонній упаковці, Серія № 10252263, Гленмарк Фармасьютикалз Лтд., Індія</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 303-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>CHLORAPREP FREPP 1,5 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 20, Серія № 3313882, 4020572, 4177103, 4264525, 3138975, 3227659, 3313884, 4169640, 4235732, 4295374, 5036189, 5037270, 5076598, 3138978, 4058927, 4085811, 4107060, 4138630, 4198196, 4198199, 4235722, 4264522, 4295373, 4330648, 5016735, 5037282, 5076588, 5114831, BD Infection Prevention, Бельгія</t>
+          <t>KEYTRUDA (pembrolizumab), 100mg/4mL, асептично оброблені парентеральні розчини малого об'єму, Серія № Y019149, з маркуванням виробника MERCK SHARP &amp; DOHME CORP., -</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>№ 306-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 304-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>CRISCY (SOMATROPINE), асептично оброблені парентеральні розчини малого об'єму, Серія № 22030133, з маркуванням виробника CRISTALIA PRODUTOS QUIMICOS FARMACEUTICOS LTDA, -</t>
+          <t>VECTIBIX 100 mg/5 mL (Panitumumab), флакон у картонній коробці, Серія № 2051100, 1166523, 1130818, 3377806, Amgen Manufacturing Limited, -</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -7222,6 +7222,90 @@
       <c r="F241" s="2" t="inlineStr"/>
       <c r="G241" s="2" t="inlineStr"/>
       <c r="H241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>CLORAPREP 1 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 60, Серія № 3196393, 3325915, 3325918, 4021709, 4058230, 4058232, 4086014, 4086017, 4149178, 4155875, 4206632, 4210656, 4212800, 4233418, 4267729, 4270388, 4302021, 4302040, 4305711, 4324566, 4348098, 5026580, 5052205, 5081618, 5127264, 5133556, 5127263, 3261045, 3321422, 3346244, 4023071, 4058231, 4086024, 4151136, 4192080, 4212805, 4212806, 4233411, 4233411, 4270390, 4192033, 4212808, 4233414, 4267722, 4302029, 4325766, 4348096, 5026579, 5052200, 5133411, 3294918, 4206633, 4326463, BD Infection Prevention, Бельгія</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr"/>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>CHLORAPREP FREPP 1,5 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 20, Серія № 3313882, 4020572, 4177103, 4264525, 3138975, 3227659, 3313884, 4169640, 4235732, 4295374, 5036189, 5037270, 5076598, 3138978, 4058927, 4085811, 4107060, 4138630, 4198196, 4198199, 4235722, 4264522, 4295373, 4330648, 5016735, 5037282, 5076588, 5114831, BD Infection Prevention, Бельгія</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr"/>
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>№ 306-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>CRISCY (SOMATROPINE), асептично оброблені парентеральні розчини малого об'єму, Серія № 22030133, з маркуванням виробника CRISTALIA PRODUTOS QUIMICOS FARMACEUTICOS LTDA, -</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr"/>
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H244"/>
+  <dimension ref="A1:H245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>№ 299-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>ГІДРОКОРТИЗОН, мазь 1 %; по  15 г у тубі; по 1 тубі в картонній пачці, Серія № 11257, ТОВ “Арпімед”, Республіка Вірменія</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5% по 25 г у тубах ламінатних, в пачці, Серія № 060924, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>ГІДРОКОРТИЗОН, мазь 1 %; по 10 г   у тубі; по 1 тубі в картонній пачці, Серія № 11255, ТОВ “Арпімед”, Республіка Вірменія</t>
+          <t>ГІДРОКОРТИЗОН, мазь 1 %; по  15 г у тубі; по 1 тубі в картонній пачці, Серія № 11257, ТОВ “Арпімед”, Республіка Вірменія</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>№ 300-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 299-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>ДІАГНОЛ®, порошок для орального розчину, 64 г/пакет по 73,69 г порошку у пакеті; по 4 пакети в пачці з картону, Серія № DMIR008780/2, АТ "Фармак", Україна</t>
+          <t>ГІДРОКОРТИЗОН, мазь 1 %; по 10 г   у тубі; по 1 тубі в картонній пачці, Серія № 11255, ТОВ “Арпімед”, Республіка Вірменія</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>№ 301-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 300-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>ОВЕСТИН®, крем вагінальний, 1 мг/г; по 15 г у тубі; по 1 тубі у комплекті з аплікатором в пачці, Серія № 24Е001, Аспен Бад-Ольдесло ГмбХ. (виробник відповідальний за виробництво, первинне та вторинне пакування, контроль якості та випуск серії), Німеччина</t>
+          <t>ДІАГНОЛ®, порошок для орального розчину, 64 г/пакет по 73,69 г порошку у пакеті; по 4 пакети в пачці з картону, Серія № DMIR008780/2, АТ "Фармак", Україна</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>№ 302-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 301-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>АСКОРІЛ, таблетки, по 10 таблеток у блістері; по 2 блістери в картонній упаковці, Серія № 10252263, Гленмарк Фармасьютикалз Лтд., Індія</t>
+          <t>ОВЕСТИН®, крем вагінальний, 1 мг/г; по 15 г у тубі; по 1 тубі у комплекті з аплікатором в пачці, Серія № 24Е001, Аспен Бад-Ольдесло ГмбХ. (виробник відповідальний за виробництво, первинне та вторинне пакування, контроль якості та випуск серії), Німеччина</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>№ 303-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 302-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>KEYTRUDA (pembrolizumab), 100mg/4mL, асептично оброблені парентеральні розчини малого об'єму, Серія № Y019149, з маркуванням виробника MERCK SHARP &amp; DOHME CORP., -</t>
+          <t>АСКОРІЛ, таблетки, по 10 таблеток у блістері; по 2 блістери в картонній упаковці, Серія № 10252263, Гленмарк Фармасьютикалз Лтд., Індія</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>№ 304-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 303-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>VECTIBIX 100 mg/5 mL (Panitumumab), флакон у картонній коробці, Серія № 2051100, 1166523, 1130818, 3377806, Amgen Manufacturing Limited, -</t>
+          <t>KEYTRUDA (pembrolizumab), 100mg/4mL, асептично оброблені парентеральні розчини малого об'єму, Серія № Y019149, з маркуванням виробника MERCK SHARP &amp; DOHME CORP., -</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 304-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>CLORAPREP 1 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 60, Серія № 3196393, 3325915, 3325918, 4021709, 4058230, 4058232, 4086014, 4086017, 4149178, 4155875, 4206632, 4210656, 4212800, 4233418, 4267729, 4270388, 4302021, 4302040, 4305711, 4324566, 4348098, 5026580, 5052205, 5081618, 5127264, 5133556, 5127263, 3261045, 3321422, 3346244, 4023071, 4058231, 4086024, 4151136, 4192080, 4212805, 4212806, 4233411, 4233411, 4270390, 4192033, 4212808, 4233414, 4267722, 4302029, 4325766, 4348096, 5026579, 5052200, 5133411, 3294918, 4206633, 4326463, BD Infection Prevention, Бельгія</t>
+          <t>VECTIBIX 100 mg/5 mL (Panitumumab), флакон у картонній коробці, Серія № 2051100, 1166523, 1130818, 3377806, Amgen Manufacturing Limited, -</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>CHLORAPREP FREPP 1,5 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 20, Серія № 3313882, 4020572, 4177103, 4264525, 3138975, 3227659, 3313884, 4169640, 4235732, 4295374, 5036189, 5037270, 5076598, 3138978, 4058927, 4085811, 4107060, 4138630, 4198196, 4198199, 4235722, 4264522, 4295373, 4330648, 5016735, 5037282, 5076588, 5114831, BD Infection Prevention, Бельгія</t>
+          <t>CLORAPREP 1 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 60, Серія № 3196393, 3325915, 3325918, 4021709, 4058230, 4058232, 4086014, 4086017, 4149178, 4155875, 4206632, 4210656, 4212800, 4233418, 4267729, 4270388, 4302021, 4302040, 4305711, 4324566, 4348098, 5026580, 5052205, 5081618, 5127264, 5133556, 5127263, 3261045, 3321422, 3346244, 4023071, 4058231, 4086024, 4151136, 4192080, 4212805, 4212806, 4233411, 4233411, 4270390, 4192033, 4212808, 4233414, 4267722, 4302029, 4325766, 4348096, 5026579, 5052200, 5133411, 3294918, 4206633, 4326463, BD Infection Prevention, Бельгія</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>№ 306-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>CRISCY (SOMATROPINE), асептично оброблені парентеральні розчини малого об'єму, Серія № 22030133, з маркуванням виробника CRISTALIA PRODUTOS QUIMICOS FARMACEUTICOS LTDA, -</t>
+          <t>CHLORAPREP FREPP 1,5 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 20, Серія № 3313882, 4020572, 4177103, 4264525, 3138975, 3227659, 3313884, 4169640, 4235732, 4295374, 5036189, 5037270, 5076598, 3138978, 4058927, 4085811, 4107060, 4138630, 4198196, 4198199, 4235722, 4264522, 4295373, 4330648, 5016735, 5037282, 5076588, 5114831, BD Infection Prevention, Бельгія</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -7306,6 +7306,34 @@
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr"/>
       <c r="H244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>№ 306-001.2/002.0/17-26 від 23.06.2026</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>CRISCY (SOMATROPINE), асептично оброблені парентеральні розчини малого об'єму, Серія № 22030133, з маркуванням виробника CRISTALIA PRODUTOS QUIMICOS FARMACEUTICOS LTDA, -</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H245"/>
+  <dimension ref="A1:H246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7335,6 +7335,34 @@
       <c r="G245" s="2" t="inlineStr"/>
       <c r="H245" s="2" t="inlineStr"/>
     </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>№ 308-001.2/002.0/17-26 від 24.06.2026</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>LEVOSIMENDAN FARMAK (Levosimendanum), концентрат для розчину для інфузій, 2,5 мг/мл, флакон 5 мл, Серія № 20825, Farmak International Sp. z o.o., Польща</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr"/>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H246"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7363,6 +7363,146 @@
       <c r="G246" s="2" t="inlineStr"/>
       <c r="H246" s="2" t="inlineStr"/>
     </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>№ 309-001.2/002.0/17-26 від 25.06.2026</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>25.06.2026</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>NILOTNIB 200 mg, капсули № 112, № 40, Серія № H0444A, H0444C, H0444E, H0444F, H0444G, H0444H, H0444AA (bulk KH0444), PHAROS MT LIMITED, -</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>№ 310-001.2/002.0/17-26 від 25.06.2026</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>25.06.2026</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>AZANESON (Azelastini hydrochloridum + Fluticasoni propionas), назальний спрей, суспензія, 1 флакон 120 доз, Серія № 251794, Basic Pharma Manufacturing B.V., Нідерланди</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr"/>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>№ 311-001.2/002.0/17-26 від 25.06.2026</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>25.06.2026</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>TEICOPLANIN APTAPHARMA 400 mg (Teicoplaninum), порошок та розчинник для приготування розчину для ін'єкцій/інфузій, 1 флакон містить 400 мг порошку та 1 ампулу 3,2 мл розчинника, Серія № E003B01K (outer packaging), E003B (vial with powder), E001K (ampoule with solvent), Sirton Pharmaceuticals S.p.A., Італiя</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr"/>
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>№ 312-001.2/002.0/17-26 від 25.06.2026</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>25.06.2026</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>TEICOPLANIN APTAPHARMA 200 mg (Teicoplaninum), порошок та розчинник для приготування розчину для ін'єкцій/інфузій, 1 флакон містить 200 мг порошку та 1 ампулу 3,2 мл розчинника, Серія № E001A01K (зовнішня упаковка), E001A (флакон з порошком), E001K (ампула з розчинником), Sirton Pharmaceuticals S.p.A., Італiя</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr"/>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>№ 313-001.2/002.0/17-26 від 25.06.2026</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>25.06.2026</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>BD CHLORAPREP™ 1 ml Applicator - Clear (2% w/v chlorhexidine gluconate (CHG) and 70% v/v isopropyl alcohol), аплікатор для стерильних розчинів, № 60, Серія № 3352268, 4049128, 4060484, 4072323, CareFusion 213 LLC, -</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr"/>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7503,6 +7503,34 @@
       <c r="G251" s="2" t="inlineStr"/>
       <c r="H251" s="2" t="inlineStr"/>
     </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>№ 314-001.2/002.0/17-26 від 26.06.2026</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>всі серії ЛЗ, виробництва Labormed Pharma SA, -, Серія № всі серії, Labormed Pharma SA, Румунія</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr"/>
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7531,6 +7531,90 @@
       <c r="G252" s="2" t="inlineStr"/>
       <c r="H252" s="2" t="inlineStr"/>
     </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>№ 316-001.2/002.0/17-26 від 26.06.2026</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>всі серії ЛЗ виробництва Sichuan New Hawk Biotechnology Co. Ltd., -, Серія № всі серії, Sichuan New Hawk Biotechnology Co. Ltd., Китай</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr"/>
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr"/>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>№ 317-001.2/002.0/17-26 від 26.06.2026</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>CIALIS 20 mg (Tadalafil), таблетки, вкриті плівковою оболонкою, по 20 мг; по 1 таблетці у блістері, по 1 блістеру в картонній коробці, по 2 таблетки у блістері, по 1, або по 2, або по 4 блістери в картонній коробці, Серія № D580306, з маркуванням виробника Lilly del Caribe Inc. Carolina, Puerto Rico, США/Іспанія</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr"/>
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>№ 318-001.2/002.0/17-26 від 26.06.2026</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>BOTOX COSMETIC FOR INJECTION 100 Units/vial, флакон у картонній коробці, Серія № C7048C4, з маркуванням виробника AbbVie Limited (раніше Allergan), -</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr"/>
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7615,6 +7615,34 @@
       <c r="G255" s="2" t="inlineStr"/>
       <c r="H255" s="2" t="inlineStr"/>
     </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>№ 319-001.2/002.0/17-26 від 03.07.2026</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>ЄВРОМІЦИН, гранули для орального розчину по 3 г; по 8 г препарату (3 г діючої речовини) у саше; по 1 або 2 саше у пачці з картону, Серія № 021124, Публічне акціонерне товариство "Хімфармзавод "Червона зірка", Україна</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr"/>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7643,6 +7643,90 @@
       <c r="G256" s="2" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr"/>
     </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>№ 320-001.2/002.0/17-26 від 03.07.2026</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>всі ЛЗ виробництва Geno Pharmaceuticals Private Limited, -, Серія № всі серії, Geno Pharmaceuticals Private Limited, Індія</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr"/>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>№ 321-001.2/002.0/17-26 від 03.07.2026</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>DIPROALT 20 mg (Omeprazole), капсули у флаконі № 120, Серія № OMEO1924, з маркуванням виробника Laboratorios Kener, S. A. de C.V., -</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr"/>
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>№ 322-001.2/002.0/17-26 від 03.07.2026</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>03.07.2026</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>BOTOX® (Botulinum Toxin Type A), розчин для ін’єкцій, флакон з ліофілізованим порошком у картонній коробці, Серія № D0044C3, C7746C3, C7936C3, з маркуванням виробника Allergan Pharmaceuticals, Ірландія</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr"/>
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7727,6 +7727,90 @@
       <c r="G259" s="2" t="inlineStr"/>
       <c r="H259" s="2" t="inlineStr"/>
     </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>№ 323-001.2/002.0/17-26 від 07.07.2026</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>DARZALEX (daratumumab) Injection 400 mg/20mL, флакон у картонній коробці, Серія № STV1K01, з маркуванням виробника JANSSEN, -</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr"/>
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>№ 323-001.2/002.0/17-26 від 07.07.2026</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>DARZALEX (daratumumab) Injection 100 mg/5 mL, флакон у картонній коробці, Серія № MYS7381, з маркуванням виробника JANSSEN, -</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr"/>
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>№ 324-001.2/002.0/17-26 від 07.07.2026</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>07.07.2026</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>ELENIUM 10 mg (Chlordiazepoxidum), таблетки, покриті оболонкою, № 20, Серія № 10424, Tarchominskie Zaklady Farmaceutyczne „Polfa”, Польща</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr"/>
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H262"/>
+  <dimension ref="A1:H265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7811,6 +7811,90 @@
       <c r="G262" s="2" t="inlineStr"/>
       <c r="H262" s="2" t="inlineStr"/>
     </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>№ 325-001.2/002.0/17-26 від 08.07.2026</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>РИПРОНАТ, розчин для ін`єкцій, 100 мг/мл; по 5 мл в ампулі; по 5 ампул в контурній чарунковій упаковці; по 2 контурні чарункові упаковки в картонній коробці, Серія № 2404611, К.О. Ромфарм Компані С.Р.Л., Румунiя</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr"/>
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>№ 326-001.2/002.0/17-26 від 08.07.2026</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>HALAVEN 0.44 mg/ml (Eribulin), розчин для ін'єкцій, флакон 2 мл, Серія № 148342 (bulk 148110), Eisai Manufacturing Limited, Велика Британія</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr"/>
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>№ 327-001.2/002.0/17-26 від 08.07.2026</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>SPIRIVA (TIOTROPIUM (TIOTROPIUM BROMIDE MONOHYDRATE)  18 MCG, 10 капсул з інгалятором, 30 капсул з інгалятором, 30 капсул, Серія № 405636, Boehringer Ingelheim Pharma GmbH &amp; Co. KG, Німеччина</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr"/>
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7895,6 +7895,62 @@
       <c r="G265" s="2" t="inlineStr"/>
       <c r="H265" s="2" t="inlineStr"/>
     </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>№ 328-001.2/002.0/17-26 від 10.07.2026</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT® 500 U (BOTULIN TOXIN), порошок для розчину для ін'єкцій, Серія № T01463, з маркуванням виробника IPSEN BIOPHARM LTD., -</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr"/>
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>№ 329-001.2/002.0/17-26 від 10.07.2026</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>ЦИТРАМОН В, таблетки; по 6 таблеток у блістерах по 10 блістерів у пачці з картону, Серія № 120126, ПАТ "Монфарм", Україна</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr"/>
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H267"/>
+  <dimension ref="A1:H269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7951,6 +7951,62 @@
       <c r="G267" s="2" t="inlineStr"/>
       <c r="H267" s="2" t="inlineStr"/>
     </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>№ 330-001.001/002.0/17-26 від 14.07.2026</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>ЛАЦЕРАН НСТ, таблетки по 5 мг/25 мг, по 7 таблеток у блістері, по 3 блістери у картонній коробці, Серія № PTG5357A, Сан Фармасьютикал Індастріз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr"/>
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>№ 331-001.001/002.0/17-26 від 14.07.2026</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>ФАРМАСЕПТИЛ, розчин для зовнішнього застосування 70 %, по 100 мл у флаконах, Серія № 011125, ТОВ "МЕДЛЕВ", Україна</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr"/>
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:H270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>№ 331-001.001/002.0/17-26 від 14.07.2026</t>
+          <t>№ 330-001.001/002.0/17-26 від 14.07.2026</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>ФАРМАСЕПТИЛ, розчин для зовнішнього застосування 70 %, по 100 мл у флаконах, Серія № 011125, ТОВ "МЕДЛЕВ", Україна</t>
+          <t>ЛАЦЕРАН НСТ, таблетки по 2,5 мг/12,5 мг, по 7 таблеток у блістері, по 3 блістери у картонній коробці, Серія № PTG4229B, Сан Фармасьютикал Індастріз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -8006,6 +8006,34 @@
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr"/>
       <c r="H269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>№ 331-001.001/002.0/17-26 від 14.07.2026</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>ФАРМАСЕПТИЛ, розчин для зовнішнього застосування 70 %, по 100 мл у флаконах, Серія № 011125, ТОВ "МЕДЛЕВ", Україна</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr"/>
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H270"/>
+  <dimension ref="A1:H275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8035,6 +8035,146 @@
       <c r="G270" s="2" t="inlineStr"/>
       <c r="H270" s="2" t="inlineStr"/>
     </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>№ 332-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>БОРНОЇ КИСЛОТИ РОЗЧИН СПИРТОВИЙ 3 %, розчин для зовнішнього застосування, спиртовий 3 % по 20 мл у флаконі, Серія № 071125, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr"/>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>№ 333-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>ЛАМІКТАЛ, таблетки,що диспергуються,по100мг; по14таблеток у блістері з полівінілхлориду/полівінілденхлориду/паперу/алюмінієвої фольги із захистом від відкривання дітьми; по 2 блістери в картонній коробці, Серія № FKRM, Делфарм Познань С.А., Польща</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr"/>
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>№ 333-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>ЛАМІКТАЛ, таблетки, що диспергуються, по 50 мг; по 14 таблеток у блістері з полівінілхлориду/полівінілденхлориду/паперу/алюмінієвої фольги із захистом від відкривання дітьми; по 2 блістери в картонній коробці, Серія № FTKG, Делфарм Познань С.А., Польща</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr"/>
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>№ 334-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>TESTOSTERONE PROPIONATE 100 mg/ml, 10 ampoules/1ml, Серія № 392407, Androlex Pharma AG, Bardejov, Словенія</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr"/>
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>№ 334-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>TRENBOLONE ENANTHATE, 200MG/ML, ампули по 1 мл, № 10 у коробці, Серія № всі серії, Androlex Pharma AG, Bardejov, Androlex Pharma AG, Bardejov, Словакія</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H275"/>
+  <dimension ref="A1:H280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8175,6 +8175,146 @@
       <c r="G275" s="2" t="inlineStr"/>
       <c r="H275" s="2" t="inlineStr"/>
     </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>№ 334-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>TURINABOL 10 MG/TABLET, таблетки № 100 у коробці, Серія № 392407, Androlex Pharma AG, Bardejov, Словакія</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr"/>
+      <c r="G276" s="2" t="inlineStr"/>
+      <c r="H276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>№ 334-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>TESTOSTERONE ENANTHATE 250 MG/ML, флакон 10 мл у картонній коробці, Серія № 300723, Androlex Pharma AG, Bardejov, Словакія</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr"/>
+      <c r="H277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>№ 334-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>TRENBOLONE ACETATE 100 MG/ML, ампули по 1 мл № 10 у коробці, Серія № 317454, Androlex Pharma AG, Bardejov, Словакія</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr"/>
+      <c r="G278" s="2" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>№ 334-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>LETROZOLE 25, таблетки, № 30 у коробці, Серія № 115118, Hilma Bicare, Індія</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr"/>
+      <c r="G279" s="2" t="inlineStr"/>
+      <c r="H279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>№ 334-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>VIAGRON 100, таблетки, вкриті плівковою оболонкою, № 10 у коробці, Серія № 861247, Hilma Bicare, Індія</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr"/>
+      <c r="G280" s="2" t="inlineStr"/>
+      <c r="H280" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8315,6 +8315,34 @@
       <c r="G280" s="2" t="inlineStr"/>
       <c r="H280" s="2" t="inlineStr"/>
     </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>№ 334-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>TESTOSTERONE PROPIONATE 100 mg/ml, 10 ampoules/1ml, Серія № 392407, Androlex Pharma AG, Bardejov, Словакія</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr"/>
+      <c r="G281" s="2" t="inlineStr"/>
+      <c r="H281" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H281"/>
+  <dimension ref="A1:H282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8343,6 +8343,34 @@
       <c r="G281" s="2" t="inlineStr"/>
       <c r="H281" s="2" t="inlineStr"/>
     </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>№ 334-001.001/002.0/17-26 від 20.07.2026</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>TADALAFIL 10 MG/TABLET, таблетки, № 20   у картонній коробці, Серія № 861247, Androlex Pharma AG, Bardejov, Словакія</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr"/>
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8371,6 +8371,258 @@
       <c r="G282" s="2" t="inlineStr"/>
       <c r="H282" s="2" t="inlineStr"/>
     </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>ДЕНІЦЕФ, порошок для розчину для ін'єкцій по 1 г, 1 флакон з порошком в коробці з картону, Серія № всі серії, Ананта Медікеар Лімітед, Індія, Індія</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr"/>
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr"/>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>ОПЕРОНІКС, порошок для розчину для ін’єкцій або інфузій по 2 г; 1 флакон з порошком у коробці з картону, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>ЕФМЕРИН, порошок для розчину для ін’єкцій по 1 г, 1 флакон з порошком в коробці, Серія № всі серії, "Венус Ремедіс Лімітед", Індія; Ананта Медікеар Лімітед, Індія, Індія</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>ЕФМЕРИН, порошок для розчину для ін’єкцій по 2 г, 1 флакон з порошком в коробці, Серія № всі серії, "Венус Ремедіс Лімітед", Індія; Ананта Медікеар Лімітед, Індія, Індія</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>ФЛОРАЗІД, порошок для розчину для ін`єкцій по 1 г, 1 флакон з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія, Індія</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr"/>
+      <c r="G287" s="2" t="inlineStr"/>
+      <c r="H287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>ФОРЦЕФТРИН, порошок для розчину для ін'єкцій по 750 мг у флаконі, по 1 флакону з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>ЦЕФЕПІМ, порошок для розчину для ін`єкцій по 1000 мг; 1 флакон з порошком у коробці з картону, Серія № всі серії, Свісс Перентералс Лтд., Індія Ананта Медікеар Лімітед, Індія, Індія</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr"/>
+      <c r="G289" s="2" t="inlineStr"/>
+      <c r="H289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>ЦЕФОПЕРАЗОН АНАНТА, порошок для розчину для ін`єкцій по 1 г, 1 флакон з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr"/>
+      <c r="G290" s="2" t="inlineStr"/>
+      <c r="H290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>ЦЕФОТАКСИМ АНАНТА, порошок для розчину для ін`єкцій по 1 г, 1 флакон з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr"/>
+      <c r="G291" s="2" t="inlineStr"/>
+      <c r="H291" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8623,6 +8623,174 @@
       <c r="G291" s="2" t="inlineStr"/>
       <c r="H291" s="2" t="inlineStr"/>
     </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>ДЕНІЗИД, порошок для розчину для ін’єкцій по 1 г, 1 флакон з порошком у коробці з картону, Серія № всі серії, Ананта Медікеар Лімітед, Індія, Індія</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr"/>
+      <c r="G292" s="2" t="inlineStr"/>
+      <c r="H292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>ДЕНІПІМ, порошок для розчину для ін'єкцій по 1000 мг, 1 флакон з порошком у коробці з картону, Серія № всі серії, Ананта Медікеар Лімітед, Індія, Індія</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr"/>
+      <c r="H293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>ЦЕФТАЗИДИМ АНАНТА, порошок для розчину для ін`єкцій по 1 г, 1 флакон з порошком у коробці з картону, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr"/>
+      <c r="G294" s="2" t="inlineStr"/>
+      <c r="H294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>ЦЕФТРИАКСОН АНАНТА, порошок для розчину для ін'єкцій по 1 г: 1 флакон з порошком в коробці (для виробника Свісс Перентералс Лтд., Індія), 1 флакон з порошком в коробці, 20 флаконів з порошком в коробці (для виробника Ананта Медікеар Лімітед, Індія), Серія № всі серії, Свісс Перентералс Лтд., Індія Ананта Медікеар Лімітед, Індія, Індія</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr"/>
+      <c r="G295" s="2" t="inlineStr"/>
+      <c r="H295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>ЦЕФТРИАКСОН АНАНТА, порошок для розчину для ін'єкцій по 2 г; 1 флакон з порошком в коробці, 10 флаконів з порошком в коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr"/>
+      <c r="G296" s="2" t="inlineStr"/>
+      <c r="H296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>ЦЕФОТРИН, порошок для розчину для ін’єкцій по 1 г, 1 флакон з порошком в картонній коробці, Серія № 33260502, 33260503, 33260504, 33260302, 33260203, 33260301, 33260501, 33260202, 33250902, 33250901, 33241101, 33241203, 33241201, 33241202, 33241102, 33241103, 33240801, 33240802, 33240601, 33240602, 3322113, Ананта Медікеар Лімітед, Індія, Індія</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr"/>
+      <c r="G297" s="2" t="inlineStr"/>
+      <c r="H297" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8791,6 +8791,34 @@
       <c r="G297" s="2" t="inlineStr"/>
       <c r="H297" s="2" t="inlineStr"/>
     </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>№ 336-001.001/002.0/17-26 від 24.07.2026</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>ПАКЛІТАКСЕЛ АМАКСА, концентрат для розчину для інфузій, 6 мг/мл; по 5 мл, 16,7 мл або 50 мл у флаконі; по 1 флакону в картонній коробці, Серія № AO261002, контроль та випуск серії: АкВіда ГмбХ, Німеччина виробництво in bulk, первинне та вторинне пакування: Самянг Холдінгз Корпорейшн, Республiка Корея виробництво in bulk, первинне пакування, вторинне пакування, контроль серії: АкВіда ГмбХ, Німеччина, Німеччина/ Республiка Корея</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr"/>
+      <c r="G298" s="2" t="inlineStr"/>
+      <c r="H298" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -7201,7 +7201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8396,17 +8396,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>№ 336-001.001/002.0/17-26 від 24.07.2026</t>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>ПАКЛІТАКСЕЛ АМАКСА, концентрат для розчину для інфузій, 6 мг/мл; по 5 мл, 16,7 мл або 50 мл у флаконі; по 1 флакону в картонній коробці, Серія № AO261002, контроль та випуск серії: АкВіда ГмбХ, Німеччина виробництво in bulk, первинне та вторинне пакування: Самянг Холдінгз Корпорейшн, Республiка Корея виробництво in bulk, первинне пакування, вторинне пакування, контроль серії: АкВіда ГмбХ, Німеччина, Німеччина/ Республiка Корея</t>
+          <t>ЦЕФЕПІМ АНАНТА, порошок для розчину для ін'єкцій по 2 г; 1 або 10 флаконів з порошком в коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8417,6 +8417,342 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>22.07.2026</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>ЦЕФЕПІМ АНАНТА, порошок для розчину для ін'єкцій по 1 г; 1 або 10 флаконів з порошком в коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>№ 336-001.001/002.0/17-26 від 24.07.2026</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>ПАКЛІТАКСЕЛ АМАКСА, концентрат для розчину для інфузій, 6 мг/мл; по 5 мл, 16,7 мл або 50 мл у флаконі; по 1 флакону в картонній коробці, Серія № AO261002, контроль та випуск серії: АкВіда ГмбХ, Німеччина виробництво in bulk, первинне та вторинне пакування: Самянг Холдінгз Корпорейшн, Республiка Корея виробництво in bulk, первинне пакування, вторинне пакування, контроль серії: АкВіда ГмбХ, Німеччина, Німеччина/ Республiка Корея</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>№ 337-001.001/002.0/17-26 від 27.07.2026</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>ЛОПЕРАМІД, таблетки по 2 мг по 10 таблеток у блістері; по 2 блістери в пачці, Серія № 011188, ТОВ "МАРІФАРМ", Словенія</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011523, ТОВ «МАРІФАРМ», Словенія</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011520, ТОВ «МАРІФАРМ», Словенія</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011502, ТОВ «МАРІФАРМ», Словенія</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній в пачці, Серія № 010124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>27.07.2026</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 090824, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>№ 343-001.001/002.0/17-26 від 28.07.2026</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Австрія</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>№ 344-001.001/002.0/17-26 від 28.07.2026</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>VALAMOR (ribociclib) 200 mg, таблетки № 63, Серія № A0213K, Novartis Sagl?k, G?da ve Tar?m Urunleri San. ve Tic. A.S., -</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>ФІБРИНАЗА-20, таблетки, вкриті оболонкою, кишковорозчинні по 20 мг; по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № EBK25010B1, EBK25011B1, EBK25012B1, EBK26004B1, EBK26005B1, EBK26007B1, Евертоджен Лайф Саєнсиз  Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>ФІБРИНАЗА-10, таблетки, вкриті оболонкою, кишковорозчинні по 10 мг, по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № ESI25011B1, ESI25012B1, ESI26002B1, ESI26003B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -7201,7 +7201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8452,17 +8452,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>№ 336-001.001/002.0/17-26 від 24.07.2026</t>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>ПАКЛІТАКСЕЛ АМАКСА, концентрат для розчину для інфузій, 6 мг/мл; по 5 мл, 16,7 мл або 50 мл у флаконі; по 1 флакону в картонній коробці, Серія № AO261002, контроль та випуск серії: АкВіда ГмбХ, Німеччина виробництво in bulk, первинне та вторинне пакування: Самянг Холдінгз Корпорейшн, Республiка Корея виробництво in bulk, первинне пакування, вторинне пакування, контроль серії: АкВіда ГмбХ, Німеччина, Німеччина/ Республiка Корея</t>
+          <t>ФЛОРАЗІД, порошок для розчину для ін`єкцій по 2 г, 1 флакон з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія, Індія</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -8480,17 +8480,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>№ 337-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>ЛОПЕРАМІД, таблетки по 2 мг по 10 таблеток у блістері; по 2 блістери в пачці, Серія № 011188, ТОВ "МАРІФАРМ", Словенія</t>
+          <t>ФОРЦЕФТРИН, порошок для розчину для ін'єкцій по 1,5 г у флаконі, по 1 флакону з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -8508,17 +8508,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 336-001.001/002.0/17-26 від 24.07.2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011523, ТОВ «МАРІФАРМ», Словенія</t>
+          <t>ПАКЛІТАКСЕЛ АМАКСА, концентрат для розчину для інфузій, 6 мг/мл; по 5 мл, 16,7 мл або 50 мл у флаконі; по 1 флакону в картонній коробці, Серія № AO261002, контроль та випуск серії: АкВіда ГмбХ, Німеччина виробництво in bulk, первинне та вторинне пакування: Самянг Холдінгз Корпорейшн, Республiка Корея виробництво in bulk, первинне пакування, вторинне пакування, контроль серії: АкВіда ГмбХ, Німеччина, Німеччина/ Республiка Корея</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 337-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011520, ТОВ «МАРІФАРМ», Словенія</t>
+          <t>ЛОПЕРАМІД, таблетки по 2 мг по 10 таблеток у блістері; по 2 блістери в пачці, Серія № 011188, ТОВ "МАРІФАРМ", Словенія</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 338-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011502, ТОВ «МАРІФАРМ», Словенія</t>
+          <t>ГРИПОМЕД®, капсули, по 10 капсул у блістері; по 2 блістери у пачці з картону, Серія № 070925, ПАТ "Хімфармзавод "Червона зірка", Україна</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній в пачці, Серія № 010124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011523, ТОВ «МАРІФАРМ», Словенія</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 090824, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011520, ТОВ «МАРІФАРМ», Словенія</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>№ 343-001.001/002.0/17-26 від 28.07.2026</t>
+          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Австрія</t>
+          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011502, ТОВ «МАРІФАРМ», Словенія</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -8676,17 +8676,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>№ 344-001.001/002.0/17-26 від 28.07.2026</t>
+          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>VALAMOR (ribociclib) 200 mg, таблетки № 63, Серія № A0213K, Novartis Sagl?k, G?da ve Tar?m Urunleri San. ve Tic. A.S., -</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній в пачці, Серія № 010124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -8704,17 +8704,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
+          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>ФІБРИНАЗА-20, таблетки, вкриті оболонкою, кишковорозчинні по 20 мг; по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № EBK25010B1, EBK25011B1, EBK25012B1, EBK26004B1, EBK26005B1, EBK26007B1, Евертоджен Лайф Саєнсиз  Лімітед, Індія</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 090824, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -8732,17 +8732,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
+          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>ФІБРИНАЗА-10, таблетки, вкриті оболонкою, кишковорозчинні по 10 мг, по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № ESI25011B1, ESI25012B1, ESI26002B1, ESI26003B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 111023, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8753,6 +8753,202 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>№ 343-001.001/002.0/17-26 від 28.07.2026</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Австрія</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>№ 344-001.001/002.0/17-26 від 28.07.2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>VALAMOR (ribociclib) 200 mg, таблетки № 63, Серія № A0213K, Novartis Sagl?k, G?da ve Tar?m Urunleri San. ve Tic. A.S., -</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>ФІБРИНАЗА-20, таблетки, вкриті оболонкою, кишковорозчинні по 20 мг; по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № EBK25010B1, EBK25011B1, EBK25012B1, EBK26004B1, EBK26005B1, EBK26007B1, Евертоджен Лайф Саєнсиз  Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>28.07.2026</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>ФІБРИНАЗА-10, таблетки, вкриті оболонкою, кишковорозчинні по 10 мг, по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № ESI25011B1, ESI25012B1, ESI26002B1, ESI26003B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>№ 346-001.001/002.0/17-26 від 29.07.2026</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>ЦИТРАМОН В, таблетки;  по  10 таблеток у блістерах, Серія № 61025, ПАТ "Монфарм", Україна</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>№ 348-001.001/002.0/17-26 від 29.07.2026</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/100 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00609BA, СЕПТОДОНТ, Франція</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>№ 348-001.001/002.0/17-26 від 29.07.2026</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/200 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00611AC, СЕПТОДОНТ, Франція</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -7201,7 +7201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8950,6 +8950,34 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
     </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>№ 349-001.001/002.0/17-26 від 30.07.2026</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/100 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00609BA, СЕПТОДОНТ, Франція</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -7201,7 +7201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8978,6 +8978,62 @@
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
     </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>№ 351-001.001/002.0/17-26 від 31.07.2026</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>№ 353-001.001/002.0/17-26 від 31.07.2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>31.07.2026</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>всі серії ЛЗ виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Травень 2026" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Червень 2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Липень 2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Серпень 2026" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9037,4 +9038,140 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№ з/п</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Дата і номер розпорядження/ рішення/припису</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Дата одержання розпорядження/ рішення/припису</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Назва лікарських засобів та перелік серій лікарських засобів, зазначених у розпорядженні/ рішенні/приписі</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Результати перевірки щодо наявності зазначених лікарських засобів</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Вжиті заходи у разі виявлення зазначених лікарських засобів</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Дата і номер листа-повідомлення територіальному органу</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Підпис уповноваженої особи</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>№ 354-001.001/002.0/17-26 від 04.08.2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>МЕФЕНАМІНОВА КИСЛОТА, таблетки по 500 мг по 10 таблеток у блістері, по 2 блістери в пачці, Серія № 151224, ТОВ "Фармацевтична компанія "ФарКоС", Україна</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -9046,7 +9046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9171,6 +9171,62 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
     </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>№ 355-001.001/002.0/17-26 від 04.08.2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>АТРАКУРІУМ-ДАРНИЦЯ, розчин для ін'єкцій, 10 мг/мл, по 5 мл в ампулі; по 5 ампул у контурній чарунковій упаковці; по 1 контурній чарунковій упаковці в пачці, Серія № UP10825, UP21125, UP10626, UP20625, ПрАТ "Фармацевтична фірма "Дарниця", Україна</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>№ 356-001.001/002.0/17-26 від 04.08.2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>КЛОПІДОГРЕЛЬ, таблетки, вкриті оболонкою, по 75 мг по 10 таблеток у блістері: по 3 блістери в коробці з картону, Серія № 1110126, всі стадії виробництва, контроль якості, випуск серії: Товариство з обмеженою відповідальністю" ФАРМЕКС ГРУП", Україна, Україна</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -9046,7 +9046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9227,6 +9227,258 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
     </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>№ 357-001.001/002.0/17-26 від 06.08.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ORAMIN-F SOFT CAP, М'які желатинові капсули, 30 капсул у коробці., Серія № 6AAA, Daewon Healthcare Ltd, Республіка Корея</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>№ 358-001.001/002.0/17-26 від 06.08.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>всі серії ЛЗ ENTECAVIR MONOHYDRATE (Intermediate) , виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>№ 358-001.001/002.0/17-26 від 06.08.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>всі серії ЛЗ CISATRACURIUM BESILATE, виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>№ 359-001.001/002.0/17-26 від 06.08.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ОМНІТРОП®/Omnitrope® (Somatropin 5 mg/1.5mL), розчин для ін'єкцій, у картриджі; по 1 або 5 картриджів у картонній коробці, Серія № PR7350, PR7351, Novartis Pharmaceutical Manufacturing GmbH, Австрія</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>№ 360-001.001/002.0/17-26 від 06.08.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>TABCIN NOCHE (paracetamol/ dextromethorphan hydrobromide /Doxylamine succinate/ Phenylephrine hydrochloride) 325.00 mg/10.00 mg/6.25 mg/5.00 mg, КАПСУЛИ № 12, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>№ 360-001.001/002.0/17-26 від 06.08.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>TABCIN ACTIVE® (paracetamol/ dextromethorphan hydrobromide /Doxylamine succinate/Phenylephrine hydrochloride), капсули № 12, Серія № M230717B (блістер), X25RXG (коробка), з маркуванням виробника Berlimed, S.A., Іспанія</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>№ 360-001.001/002.0/17-26 від 06.08.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>FLANAX® (Naproxen) 550 mg, таблетки № 30, Серія № X2557P, X25CFZ, з маркуванням виробника Bayer Bitterfeld Gmb, Німеччина</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>№ 360-001.001/002.0/17-26 від 06.08.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>DESENFRIOL D® (Chlorphenamine/Phenylephrine/Paracetamol) 2 mg/5 mg/500 mg, таблетки  № 30, Серія № X24EKH, з маркуванням виробника Bayer de Mexico, S.A. de C.V., Мексика</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>№ 360-001.001/002.0/17-26 від 06.08.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>06.08.2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>ALKA SELTZER® (Acetylsalicylic acid/Sodium bicarbonate/Citric acid) 0,324 g/1,976 g/1,000 g, таблетки № 100, Серія № X25GUE, з маркуванням виробника Bayer de Mexico, S.A. de C.V., Мексика</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -9046,7 +9046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9479,6 +9479,34 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
     </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>№ 361-001.001/002.0/17-26 від 07.08.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>07.08.2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>КЕТОСТЕРИЛ, таблетки, вкриті плівковою оболонкою; по 20 таблеток у блістері; по 5 блістерів у запаяному пакеті з алюмінієвої фольги; по 1 пакету в картонній коробці, Серія № 18B1337, Лабесфаль Лабораторіос Алміро, С.А., Португалія</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -9046,7 +9046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9507,6 +9507,370 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
     </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>№ 363-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>SPIRIVA (TIOTROPIUM) 18 MCG, 10 капсул у блістері, Серія № 404993, BOEHRINGER INGELHEIM PHARMA GMBH &amp; CO., Німеччина</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>№ 364-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>RISPERIDONE TEVA (Risperidonum) 37,5 mg, 1 флакон порошку + 1 шприц + 2 голки + 1 адаптер, 2 флакони порошку + 2 шприци + 4 голки + 2 адаптери, 5 флаконів порошку + 5 шприців + 10 голок + 5 адаптерів, Серія № всі серії, Pharmathen International S.A, Греція</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>№ 364-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>RISPERIDONE TEVA (Risperidonum) 25 mg, 1 флакон порошку + 1 шприц + 2 голки + 1 адаптер, 2 флакони порошку + 2 шприци + 4 голки + 2 адаптери, 5 флаконів порошку + 5 шприців + 10 голок + 5 адаптерів, Серія № всі серії, Pharmathen International S.A Industrial Park Sapes, Rodopi Prefecture, Греція</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>№ 364-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>RISPERIDONE TEVA RISPERIDONE TEVA (Risperidonum) 50 mg, порошок та розчинник для пролонгованої суспензії для ін'єкцій, 1 флакон порошку + 1 шприц + 2 голки + 1 адаптер, 2 флакони порошку + 2 шприци + 4 голки + 2 адаптери, 5 флаконів порошку + 5 шприців + 10 голок + 5 адаптерів, Серія № всі серії, Pharmathen International S.A Industrial Park Sapes, Rodopi Prefecture, Греція</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>№ 365-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>CHLORAPREP INCOLORO 20 mg/ml + 0,70 ml/ml, шкірний розчин, 60 аплікаторів по 1 мл, Серія № 5344684, BD INFECTION PREVENTION - Erembodegen-Dorp 86, Erembodegem, 9320, Бельгія</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>№ 366-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>ADRENALINE INJECTION (EPINEPHRINE BITARTRATE), розчин для ін'єкцій, 1 мл в ампулі, Серія № IA02C01, LAMTHONG KARNPAT PHARMACEUTICAL FACTORY CO. LTD., -</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>№ 367-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>NITROFURANTION PHARMEVID (Nitrofurantoin) 100 mg, тверді капсули № 30, Серія № 8250243, 8250235, Iasis Pharmaceuticals Hellas S.A., Греція</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>№ 368-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>REMETHAN 100 R (Diclofenac Sodium 100mg), таблетки, Серія № 104024, REMEDICA LTD, Кіпр</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>№ 369-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>TEICOPLANIN PHARMLINE (Teicoplaninum) 400 mg, порошок та розчинник для розчину для ін'єкцій/інфузій або розчину для перорального застосування, Серія № серії 2602581 (флакон з порошком та вторинна упаковка) та серії 2513798 (розчинник), S.C. Rompharm Company S.R.L., Румунія</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>№ 369-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>TEICOPLANIN PHARMLINE (Teicoplaninum), порошок та розчинник для розчину для ін'єкцій/інфузій або розчину для перорального застосування, Серія № 2513534 (на вторинній упаковці та первинній упаковці - флакон з порошком)/ 2513797 (на первинній упаковці - розчинник, S.C. Rompharm Company S.R.L., Румунія</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>№ 370-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>ADNAMIL (Allopurinolum), таблетки  № 30, Серія № HIY0325001, Polfarmex S.A., Польща</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>№ 371-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>CEVITIL (ASCORBIC ACID) 1 g, шипучі таблетки  у флаконі, Серія № 2509984, EPICO, Єгипет</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>№ 372-001.001/002.0/17-26 від 11.08.2026</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>11.08.2026</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ATORVASTATIN MEDICAL VALLEY (Atorvastatinum) 40 mg, таблетки, 30 таблеток, вкритих плівковою оболонкою, у блістері, Серія № всі серії, Laboratorios Liconsa, S.A, Гвадалахара</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -3486,7 +3486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>№ 244-001.2/002.0/17-26 від 14.05.2026</t>
+          <t>№ 245-001.2/002.0/17-26 від 14.05.2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>НІМЕЛГАН, гранули для оральної суспензії, по 100 мг; по 30 саше у коробці з картону, Серія № 070324, ТОВ "АСТРАФАРМ", Україна</t>
+          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -4121,17 +4121,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>№ 245-001.2/002.0/17-26 від 14.05.2026</t>
+          <t>№ 246-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>14.05.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
+          <t>Baclofen-neuraxpharm®, 25mg, Tabletten, 100 Tabletten, Серія № 230012, NEURAXPHARM Arzneimittel GmbH Elisabeth-Selbert-Str. 23 40764, Langenfeld</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>№ 246-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 247-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Baclofen-neuraxpharm®, 25mg, Tabletten, 100 Tabletten, Серія № 230012, NEURAXPHARM Arzneimittel GmbH Elisabeth-Selbert-Str. 23 40764, Langenfeld</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 42726A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 42726A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 20914A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 20914A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 13850A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>№ 247-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 248-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 13850A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+          <t>Naratriptan – 1A Pharma®, bei Migrane 2,5 mg Filmtabletten, 2 Filmtabletten № 1, Серія № PT5595, Lek S.A. Ul. Podlipie 16 Strykow 95-010, Polen</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>№ 248-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 249-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Naratriptan – 1A Pharma®, bei Migrane 2,5 mg Filmtabletten, 2 Filmtabletten № 1, Серія № PT5595, Lek S.A. Ul. Podlipie 16 Strykow 95-010, Polen</t>
+          <t>Duloxetin Glenmark, 30 mg magensaftresistente Hartkapseln, 28 magensaftresistente Hartkapseln, Серія № 40784, Towa Pharmaceutical Europe, S.L. C/ de Sant Marti, 75-97 Martorelles, 08107 Barcelona, Spanien</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>№ 249-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Duloxetin Glenmark, 30 mg magensaftresistente Hartkapseln, 28 magensaftresistente Hartkapseln, Серія № 40784, Towa Pharmaceutical Europe, S.L. C/ de Sant Marti, 75-97 Martorelles, 08107 Barcelona, Spanien</t>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 60 Film Kapli Tablet, Серія № 25371012, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 60 Film Kapli Tablet, Серія № 25371012, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 3 Film Kapli Tablet, Серія № 25371015, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 3 Film Kapli Tablet, Серія № 25371015, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>ANDAZOL®, 200mg/10ml Suspansiyon, % 2 suspansiyon 60 ml, Серія № 25020011, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 200mg/10ml Suspansiyon, % 2 suspansiyon 60 ml, Серія № 25020011, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>NUROFEN® JUNIOR, ERDBEER, 40 mg/ml SUSPENSION ZUM EINNEHMEN 100ml, Серія № AHC903, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® JUNIOR, ERDBEER, 40 mg/ml SUSPENSION ZUM EINNEHMEN 100ml, Серія № AHC903, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® IMMEDIA, 400 mg Filmtabletten, 12 Filmtabletten, Серія № TE404, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® IMMEDIA, 400 mg Filmtabletten, 12 Filmtabletten, Серія № TE404, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN®, 400MG WEICHKAPSELN, 20 Weichkapseln, Серія № TY059, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN®, 400MG WEICHKAPSELN, 20 Weichkapseln, Серія № TY059, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® Immedia, 200 mg, 10 Weichkapseln, Серія № TK473, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® Immedia, 200 mg, 10 Weichkapseln, Серія № TK473, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® JUNIOR, ORANGE, 40 mg/ml SUSPENSION ZUM EINNEHMEN, 100ml, Серія № AHB068, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® JUNIOR, ORANGE, 40 mg/ml SUSPENSION ZUM EINNEHMEN, 100ml, Серія № AHB068, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>TYLOL®HOT DAY, 12 poset, Серія № 270630, NOBEL ILAC SANAYII VE TICARET A.S. Sancaklar 81100, DUZCE</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>TYLOL®HOT DAY, 12 poset, Серія № 270630, NOBEL ILAC SANAYII VE TICARET A.S. Sancaklar 81100, DUZCE</t>
+          <t>Tadalafil beta, 5 mg 84 Filmtabletten, Серія № 2405018050, betapharm Arzneimittel GmbH Kobelweg 95, 86156, Augsburg</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Tadalafil beta, 5 mg 84 Filmtabletten, Серія № 2405018050, betapharm Arzneimittel GmbH Kobelweg 95, 86156, Augsburg</t>
+          <t>Soldesam, 0,2% gocce orali, soluzione Flacone da 10 ml, Серія № 260128, laboratorio farmacologico milanese s.r.l. via monterosso, 273 21042, caronno pertusella (va)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Soldesam, 0,2% gocce orali, soluzione Flacone da 10 ml, Серія № 260128, laboratorio farmacologico milanese s.r.l. via monterosso, 273 21042, caronno pertusella (va)</t>
+          <t>Tolperison-HCI dura®, 50 mg Filmtabletten, 96 Filmtabletten, Серія № TN47017H, Mylan Germany GmbH Lutticher Stra?e 5 53842, Troisdorf</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Tolperison-HCI dura®, 50 mg Filmtabletten, 96 Filmtabletten, Серія № TN47017H, Mylan Germany GmbH Lutticher Stra?e 5 53842, Troisdorf</t>
+          <t>Escitalopram A?Z, 20 mg Filmtabletten, 100 Filmtabletten, Серія № 16515423, Merckle GmbH Ludwig-Merckle-Str. 3 89143, Blaubeuren</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Escitalopram A?Z, 20 mg Filmtabletten, 100 Filmtabletten, Серія № 16515423, Merckle GmbH Ludwig-Merckle-Str. 3 89143, Blaubeuren</t>
+          <t>Ezetimib Arasto, 10 mg Tabletten, 50 Tabletten, Серія № 26046T5, Laboratorios Medicamentos Internacionales S.A. Calle Solana 26 28850 Torrejon de Ardoz (Madrid), Spanien</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Ezetimib Arasto, 10 mg Tabletten, 50 Tabletten, Серія № 26046T5, Laboratorios Medicamentos Internacionales S.A. Calle Solana 26 28850 Torrejon de Ardoz (Madrid), Spanien</t>
+          <t>Sab simplex®, 69,19 mg/ml Suspension zum Einnehmen Simeticon, 30 ml, Серія № 01261, Delpharm Orleans 5, avenue de Concyr 45071 Orleans Cedex 2, Frankreich</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Sab simplex®, 69,19 mg/ml Suspension zum Einnehmen Simeticon, 30 ml, Серія № 01261, Delpharm Orleans 5, avenue de Concyr 45071 Orleans Cedex 2, Frankreich</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953167, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953167, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D937842, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D937842, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953182, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953182, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Mounjaro® KwikPen®, 10 mg/Dosis, Injektionslosung in einem Fertigpen 3 Pens (jeder Pen gibt 4 Dosen ad), Серія № D871349D, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/Dosis, Injektionslosung in einem Fertigpen 3 Pens (jeder Pen gibt 4 Dosen ad), Серія № D871349D, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Espumisan®, Emulsion 40 mg/ml, 32 ml Emulsion zum Einnehmen, Серія № 51001A, BERLIN-CHEMIE AG Glienicker Weg 125, 12489 Berlin, Deutschland</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Espumisan®, Emulsion 40 mg/ml, 32 ml Emulsion zum Einnehmen, Серія № 51001A, BERLIN-CHEMIE AG Glienicker Weg 125, 12489 Berlin, Deutschland</t>
+          <t>Ben-u-ron® Saft, 40 mg/ml Sirup, 100 ml Sirup Zum Einnehmen, Серія № 306L241, Medinfar Manufacturing S.A. Parque Industrial Armando Martins Tavares Rua Outeiro da Armada No 5 Condeixa-а-Nova 3150-194 Sebal, Portugal</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Ben-u-ron® Saft, 40 mg/ml Sirup, 100 ml Sirup Zum Einnehmen, Серія № 306L241, Medinfar Manufacturing S.A. Parque Industrial Armando Martins Tavares Rua Outeiro da Armada No 5 Condeixa-а-Nova 3150-194 Sebal, Portugal</t>
+          <t>Lymphomyosot®N, 100 ml Mischung, Серія № 09982, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 100 ml Mischung, Серія № 09982, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Femoston® conti, 1mg/5mg Filmtabletten, 84 (3x28) Filmtabletten Zum Einnehmen, Серія № 375648, Abbott Biologicals B.V. C.J. van Houtenlaan 36 1381 CP Weesp, Niederlande</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Femoston® conti, 1mg/5mg Filmtabletten, 84 (3x28) Filmtabletten Zum Einnehmen, Серія № 375648, Abbott Biologicals B.V. C.J. van Houtenlaan 36 1381 CP Weesp, Niederlande</t>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 08900, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 08900, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 10944, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 10944, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5V443, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5V443, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T599, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5073,17 +5073,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 258-001.2/002.0/17-26 від 18.05.2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>18.05.2026</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T599, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5101,17 +5101,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>№ 258-001.2/002.0/17-26 від 18.05.2026</t>
+          <t>№ 259-001.2/002.0/17-26 від 21.05.2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>21.05.2026</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>ВАЛОКОРМІД, краплі оральні, по 25 мл у флаконах;, Серія № 11225, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -5129,17 +5129,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>№ 259-001.2/002.0/17-26 від 21.05.2026</t>
+          <t>№ 260-001.2/002.0/17-26 від 22.05.2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>21.05.2026</t>
+          <t>22.05.2026</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>ВАЛОКОРМІД, краплі оральні, по 25 мл у флаконах;, Серія № 11225, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
+          <t>GENTEAL GEL, гель для очей, Серія № 2X11, EXCELVISION 27 RUE DE LA LOMBARDIER ANNONAY, 07100, FRENCH REPUBLIC, Франція</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>№ 260-001.2/002.0/17-26 від 22.05.2026</t>
+          <t>№ 261-001.2/002.0/17-26 від 22.05.2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>GENTEAL GEL, гель для очей, Серія № 2X11, EXCELVISION 27 RUE DE LA LOMBARDIER ANNONAY, 07100, FRENCH REPUBLIC, Франція</t>
+          <t>HEROGEL, суспензія для перорального застосування, ПЕТ-пляшка 240 мл, Серія № 83300804, Heromycin pharma Co., Ltd., -</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5185,17 +5185,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>№ 261-001.2/002.0/17-26 від 22.05.2026</t>
+          <t>№ 262-001.2/002.0/17-26 від 25.05.2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>22.05.2026</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>HEROGEL, суспензія для перорального застосування, ПЕТ-пляшка 240 мл, Серія № 83300804, Heromycin pharma Co., Ltd., -</t>
+          <t>ЕЗОЛОНГ®-20, таблетки, вкриті плівковою оболонкою, по 20 мг; по 7 таблеток у блістері; по 2 блістери у картонній коробці, Серія № ЕЕР25008А1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>№ 262-001.2/002.0/17-26 від 25.05.2026</t>
+          <t>№ 263-001.2/002.0/17-26 від 26.05.2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>25.05.2026</t>
+          <t>26.05.2026</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>ЕЗОЛОНГ®-20, таблетки, вкриті плівковою оболонкою, по 20 мг; по 7 таблеток у блістері; по 2 блістери у картонній коробці, Серія № ЕЕР25008А1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг, по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці;, Серія № ЕСМ25001В1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5241,17 +5241,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>№ 263-001.2/002.0/17-26 від 26.05.2026</t>
+          <t>№ 264-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>26.05.2026</t>
+          <t>27.05.2026</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг, по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці;, Серія № ЕСМ25001В1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>MONSEL`S SOLUTION, розчин, Серія № 640911253, Premier Medical Products, -</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>№ 264-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 265-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>MONSEL`S SOLUTION, розчин, Серія № 640911253, Premier Medical Products, -</t>
+          <t>APALIN 250 mg Injection, 125 mg/1 mL, розчин для ін`єкцій по 2 мл в ампулі; по 10 ампул у картонній пачці, Серія № 242837T, Duopharma (M) Sdn. Bhd., Малайзія</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>№ 265-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 266-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>APALIN 250 mg Injection, 125 mg/1 mL, розчин для ін`єкцій по 2 мл в ампулі; по 10 ампул у картонній пачці, Серія № 242837T, Duopharma (M) Sdn. Bhd., Малайзія</t>
+          <t>AMPICILLIN SODIUM, порошок для ін'єкцій, Серія № 315089, TP Drug Laboratories (1969) Co., Ltd (Praram 2 Branch), -</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>№ 266-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 267-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>AMPICILLIN SODIUM, порошок для ін'єкцій, Серія № 315089, TP Drug Laboratories (1969) Co., Ltd (Praram 2 Branch), -</t>
+          <t>FLEBOGAMMA DIF 5%, 50 mg/ml, розчин для інфузій, 400 мл, Серія № G04K181561, Instituto Grifols, S.A facility in Parets del Valles, Barcelona, Іспанія</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>№ 267-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 268-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>FLEBOGAMMA DIF 5%, 50 mg/ml, розчин для інфузій, 400 мл, Серія № G04K181561, Instituto Grifols, S.A facility in Parets del Valles, Barcelona, Іспанія</t>
+          <t>DURATESTON, 30  mg, 60  mg, 100 mg, cтерилізовані парентеральні розчини малого об'єму, Серія № 945858, ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>№ 268-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>DURATESTON, 30  mg, 60  mg, 100 mg, cтерилізовані парентеральні розчини малого об'єму, Серія № 945858, ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
+          <t>АА PHARMA HYDROXYZINE CAPSULE, 10 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW6213A, AW6448A, AW8160A, AW8161A, AW8177A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>АА PHARMA HYDROXYZINE CAPSULE, 10 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW6213A, AW6448A, AW8160A, AW8161A, AW8177A, Catalent Ontario Limited, Канада</t>
+          <t>PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
+          <t>АА PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 270-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>АА PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
+          <t>GLUMET XR 500 mg, таблетки № 10 у блістері, у картонній коробці № 100, Серія № 5028486, 5032332, 5032334, 2034104, 5034103, 5034100, 5036722, 5036724, 5036723, 5037167, 5036983, 5036984, 5038424, 5039549, 5040444, Pharmaniaga Manufacturing Berhad, Selangor, Малайзія</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>№ 270-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 271-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>GLUMET XR 500 mg, таблетки № 10 у блістері, у картонній коробці № 100, Серія № 5028486, 5032332, 5032334, 2034104, 5034103, 5034100, 5036722, 5036724, 5036723, 5037167, 5036983, 5036984, 5038424, 5039549, 5040444, Pharmaniaga Manufacturing Berhad, Selangor, Малайзія</t>
+          <t>PALIFREN LONG 150 mg ( Paliperidonum), пролонгована суспензія для ін’єкцій у попередньо наповненому шприці, Серія № 4201120, 4300099, 4201591, PHARMATHEN INTERNATIONAL S.A Rodopi, Evrou, Греція</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>№ 271-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 272-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>PALIFREN LONG 150 mg ( Paliperidonum), пролонгована суспензія для ін’єкцій у попередньо наповненому шприці, Серія № 4201120, 4300099, 4201591, PHARMATHEN INTERNATIONAL S.A Rodopi, Evrou, Греція</t>
+          <t>FOSFATO DISSODICO DE DEXAMETASONA, 4 MG/ML, парентеральні розчини малого об’єму, стерилізовані термінальним методом, № 50, Серія № 25091566, HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, Бразилія</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>№ 272-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 273-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>FOSFATO DISSODICO DE DEXAMETASONA, 4 MG/ML, парентеральні розчини малого об’єму, стерилізовані термінальним методом, № 50, Серія № 25091566, HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, Бразилія</t>
+          <t>SPHERICAL ADSORPTIVE CARBON (Black Tablets), № 336, Серія № TK24804, TK24Y18, TK24Y19, TK25115, TK25117, TK25209, TK25306, TK25307, TK25308, TK25908, TT24Y05, TT24Z13, TP24601, TP24607, TP25222, TP25804, KUREHA Corporation, -</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5570,34 +5570,6 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74" ht="40" customHeight="1">
-      <c r="A74" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>№ 273-001.2/002.0/17-26 від 27.05.2026</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>27.05.2026</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>SPHERICAL ADSORPTIVE CARBON (Black Tablets), № 336, Серія № TK24804, TK24Y18, TK24Y19, TK25115, TK25117, TK25209, TK25306, TK25307, TK25308, TK25908, TT24Y05, TT24Z13, TP24601, TP24607, TP25222, TP25804, KUREHA Corporation, -</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5610,7 +5582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5797,7 +5769,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>№ 276-001.2/002.0/17-26 від 01.06.2026</t>
+          <t>№ 277-001.2/002.0/17-26 від 01.06.2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -5807,7 +5779,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ФЕНІБУТ, таблетки по 250 мг по 10 таблеток у блістері, по 2 блістери у коробці з картону, Серія № 070925, ТОВ "АСТРАФАРМ", Україна,</t>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг, по 10 таблеток у блістері; по 2 блістери в пачці з картону, Серія № 170226, ПАТ "Лубнифарм", Україна</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5825,7 +5797,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>№ 277-001.2/002.0/17-26 від 01.06.2026</t>
+          <t>№ 278-001.2/002.0/17-26 від 01.06.2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5835,7 +5807,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг, по 10 таблеток у блістері; по 2 блістери в пачці з картону, Серія № 170226, ПАТ "Лубнифарм", Україна</t>
+          <t>OZEMPIC (Semaglutide), 0.25 mg-0.5 mg/doses, розчин для ін'єкцій у попередньо заповненій шприц-ручці, у картонній коробці з 1 ручкою та 6 одноразовими голками                       (6 доз), Серія № PP5K617, з маркуванням виробника Novo Nordisk A/S., -</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5853,7 +5825,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>№ 278-001.2/002.0/17-26 від 01.06.2026</t>
+          <t>№ 279-001.2/002.0/17-26 від 01.06.2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5863,7 +5835,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>OZEMPIC (Semaglutide), 0.25 mg-0.5 mg/doses, розчин для ін'єкцій у попередньо заповненій шприц-ручці, у картонній коробці з 1 ручкою та 6 одноразовими голками                       (6 доз), Серія № PP5K617, з маркуванням виробника Novo Nordisk A/S., -</t>
+          <t>МЕТРОГІЛ®, гель для зовнішнього застосування, 10 мг/г, по 30 г у тубі з ламінованого пластику, по 1 тубі в картонній коробці, Серія № PGN6003, Юнік Фармасьютикал Лабораторіз (відділення фірми "Дж. Б. Кемікалз енд Фармасьютикалз Лтд."), Індія</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5881,17 +5853,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>№ 279-001.2/002.0/17-26 від 01.06.2026</t>
+          <t>№ 280-001.2/002.0/17-26 від 02.06.2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>01.06.2026</t>
+          <t>02.06.2026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>МЕТРОГІЛ®, гель для зовнішнього застосування, 10 мг/г, по 30 г у тубі з ламінованого пластику, по 1 тубі в картонній коробці, Серія № PGN6003, Юнік Фармасьютикал Лабораторіз (відділення фірми "Дж. Б. Кемікалз енд Фармасьютикалз Лтд."), Індія</t>
+          <t>ПЕРЕКИС - ВІШФА, розчин для зовнішнього застосування 3 %; по 100 мл у флаконах полімерних, Серія № 60825, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5909,17 +5881,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>№ 280-001.2/002.0/17-26 від 02.06.2026</t>
+          <t>№ 281-001.2/002.0/17-26 від 03.06.2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>02.06.2026</t>
+          <t>03.06.2026</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ПЕРЕКИС - ВІШФА, розчин для зовнішнього застосування 3 %; по 100 мл у флаконах полімерних, Серія № 60825, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
+          <t>TRZ-10 (Tirzepatide (rDNA origin), контейнер із прозорого пластику, що містить два скляних флакони: TRZ-10, 10 mg/vial; WATER (bacteriostatic USP) 3ml/vial, Серія № всі серії, із маркуванням GENIK, Netherlands</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5937,17 +5909,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>№ 281-001.2/002.0/17-26 від 03.06.2026</t>
+          <t>№ 282-001.2/002.0/17-26 від 05.06.2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>03.06.2026</t>
+          <t>05.06.2026</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>TRZ-10 (Tirzepatide (rDNA origin), контейнер із прозорого пластику, що містить два скляних флакони: TRZ-10, 10 mg/vial; WATER (bacteriostatic USP) 3ml/vial, Серія № всі серії, із маркуванням GENIK, Netherlands</t>
+          <t>BAIRABRON® (Trimebutine and Simethicone) 200 mg/75 mg, таблетки № 24 у картонній коробці, Серія № 0418D25, 0513M25, 0514M25A, 0802G25, 0803G25, 0804G25, 1112N25A, Protein, S.A. de C.V., -</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -5965,7 +5937,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>№ 282-001.2/002.0/17-26 від 05.06.2026</t>
+          <t>№ 283-001.2/002.0/17-26 від 05.06.2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5975,7 +5947,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>BAIRABRON® (Trimebutine and Simethicone) 200 mg/75 mg, таблетки № 24 у картонній коробці, Серія № 0418D25, 0513M25, 0514M25A, 0802G25, 0803G25, 0804G25, 1112N25A, Protein, S.A. de C.V., -</t>
+          <t>ALDOMET 250 mg (Methyldopa), таблетки, вкриті оболонкою, Серія № P0019875, ASPEN SA OSD, Південно-Африканська Республіка</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -5993,7 +5965,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>№ 283-001.2/002.0/17-26 від 05.06.2026</t>
+          <t>№ 284-001.2/002.0/17-26 від 05.06.2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -6003,7 +5975,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ALDOMET 250 mg (Methyldopa), таблетки, вкриті оболонкою, Серія № P0019875, ASPEN SA OSD, Південно-Африканська Республіка</t>
+          <t>RIVIAL MV12, Ergocalciferol 5 mcg +Biotina 60 mcg + Acido Folico 400 mcg + Cianocobalamina 5 mcg + Riboflavina 5fosfato sodico 3.6 mg + Piridoxina clorhidrato 4.86 mg + Tiamina clorhidrato, 50 ліофілізованих ампул (лише для використання в лікарні), Серія № G/099, G/101, G/105, G/111, G/112, G/118, H/099, Н/105, H/111, H/112, I/112, LABORATORIOS SOLKOTAL S.A., , Аргентина</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -6021,7 +5993,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>№ 284-001.2/002.0/17-26 від 05.06.2026</t>
+          <t>№ Проект від 05.06.2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -6031,7 +6003,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>RIVIAL MV12, Ergocalciferol 5 mcg +Biotina 60 mcg + Acido Folico 400 mcg + Cianocobalamina 5 mcg + Riboflavina 5fosfato sodico 3.6 mg + Piridoxina clorhidrato 4.86 mg + Tiamina clorhidrato, 50 ліофілізованих ампул (лише для використання в лікарні), Серія № G/099, G/101, G/105, G/111, G/112, G/118, H/099, Н/105, H/111, H/112, I/112, LABORATORIOS SOLKOTAL S.A., , Аргентина</t>
+          <t>BAIRABRON® (Trimebutine and Simethicone) 200 mg/75 mg, таблетки № 24 у картонній коробці, Серія № 0418D25, 0513M25, 0514M25A, 0802G25, 0803G25, 0804G25, 1112N25A, Protein, S.A. de C.V., -</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6049,17 +6021,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>№ Проект від 05.06.2026</t>
+          <t>№ 285-001.2/002.0/17-26 від 09.06.2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>05.06.2026</t>
+          <t>09.06.2026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>BAIRABRON® (Trimebutine and Simethicone) 200 mg/75 mg, таблетки № 24 у картонній коробці, Серія № 0418D25, 0513M25, 0514M25A, 0802G25, 0803G25, 0804G25, 1112N25A, Protein, S.A. de C.V., -</t>
+          <t>КАРДАК, таблетки вкриті плівковою оболонкою, по 40 мг, по 10 таблеток у блістері, по 3 блістера у пачці з картону, Серія № SBM2500740B, Ауробіндо Фарма Лімітед, Формулейшин, Юніт-XV, Індія</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -6087,7 +6059,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>КАРДАК, таблетки вкриті плівковою оболонкою, по 40 мг, по 10 таблеток у блістері, по 3 блістера у пачці з картону, Серія № SBM2500740B, Ауробіндо Фарма Лімітед, Формулейшин, Юніт-XV, Індія</t>
+          <t>КАРДАК, таблетки вкриті плівковою оболонкою, по 20 мг, по 10 таблеток у блістері, по 3 блістера у пачці з картону, Серія № SBM2500420F, Ауробіндо Фарма Лімітед, Формулейшин, Юніт-XV, Індія</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -6105,17 +6077,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>№ 285-001.2/002.0/17-26 від 09.06.2026</t>
+          <t>№ 287-001.2/002.0/17-26 від 10.06.2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>09.06.2026</t>
+          <t>10.06.2026</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>КАРДАК, таблетки вкриті плівковою оболонкою, по 20 мг, по 10 таблеток у блістері, по 3 блістера у пачці з картону, Серія № SBM2500420F, Ауробіндо Фарма Лімітед, Формулейшин, Юніт-XV, Індія</t>
+          <t>СПИРТ ЕТИЛОВИЙ 96%, розчин для зовнішнього застосування 96 %, по 100 мл у флаконах, Серія № 170725, ПрАТ "Біолік", Україна</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -6133,17 +6105,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>№ 287-001.2/002.0/17-26 від 10.06.2026</t>
+          <t>№ 288-001.2/002.0/17-26 від 11.06.2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10.06.2026</t>
+          <t>11.06.2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>СПИРТ ЕТИЛОВИЙ 96%, розчин для зовнішнього застосування 96 %, по 100 мл у флаконах, Серія № 170725, ПрАТ "Біолік", Україна</t>
+          <t>TEIKOPLANINA BRADEX, 200 mg, порошок та розчинник для розчину для ін'єкцій/інфузій або перорального розчину, Серія № 2457043, DEMO S.A. PHARMACEUTICAL INDUSTRY, Греція</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6161,7 +6133,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>№ 288-001.2/002.0/17-26 від 11.06.2026</t>
+          <t>№ 289-001.2/002.0/17-26 від 11.06.2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -6171,7 +6143,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>TEIKOPLANINA BRADEX, 200 mg, порошок та розчинник для розчину для ін'єкцій/інфузій або перорального розчину, Серія № 2457043, DEMO S.A. PHARMACEUTICAL INDUSTRY, Греція</t>
+          <t>CONVULEX, (Valproic acid) 50 mg/ml, сіроп для дітей, скляний флакон об'ємом 100 мл, Серія № M00651, G.L. Pharma GmbH Standort 1160 Wien, Австрія</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -6189,7 +6161,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>№ 289-001.2/002.0/17-26 від 11.06.2026</t>
+          <t>№ 290-001.2/002.0/17-26 від 11.06.2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -6199,7 +6171,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CONVULEX, (Valproic acid) 50 mg/ml, сіроп для дітей, скляний флакон об'ємом 100 мл, Серія № M00651, G.L. Pharma GmbH Standort 1160 Wien, Австрія</t>
+          <t>Re N ToxTM, clostridium botulinum toxin type A, 100 units, 1 vial, Серія № всі серії, Pharma Research BIO Co., Ltd., Republic of Korea</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -6217,7 +6189,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>№ 290-001.2/002.0/17-26 від 11.06.2026</t>
+          <t>№ 291-001.2/002.0/17-26 від 11.06.2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -6227,7 +6199,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Re N ToxTM, clostridium botulinum toxin type A, 100 units, 1 vial, Серія № всі серії, Pharma Research BIO Co., Ltd., Republic of Korea</t>
+          <t>CARDIOPLEGIC SOLUTION IB, 500 ml, внутрішньосерцевий розчин, Серія № 2621440229, 2621440230, 2621440231, 2621440232, 2621440233, 2621440234, 2621440235, 2621440236, 2621440237, 2621440287, 2621440288, 2621440289, 2621440290, 2621440291, 2621440292, 2621440293, 2621440294, 2621440295, 2622240318, 2622240319, 2622240320, 2622240321, 2622240322, 2622240323, 2622240324, 2622240325, 2622240326, 2622240327, 2622240328, 2622240329, B. Braun Medical, S.A. Carretera de Terrassa, Іспанія</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -6255,7 +6227,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CARDIOPLEGIC SOLUTION IB, 500 ml, внутрішньосерцевий розчин, Серія № 2621440229, 2621440230, 2621440231, 2621440232, 2621440233, 2621440234, 2621440235, 2621440236, 2621440237, 2621440287, 2621440288, 2621440289, 2621440290, 2621440291, 2621440292, 2621440293, 2621440294, 2621440295, 2622240318, 2622240319, 2622240320, 2622240321, 2622240322, 2622240323, 2622240324, 2622240325, 2622240326, 2622240327, 2622240328, 2622240329, B. Braun Medical, S.A. Carretera de Terrassa, Іспанія</t>
+          <t>CARDIOPLEGIC SOLUTION (HB) WITHOUT POTASSIUM, 500 ml,, внутрішньосерцевий розчин, Серія № 2621340250, 2621340251, 2621340252, 2621340253, 2621340255, 2621340256, 2621340257, 2621340414, B. Braun Medical, S.A. Carretera de Terrassa, Іспанія</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -6283,7 +6255,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CARDIOPLEGIC SOLUTION (HB) WITHOUT POTASSIUM, 500 ml,, внутрішньосерцевий розчин, Серія № 2621340250, 2621340251, 2621340252, 2621340253, 2621340255, 2621340256, 2621340257, 2621340414, B. Braun Medical, S.A. Carretera de Terrassa, Іспанія</t>
+          <t>CARDIOPLEGIC SOLUTION (HB) WITH POTASSIUM, 500 ml, внутрішньосерцевий розчин, Серія № 2621340258, 2621340259, 2621340260, 2621340261, B. Braun Medical, S.A. Carretera de Terrassa, Іспанія</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -6301,17 +6273,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>№ 291-001.2/002.0/17-26 від 11.06.2026</t>
+          <t>№ 294-001.2/002.0/17-26 від 19.06.2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11.06.2026</t>
+          <t>19.06.2026</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CARDIOPLEGIC SOLUTION (HB) WITH POTASSIUM, 500 ml, внутрішньосерцевий розчин, Серія № 2621340258, 2621340259, 2621340260, 2621340261, B. Braun Medical, S.A. Carretera de Terrassa, Іспанія</t>
+          <t>ALBUNATE® 20%, розчин для ін'єкцій, флакон у картонній коробці., Серія № P100542812, P100564605, P100622643, P100544607, з маркуванням виробника CSL Behring AG, -</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -6339,7 +6311,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ALBUNATE® 20%, розчин для ін'єкцій, флакон у картонній коробці., Серія № P100542812, P100564605, P100622643, P100544607, з маркуванням виробника CSL Behring AG, -</t>
+          <t>HIGLOBIN® 5 g, розчин для ін'єкцій, флакон у картонній коробці, Серія № P100687928, P100697335, P100583631, P100649549, P100592175, P100687928, P100658686, P100681628, P100697335, P100589056, P100707988, P100662582, P100566928, P100600969, P100641596, P100574249, P100626316, P100632461, P100549898, P100592194, P100626311, P100594944, P100551256, P100592166, P100582242, P100539704, P100624139, P100454993, CSL Behring AG., -</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -6357,7 +6329,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>№ 294-001.2/002.0/17-26 від 19.06.2026</t>
+          <t>№ 297-001.2/002.0/17-26 від 19.06.2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -6367,7 +6339,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>HIGLOBIN® 5 g, розчин для ін'єкцій, флакон у картонній коробці, Серія № P100687928, P100697335, P100583631, P100649549, P100592175, P100687928, P100658686, P100681628, P100697335, P100589056, P100707988, P100662582, P100566928, P100600969, P100641596, P100574249, P100626316, P100632461, P100549898, P100592194, P100626311, P100594944, P100551256, P100592166, P100582242, P100539704, P100624139, P100454993, CSL Behring AG., -</t>
+          <t>JAKAVI 20 mg, таблетки № 50, Серія № AVT50, з маркуванням виробника Novartis, -</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -6395,7 +6367,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>JAKAVI 20 mg, таблетки № 50, Серія № AVT50, з маркуванням виробника Novartis, -</t>
+          <t>JAKAVI 15 mg, таблетки № 56, Серія № SGL04, з маркуванням виробника Novartis, -</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -6413,17 +6385,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>№ 297-001.2/002.0/17-26 від 19.06.2026</t>
+          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>19.06.2026</t>
+          <t>23.06.2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>JAKAVI 15 mg, таблетки № 56, Серія № SGL04, з маркуванням виробника Novartis, -</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по 25 г у контейнерах; по 20 г або 25 г у тубах; по 20 г або по 25 г у тубі; по 1 тубі в пачці; по 20 г або по 25 г у тубах ламінатних; по 20 г або по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 060924, 010125, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -6451,7 +6423,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по 25 г у контейнерах; по 20 г або 25 г у тубах; по 20 г або по 25 г у тубі; по 1 тубі в пачці; по 20 г або по 25 г у тубах ламінатних; по 20 г або по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 060924, 010125, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по  25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 071024, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -6479,7 +6451,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по  25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 071024, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по 25 г у  тубі; по 1 тубі в пачці;, Серія № 081124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6507,7 +6479,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по 25 г у  тубі; по 1 тубі в пачці;, Серія № 081124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по 25 г у тубі; по 1 тубі в пачці;, Серія № 020325, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -6535,7 +6507,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 5 % по 25 г у тубі; по 1 тубі в пачці;, Серія № 020325, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 060423, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6563,7 +6535,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 060423, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 050524, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -6591,7 +6563,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 050524, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г ламінатній тубі;  по 1 тубі в пачці, Серія № 131224, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6619,7 +6591,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г ламінатній тубі;  по 1 тубі в пачці, Серія № 131224, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній пачці, Серія № 070724, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6647,7 +6619,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній пачці, Серія № 070724, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 2% по 25 г у тубі, по 1 тубі у пачці, Серія № 040924, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6675,7 +6647,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 2% по 25 г у тубі, по 1 тубі у пачці, Серія № 040924, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 5% по 25 г у тубах ламінатних, в пачці, Серія № 060924, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -6693,7 +6665,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>№ 298-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 300-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -6703,7 +6675,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 5% по 25 г у тубах ламінатних, в пачці, Серія № 060924, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>ДІАГНОЛ®, порошок для орального розчину, 64 г/пакет по 73,69 г порошку у пакеті; по 4 пакети в пачці з картону, Серія № DMIR008780/2, АТ "Фармак", Україна</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6721,7 +6693,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>№ 300-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 301-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -6731,7 +6703,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>ДІАГНОЛ®, порошок для орального розчину, 64 г/пакет по 73,69 г порошку у пакеті; по 4 пакети в пачці з картону, Серія № DMIR008780/2, АТ "Фармак", Україна</t>
+          <t>ОВЕСТИН®, крем вагінальний, 1 мг/г; по 15 г у тубі; по 1 тубі у комплекті з аплікатором в пачці, Серія № 24Е001, Аспен Бад-Ольдесло ГмбХ. (виробник відповідальний за виробництво, первинне та вторинне пакування, контроль якості та випуск серії), Німеччина</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -6749,7 +6721,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>№ 301-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 303-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -6759,7 +6731,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>ОВЕСТИН®, крем вагінальний, 1 мг/г; по 15 г у тубі; по 1 тубі у комплекті з аплікатором в пачці, Серія № 24Е001, Аспен Бад-Ольдесло ГмбХ. (виробник відповідальний за виробництво, первинне та вторинне пакування, контроль якості та випуск серії), Німеччина</t>
+          <t>KEYTRUDA (pembrolizumab), 100mg/4mL, асептично оброблені парентеральні розчини малого об'єму, Серія № Y019149, з маркуванням виробника MERCK SHARP &amp; DOHME CORP., -</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6777,7 +6749,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>№ 303-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 304-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -6787,7 +6759,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>KEYTRUDA (pembrolizumab), 100mg/4mL, асептично оброблені парентеральні розчини малого об'єму, Серія № Y019149, з маркуванням виробника MERCK SHARP &amp; DOHME CORP., -</t>
+          <t>VECTIBIX 100 mg/5 mL (Panitumumab), флакон у картонній коробці, Серія № 2051100, 1166523, 1130818, 3377806, Amgen Manufacturing Limited, -</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6805,7 +6777,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>№ 304-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -6815,7 +6787,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>VECTIBIX 100 mg/5 mL (Panitumumab), флакон у картонній коробці, Серія № 2051100, 1166523, 1130818, 3377806, Amgen Manufacturing Limited, -</t>
+          <t>CLORAPREP 1 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 60, Серія № 3196393, 3325915, 3325918, 4021709, 4058230, 4058232, 4086014, 4086017, 4149178, 4155875, 4206632, 4210656, 4212800, 4233418, 4267729, 4270388, 4302021, 4302040, 4305711, 4324566, 4348098, 5026580, 5052205, 5081618, 5127264, 5133556, 5127263, 3261045, 3321422, 3346244, 4023071, 4058231, 4086024, 4151136, 4192080, 4212805, 4212806, 4233411, 4233411, 4270390, 4192033, 4212808, 4233414, 4267722, 4302029, 4325766, 4348096, 5026579, 5052200, 5133411, 3294918, 4206633, 4326463, BD Infection Prevention, Бельгія</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6843,7 +6815,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CLORAPREP 1 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 60, Серія № 3196393, 3325915, 3325918, 4021709, 4058230, 4058232, 4086014, 4086017, 4149178, 4155875, 4206632, 4210656, 4212800, 4233418, 4267729, 4270388, 4302021, 4302040, 4305711, 4324566, 4348098, 5026580, 5052205, 5081618, 5127264, 5133556, 5127263, 3261045, 3321422, 3346244, 4023071, 4058231, 4086024, 4151136, 4192080, 4212805, 4212806, 4233411, 4233411, 4270390, 4192033, 4212808, 4233414, 4267722, 4302029, 4325766, 4348096, 5026579, 5052200, 5133411, 3294918, 4206633, 4326463, BD Infection Prevention, Бельгія</t>
+          <t>CHLORAPREP FREPP 1,5 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 20, Серія № 3313882, 4020572, 4177103, 4264525, 3138975, 3227659, 3313884, 4169640, 4235732, 4295374, 5036189, 5037270, 5076598, 3138978, 4058927, 4085811, 4107060, 4138630, 4198196, 4198199, 4235722, 4264522, 4295373, 4330648, 5016735, 5037282, 5076588, 5114831, BD Infection Prevention, Бельгія</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -6861,7 +6833,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>№ 305-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 306-001.2/002.0/17-26 від 23.06.2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -6871,7 +6843,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CHLORAPREP FREPP 1,5 ml (2-propanol Chlorhexidine digluconate), концентрат для розчину для шкірного застосування, аплікатори № 20, Серія № 3313882, 4020572, 4177103, 4264525, 3138975, 3227659, 3313884, 4169640, 4235732, 4295374, 5036189, 5037270, 5076598, 3138978, 4058927, 4085811, 4107060, 4138630, 4198196, 4198199, 4235722, 4264522, 4295373, 4330648, 5016735, 5037282, 5076588, 5114831, BD Infection Prevention, Бельгія</t>
+          <t>CRISCY (SOMATROPINE), асептично оброблені парентеральні розчини малого об'єму, Серія № 22030133, з маркуванням виробника CRISTALIA PRODUTOS QUIMICOS FARMACEUTICOS LTDA, -</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -6889,17 +6861,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>№ 306-001.2/002.0/17-26 від 23.06.2026</t>
+          <t>№ 308-001.2/002.0/17-26 від 24.06.2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>23.06.2026</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CRISCY (SOMATROPINE), асептично оброблені парентеральні розчини малого об'єму, Серія № 22030133, з маркуванням виробника CRISTALIA PRODUTOS QUIMICOS FARMACEUTICOS LTDA, -</t>
+          <t>LEVOSIMENDAN FARMAK (Levosimendanum), концентрат для розчину для інфузій, 2,5 мг/мл, флакон 5 мл, Серія № 20825, Farmak International Sp. z o.o., Польща</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -6917,17 +6889,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>№ 308-001.2/002.0/17-26 від 24.06.2026</t>
+          <t>№ 309-001.2/002.0/17-26 від 25.06.2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>25.06.2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>LEVOSIMENDAN FARMAK (Levosimendanum), концентрат для розчину для інфузій, 2,5 мг/мл, флакон 5 мл, Серія № 20825, Farmak International Sp. z o.o., Польща</t>
+          <t>NILOTNIB 200 mg, капсули № 112, № 40, Серія № H0444A, H0444C, H0444E, H0444F, H0444G, H0444H, H0444AA (bulk KH0444), PHAROS MT LIMITED, -</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6945,7 +6917,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>№ 309-001.2/002.0/17-26 від 25.06.2026</t>
+          <t>№ 310-001.2/002.0/17-26 від 25.06.2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -6955,7 +6927,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>NILOTNIB 200 mg, капсули № 112, № 40, Серія № H0444A, H0444C, H0444E, H0444F, H0444G, H0444H, H0444AA (bulk KH0444), PHAROS MT LIMITED, -</t>
+          <t>AZANESON (Azelastini hydrochloridum + Fluticasoni propionas), назальний спрей, суспензія, 1 флакон 120 доз, Серія № 251794, Basic Pharma Manufacturing B.V., Нідерланди</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -6973,7 +6945,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>№ 310-001.2/002.0/17-26 від 25.06.2026</t>
+          <t>№ 311-001.2/002.0/17-26 від 25.06.2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -6983,7 +6955,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>AZANESON (Azelastini hydrochloridum + Fluticasoni propionas), назальний спрей, суспензія, 1 флакон 120 доз, Серія № 251794, Basic Pharma Manufacturing B.V., Нідерланди</t>
+          <t>TEICOPLANIN APTAPHARMA 400 mg (Teicoplaninum), порошок та розчинник для приготування розчину для ін'єкцій/інфузій, 1 флакон містить 400 мг порошку та 1 ампулу 3,2 мл розчинника, Серія № E003B01K (outer packaging), E003B (vial with powder), E001K (ampoule with solvent), Sirton Pharmaceuticals S.p.A., Італiя</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7001,7 +6973,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>№ 311-001.2/002.0/17-26 від 25.06.2026</t>
+          <t>№ 312-001.2/002.0/17-26 від 25.06.2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -7011,7 +6983,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>TEICOPLANIN APTAPHARMA 400 mg (Teicoplaninum), порошок та розчинник для приготування розчину для ін'єкцій/інфузій, 1 флакон містить 400 мг порошку та 1 ампулу 3,2 мл розчинника, Серія № E003B01K (outer packaging), E003B (vial with powder), E001K (ampoule with solvent), Sirton Pharmaceuticals S.p.A., Італiя</t>
+          <t>TEICOPLANIN APTAPHARMA 200 mg (Teicoplaninum), порошок та розчинник для приготування розчину для ін'єкцій/інфузій, 1 флакон містить 200 мг порошку та 1 ампулу 3,2 мл розчинника, Серія № E001A01K (зовнішня упаковка), E001A (флакон з порошком), E001K (ампула з розчинником), Sirton Pharmaceuticals S.p.A., Італiя</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -7029,7 +7001,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>№ 312-001.2/002.0/17-26 від 25.06.2026</t>
+          <t>№ 313-001.2/002.0/17-26 від 25.06.2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -7039,7 +7011,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>TEICOPLANIN APTAPHARMA 200 mg (Teicoplaninum), порошок та розчинник для приготування розчину для ін'єкцій/інфузій, 1 флакон містить 200 мг порошку та 1 ампулу 3,2 мл розчинника, Серія № E001A01K (зовнішня упаковка), E001A (флакон з порошком), E001K (ампула з розчинником), Sirton Pharmaceuticals S.p.A., Італiя</t>
+          <t>BD CHLORAPREP™ 1 ml Applicator - Clear (2% w/v chlorhexidine gluconate (CHG) and 70% v/v isopropyl alcohol), аплікатор для стерильних розчинів, № 60, Серія № 3352268, 4049128, 4060484, 4072323, CareFusion 213 LLC, -</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7057,17 +7029,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>№ 313-001.2/002.0/17-26 від 25.06.2026</t>
+          <t>№ 314-001.2/002.0/17-26 від 26.06.2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>25.06.2026</t>
+          <t>26.06.2026</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>BD CHLORAPREP™ 1 ml Applicator - Clear (2% w/v chlorhexidine gluconate (CHG) and 70% v/v isopropyl alcohol), аплікатор для стерильних розчинів, № 60, Серія № 3352268, 4049128, 4060484, 4072323, CareFusion 213 LLC, -</t>
+          <t>всі серії ЛЗ, виробництва Labormed Pharma SA, -, Серія № всі серії, Labormed Pharma SA, Румунія</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -7085,7 +7057,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>№ 314-001.2/002.0/17-26 від 26.06.2026</t>
+          <t>№ 316-001.2/002.0/17-26 від 26.06.2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7095,7 +7067,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>всі серії ЛЗ, виробництва Labormed Pharma SA, -, Серія № всі серії, Labormed Pharma SA, Румунія</t>
+          <t>всі серії ЛЗ виробництва Sichuan New Hawk Biotechnology Co. Ltd., -, Серія № всі серії, Sichuan New Hawk Biotechnology Co. Ltd., Китай</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7113,7 +7085,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>№ 316-001.2/002.0/17-26 від 26.06.2026</t>
+          <t>№ 317-001.2/002.0/17-26 від 26.06.2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -7123,7 +7095,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>всі серії ЛЗ виробництва Sichuan New Hawk Biotechnology Co. Ltd., -, Серія № всі серії, Sichuan New Hawk Biotechnology Co. Ltd., Китай</t>
+          <t>CIALIS 20 mg (Tadalafil), таблетки, вкриті плівковою оболонкою, по 20 мг; по 1 таблетці у блістері, по 1 блістеру в картонній коробці, по 2 таблетки у блістері, по 1, або по 2, або по 4 блістери в картонній коробці, Серія № D580306, з маркуванням виробника Lilly del Caribe Inc. Carolina, Puerto Rico, США/Іспанія</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -7141,7 +7113,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>№ 317-001.2/002.0/17-26 від 26.06.2026</t>
+          <t>№ 318-001.2/002.0/17-26 від 26.06.2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -7151,7 +7123,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CIALIS 20 mg (Tadalafil), таблетки, вкриті плівковою оболонкою, по 20 мг; по 1 таблетці у блістері, по 1 блістеру в картонній коробці, по 2 таблетки у блістері, по 1, або по 2, або по 4 блістери в картонній коробці, Серія № D580306, з маркуванням виробника Lilly del Caribe Inc. Carolina, Puerto Rico, США/Іспанія</t>
+          <t>BOTOX COSMETIC FOR INJECTION 100 Units/vial, флакон у картонній коробці, Серія № C7048C4, з маркуванням виробника AbbVie Limited (раніше Allergan), -</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7162,34 +7134,6 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="40" customHeight="1">
-      <c r="A55" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>№ 318-001.2/002.0/17-26 від 26.06.2026</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>26.06.2026</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>BOTOX COSMETIC FOR INJECTION 100 Units/vial, флакон у картонній коробці, Серія № C7048C4, з маркуванням виробника AbbVie Limited (раніше Allergan), -</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9046,7 +8990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9871,6 +9815,62 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
     </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>№ 374-001.001/002.0/17-26 від 13.08.2026</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT® 500 U (Botulinum toxin type A), порошок для розчину для ін'єкцій, Серія № 020302, 029035, з маркуванням виробника Ipsen Biopharm Ltd, -</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>№ 375-001.001/002.0/17-26 від 13.08.2026</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>NEBIDO(Testosterone undecylate) 250 mg/ml,, термінально стерилізовані парентеральні розчини малого об'єму, Серія № KT0S5T4, з маркуванням виробника BAYER AG, -</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8990,7 +8990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9871,6 +9871,118 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
     </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>№ 377-001.001/002.0/17-26 від 14.08.2026</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>МЕЗИМ® КАПСУЛИ 10000, капсули тверді з кишковорозчинними міні-таблетками; по 20 капсул у банці з поліпропілену; по 1 банці в картонній коробці, Серія № 51225В, БЕРЛІН-ХЕМІ АГ, Німеччина</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>№ 378-001.001/002.0/17-26 від 14.08.2026</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ПРЕСКОР®, концентрат для приготування розчину для інфузій, по 2,5 мг/мл, по 5 мл у флаконі скляному, по 1 флакону в пачці, Серія № 30825, АТ "Фармак", Україна</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>№ 379-001.001/002.0/17-26 від 14.08.2026</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>PHARMATON® 50+ SENIOR (Multivitamin), капсули у картонній коробці № 30, № 60, Серія № P0334801, з маркуванням виробника Swiss Caps AG, Husenstrasse 35, 9533 Kirchberg, Swiss, Швейцарія</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>№ 380-001.001/002.0/17-26 від 14.08.2026</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>14.08.2026</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>всі ЛЗ, виробництва  Aculife Healthcare Private Limited (Unit 9), -, Серія № всі серії, Aculife Healthcare Private Limited (Unit 9), Індія</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8990,7 +8990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9983,6 +9983,258 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
     </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>№ 381-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>ЛІНЕБІОТИК, розчин для інфузій, 2 мг/мл; по 300 мл у флаконі, по 1 флакону у картонній коробці, Серія № 6188004, ВЕМ Ілач Сан. ве Тік. А.С., Туреччина</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>ROSUVASTATIN CALCIUM, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD, Китай</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>PARICALCITOL, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>TANDOSPIRONE CITRATE, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>TADALAFIL, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD, Китай</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>BILASTIN, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>FOSAPREPITANT DIMEGLUMINE, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>№ 384-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>LATANOPROST 125 mcg/2,5 ml, краплі, Серія № 3141125, 3151225, 3010126, 3020126, 3030126, Zentiva k.s., Чехія</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>№ 384-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>SOFRADEX 40 mg/8 ml EEDRO BT1, -, Серія № 2110426, Zentiva k.s., Чехія</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8990,7 +8990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>№ 384-001.001/002.0/17-26 від 19.08.2026</t>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>LATANOPROST 125 mcg/2,5 ml, краплі, Серія № 3141125, 3151225, 3010126, 3020126, 3030126, Zentiva k.s., Чехія</t>
+          <t>POLIDOCANOL, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>№ 384-001.001/002.0/17-26 від 19.08.2026</t>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>SOFRADEX 40 mg/8 ml EEDRO BT1, -, Серія № 2110426, Zentiva k.s., Чехія</t>
+          <t>CLEMASTINE FUMARATE, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -10234,6 +10234,174 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>ILAPRAZOLE SODIUM, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>MANGANESE SULFATE, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>SELENIOUS ACID, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай, Китай</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>№ 382-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>CINACALCET HYDROCHLORIDE, АФІ, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>№ 384-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>LATANOPROST 125 mcg/2,5 ml, краплі, Серія № 3141125, 3151225, 3010126, 3020126, 3030126, Zentiva k.s., Чехія</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>№ 384-001.001/002.0/17-26 від 19.08.2026</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>SOFRADEX 40 mg/8 ml EEDRO BT1, -, Серія № 2110426, Zentiva k.s., Чехія</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8990,7 +8990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10403,6 +10403,34 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
     </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>№ 385-001.001/002.0/17-26 від 20.08.2026</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Кисень, у  балонах, Серія № всі серії, згідно наданої інформації ПрАТ "Рівнеазот", Україна</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8990,7 +8990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>№ 384-001.001/002.0/17-26 від 19.08.2026</t>
+          <t>№ 383-001.001/002.0/17-26 від 19.08.2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>LATANOPROST 125 mcg/2,5 ml, краплі, Серія № 3141125, 3151225, 3010126, 3020126, 3030126, Zentiva k.s., Чехія</t>
+          <t>НАКЛОФЕН ДУО, капсули по 75 мг по 10 капсул у блістері; по 2 блістери у картонній коробці, Серія № DH0676, КРКА, д.д., Ново место, Словенія</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>SOFRADEX 40 mg/8 ml EEDRO BT1, -, Серія № 2110426, Zentiva k.s., Чехія</t>
+          <t>LATANOPROST 125 mcg/2,5 ml, краплі, Серія № 3141125, 3151225, 3010126, 3020126, 3030126, Zentiva k.s., Чехія</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -10409,17 +10409,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>№ 385-001.001/002.0/17-26 від 20.08.2026</t>
+          <t>№ 384-001.001/002.0/17-26 від 19.08.2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Кисень, у  балонах, Серія № всі серії, згідно наданої інформації ПрАТ "Рівнеазот", Україна</t>
+          <t>SOFRADEX 40 mg/8 ml EEDRO BT1, -, Серія № 2110426, Zentiva k.s., Чехія</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10430,6 +10430,34 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>№ 385-001.001/002.0/17-26 від 20.08.2026</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Кисень, у  балонах, Серія № всі серії, згідно наданої інформації ПрАТ "Рівнеазот", Україна</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8990,7 +8990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10459,6 +10459,34 @@
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
     </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>№ 387-001.001/002.0/17-26 від 21.08.2026</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>ЕРГОС®, таблетки по 50 мг по 2 таблетки у блістері; по 1 блістеру в коробці, Серія № 020525, ТОВ "Фармацевтична компанія "ФарКоС", Україна</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8990,7 +8990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10487,6 +10487,90 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
     </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>№ 389-001.001/002.0/17-26 від 24.08.2026</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>всі ЛЗ, виробництва Norgine Limited, Сполучене Королівство, -, Серія № всі серії, Norgine Limited, Сполучене Королівство</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>№ 390-001.001/002.0/17-26 від 24.08.2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>LANZOTRED SOFT CAPSULES (Enzalutamide) 40 mg, капсули в алюмінієвому блістері, Серія № F10753P2 &amp; G19850P2, Lotus Pharmaceutical Co., Ltd. Nantou Plant, Тайвань</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>№ 391-001.001/002.0/17-26 від 24.08.2026</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>RHEUMESSER, розчин для дисперсії для ін'єкцій/інфузій, Серія № G10759, K09548, K09549, K09548, H08873, M04154, G09087, G09087, G.L. Pharma GmbH, Австрія</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -3486,7 +3486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>№ 227-001.2/002.0/17-26 від 05.05.2026</t>
+          <t>№ 228-001.2/002.0/17-26 від 05.05.2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ГЛОДУ НАСТОЙКА, настойка для перорального застосування по 100 мл у флаконах полімерних, Серія № 591025, ПП "Кілафф", Україна</t>
+          <t>САЛІЦИЛОВА КИСЛОТА, розчин для зовнішнього застосування, спиртовий 1 % по 40 мл у флаконах скляних, укупорених пробками і кришками;, Серія № 320725, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>№ 228-001.2/002.0/17-26 від 05.05.2026</t>
+          <t>№ 229-001.2/002.0/17-26 від 05.05.2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА КИСЛОТА, розчин для зовнішнього застосування, спиртовий 1 % по 40 мл у флаконах скляних, укупорених пробками і кришками;, Серія № 320725, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>СОФОРИ ЯПОНСЬКОЇ НАСТОЙКА, настойка, по 40 мл у флаконах полімерних, Серія № 040424, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>№ 229-001.2/002.0/17-26 від 05.05.2026</t>
+          <t>№ 230-001.2/002.0/17-26 від 05.05.2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>СОФОРИ ЯПОНСЬКОЇ НАСТОЙКА, настойка, по 40 мл у флаконах полімерних, Серія № 040424, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>ЗОНІК, капсули тверді по 25 мг; по 14 капсул у блістері; по 2   блістери в картонній упаковці, Серія № 1008141, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>№ 230-001.2/002.0/17-26 від 05.05.2026</t>
+          <t>№ 231-001.2/002.0/17-26 від 06.05.2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>05.05.2026</t>
+          <t>06.05.2026</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ЗОНІК, капсули тверді по 25 мг; по 14 капсул у блістері; по 2   блістери в картонній упаковці, Серія № 1008141, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
+          <t>пмс-БУСУЛЬФАН / pms-BUSULFAN, розчин для ін'єкцій, 6 мг/мл, по 10 мл у флаконі;  по 8 флаконів у коробці, Серія № 660609, Фармасайнс Інк., Канада</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3729,17 +3729,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>№ 231-001.2/002.0/17-26 від 06.05.2026</t>
+          <t>№ 232-001.2/002.0/17-26 від 07.05.2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
+          <t>07.05.2026</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>пмс-БУСУЛЬФАН / pms-BUSULFAN, розчин для ін'єкцій, 6 мг/мл, по 10 мл у флаконі;  по 8 флаконів у коробці, Серія № 660609, Фармасайнс Інк., Канада</t>
+          <t>АВЕЦИН-Н, розчин для інфузій, 400 мг/250 мл, по 250 мл у флаконі;  по 10 флаконів у коробці, Серія № А010624, Нерозфасований продукт, первинна упаковка, вторинна упаковка, контроль: ВІОСЕР С.А. ПАРЕНТЕРАЛ СОЛЮШНС ІНДАСТРІ, Греція Контроль, випуск серії: ТОВ "ФАРМАСЕЛ", Україна, Греція/ Україна</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>№ 232-001.2/002.0/17-26 від 07.05.2026</t>
+          <t>№ 233-001.2/002.0/17-26 від 07.05.2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>АВЕЦИН-Н, розчин для інфузій, 400 мг/250 мл, по 250 мл у флаконі;  по 10 флаконів у коробці, Серія № А010624, Нерозфасований продукт, первинна упаковка, вторинна упаковка, контроль: ВІОСЕР С.А. ПАРЕНТЕРАЛ СОЛЮШНС ІНДАСТРІ, Греція Контроль, випуск серії: ТОВ "ФАРМАСЕЛ", Україна, Греція/ Україна</t>
+          <t>ГАРДАСИЛ / GARDASIL® ВАКЦИНА ПРОТИ ВІРУСУ ПАПІЛОМИ ЛЮДИНИ (ТИПІВ 6, 11, 16, 18) КВАДРИВАЛЕНТНА РЕКОМБІНАНТНА, суспензія для ін’єкцій; 1 або 10 флаконів (по 0,5 мл (1 доза)) у картонній коробці; 1 або 6 попередньо наповнених шприців (по 0,5 мл (1 доза)) у комплекті з 1 голкою у контурній комірковій упаковці в картонній коробці, Серія № Z003787, MERCK SHARP &amp; DOHME LLC та MSD Ireland (Carlow), -</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>ГАРДАСИЛ / GARDASIL® ВАКЦИНА ПРОТИ ВІРУСУ ПАПІЛОМИ ЛЮДИНИ (ТИПІВ 6, 11, 16, 18) КВАДРИВАЛЕНТНА РЕКОМБІНАНТНА, суспензія для ін’єкцій; 1 або 10 флаконів (по 0,5 мл (1 доза)) у картонній коробці; 1 або 6 попередньо наповнених шприців (по 0,5 мл (1 доза)) у комплекті з 1 голкою у контурній комірковій упаковці в картонній коробці, Серія № Z003787, MERCK SHARP &amp; DOHME LLC та MSD Ireland (Carlow), -</t>
+          <t>ГАРДАСИЛ® 9 ВАКЦИНА ПРОТИ ВІРУСУ ПАПІЛОМИ ЛЮДИНИ 9-ВАЛЕНТНА (РЕКОМБІНАНТНА, АДСОРБОВАНА), суспензія для ін'єкцій, по 0,5 мл (1 доза); по 0,5 мл суспензії у попередньо наповненому шприці (скло) з обмежувачем ходу поршня (силіконізований бромбутиловий еластомер із покриттям FluroTec) та ковпачком (синтетична ізопрен-бромбутилова суміш). По 1 поп, Серія № W036325, 800-672, XG663784, XG66374, W036351, MERCK SHARP &amp; DOHME LLC та MSD Ireland (Carlow), -</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3813,17 +3813,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>№ 233-001.2/002.0/17-26 від 07.05.2026</t>
+          <t>№ 234-001.2/002.0/17-26 від 08.05.2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>07.05.2026</t>
+          <t>08.05.2026</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ГАРДАСИЛ® 9 ВАКЦИНА ПРОТИ ВІРУСУ ПАПІЛОМИ ЛЮДИНИ 9-ВАЛЕНТНА (РЕКОМБІНАНТНА, АДСОРБОВАНА), суспензія для ін'єкцій, по 0,5 мл (1 доза); по 0,5 мл суспензії у попередньо наповненому шприці (скло) з обмежувачем ходу поршня (силіконізований бромбутиловий еластомер із покриттям FluroTec) та ковпачком (синтетична ізопрен-бромбутилова суміш). По 1 поп, Серія № W036325, 800-672, XG663784, XG66374, W036351, MERCK SHARP &amp; DOHME LLC та MSD Ireland (Carlow), -</t>
+          <t>КУРОСУРФ® (CUROSURF) 80 mg/ml, суспензія для ендотрахеального введення, 80 мг/мл; по 1,5 мл у флаконі; по 1 флакону в картонній коробці, Серія № 1223993, 1222945, 1226966, 1204364, CHIESI FARMACEUTICI S.P.A., -</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>№ 234-001.2/002.0/17-26 від 08.05.2026</t>
+          <t>№ 235-001.2/002.0/17-26 від 08.05.2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>КУРОСУРФ® (CUROSURF) 80 mg/ml, суспензія для ендотрахеального введення, 80 мг/мл; по 1,5 мл у флаконі; по 1 флакону в картонній коробці, Серія № 1223993, 1222945, 1226966, 1204364, CHIESI FARMACEUTICI S.P.A., -</t>
+          <t>всі серії лікарських засобів виробництва ЛЗ виробництва Navesta Pharmaceuticals Pvt Ltd., -, Серія № всі серії, Navesta Pharmaceuticals Pvt Ltd., Sri Lanka</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>№ 235-001.2/002.0/17-26 від 08.05.2026</t>
+          <t>№ 236-001.2/002.0/17-26 від 08.05.2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>всі серії лікарських засобів виробництва ЛЗ виробництва Navesta Pharmaceuticals Pvt Ltd., -, Серія № всі серії, Navesta Pharmaceuticals Pvt Ltd., Sri Lanka</t>
+          <t>SAIZEN (Somatropin)8 mg/ml (20 MG / 2.5mL), стерилізовані парентеральні розчини малого об'єму, Серія № AB003660, з маркуванням виробника AstraZeneca AB MERCK S/A (ESTRADA DOS BANDEIRANTES, Бразилія</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>№ 236-001.2/002.0/17-26 від 08.05.2026</t>
+          <t>№ 237-001.2/002.0/17-26 від 08.05.2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>SAIZEN (Somatropin)8 mg/ml (20 MG / 2.5mL), стерилізовані парентеральні розчини малого об'єму, Серія № AB003660, з маркуванням виробника AstraZeneca AB MERCK S/A (ESTRADA DOS BANDEIRANTES, Бразилія</t>
+          <t>DEPO MEDROL (Methylprednisolone Acetate) 40mg/1ml, супензія для ін'єкцій, Серія № LX9826, NL5172, ML7753, з маркуванням виробника  PFIZER MANUFACTURING BELGIUM, Бельгія</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>№ 237-001.2/002.0/17-26 від 08.05.2026</t>
+          <t>№ 238-001.2/002.0/17-26 від 08.05.2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>DEPO MEDROL (Methylprednisolone Acetate) 40mg/1ml, супензія для ін'єкцій, Серія № LX9826, NL5172, ML7753, з маркуванням виробника  PFIZER MANUFACTURING BELGIUM, Бельгія</t>
+          <t>DURATESTON (30 + 60 + 100 + 60) mg, cтерилізовані gарентеральні розчини малого об'єму, Серія № 900124, з маркуванням виробника ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -3953,17 +3953,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>№ 238-001.2/002.0/17-26 від 08.05.2026</t>
+          <t>№ 239-001.2/002.0/17-26 від 12.05.2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>08.05.2026</t>
+          <t>12.05.2026</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DURATESTON (30 + 60 + 100 + 60) mg, cтерилізовані gарентеральні розчини малого об'єму, Серія № 900124, з маркуванням виробника ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
+          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники; по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ТR056, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>№ 239-001.2/002.0/17-26 від 12.05.2026</t>
+          <t>№ 240-001.2/002.0/17-26 від 12.05.2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники; по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ТR056, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+          <t>СТРЕПСІЛС® ОРИГІНАЛЬНИЙ, льодяники; по 12 льодяників у блістері, по 2 блістери в картонній коробці, Серія № VC784, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>№ 240-001.2/002.0/17-26 від 12.05.2026</t>
+          <t>№ 242-001.2/002.0/17-26 від 13.05.2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12.05.2026</t>
+          <t>13.05.2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>СТРЕПСІЛС® ОРИГІНАЛЬНИЙ, льодяники; по 12 льодяників у блістері, по 2 блістери в картонній коробці, Серія № VC784, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британія</t>
+          <t>всі серії ЛЗ виробництва Technophage Investigacao E Desenvolvimento Em Biotecnologia S.A., -, Серія № всі серії, Technophage Investigacao E Desenvolvimento Em Biotecnologia S.A., Португалія</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>№ 242-001.2/002.0/17-26 від 13.05.2026</t>
+          <t>№ 243-001.2/002.0/17-26 від 14.05.2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13.05.2026</t>
+          <t>14.05.2026</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>всі серії ЛЗ виробництва Technophage Investigacao E Desenvolvimento Em Biotecnologia S.A., -, Серія № всі серії, Technophage Investigacao E Desenvolvimento Em Biotecnologia S.A., Португалія</t>
+          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг; по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці, Серія № ECM25002B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>№ 243-001.2/002.0/17-26 від 14.05.2026</t>
+          <t>№ 245-001.2/002.0/17-26 від 14.05.2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг; по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці, Серія № ECM25002B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -4093,17 +4093,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>№ 245-001.2/002.0/17-26 від 14.05.2026</t>
+          <t>№ 246-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14.05.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
+          <t>Baclofen-neuraxpharm®, 25mg, Tabletten, 100 Tabletten, Серія № 230012, NEURAXPHARM Arzneimittel GmbH Elisabeth-Selbert-Str. 23 40764, Langenfeld</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>№ 246-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 247-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Baclofen-neuraxpharm®, 25mg, Tabletten, 100 Tabletten, Серія № 230012, NEURAXPHARM Arzneimittel GmbH Elisabeth-Selbert-Str. 23 40764, Langenfeld</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 42726A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 42726A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 20914A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 20914A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 13850A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>№ 247-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 248-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 13850A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+          <t>Naratriptan – 1A Pharma®, bei Migrane 2,5 mg Filmtabletten, 2 Filmtabletten № 1, Серія № PT5595, Lek S.A. Ul. Podlipie 16 Strykow 95-010, Polen</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>№ 248-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 249-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Naratriptan – 1A Pharma®, bei Migrane 2,5 mg Filmtabletten, 2 Filmtabletten № 1, Серія № PT5595, Lek S.A. Ul. Podlipie 16 Strykow 95-010, Polen</t>
+          <t>Duloxetin Glenmark, 30 mg magensaftresistente Hartkapseln, 28 magensaftresistente Hartkapseln, Серія № 40784, Towa Pharmaceutical Europe, S.L. C/ de Sant Marti, 75-97 Martorelles, 08107 Barcelona, Spanien</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>№ 249-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Duloxetin Glenmark, 30 mg magensaftresistente Hartkapseln, 28 magensaftresistente Hartkapseln, Серія № 40784, Towa Pharmaceutical Europe, S.L. C/ de Sant Marti, 75-97 Martorelles, 08107 Barcelona, Spanien</t>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 60 Film Kapli Tablet, Серія № 25371012, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 60 Film Kapli Tablet, Серія № 25371012, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 3 Film Kapli Tablet, Серія № 25371015, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 3 Film Kapli Tablet, Серія № 25371015, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>ANDAZOL®, 200mg/10ml Suspansiyon, % 2 suspansiyon 60 ml, Серія № 25020011, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 200mg/10ml Suspansiyon, % 2 suspansiyon 60 ml, Серія № 25020011, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>NUROFEN® JUNIOR, ERDBEER, 40 mg/ml SUSPENSION ZUM EINNEHMEN 100ml, Серія № AHC903, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® JUNIOR, ERDBEER, 40 mg/ml SUSPENSION ZUM EINNEHMEN 100ml, Серія № AHC903, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® IMMEDIA, 400 mg Filmtabletten, 12 Filmtabletten, Серія № TE404, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® IMMEDIA, 400 mg Filmtabletten, 12 Filmtabletten, Серія № TE404, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN®, 400MG WEICHKAPSELN, 20 Weichkapseln, Серія № TY059, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN®, 400MG WEICHKAPSELN, 20 Weichkapseln, Серія № TY059, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® Immedia, 200 mg, 10 Weichkapseln, Серія № TK473, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® Immedia, 200 mg, 10 Weichkapseln, Серія № TK473, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® JUNIOR, ORANGE, 40 mg/ml SUSPENSION ZUM EINNEHMEN, 100ml, Серія № AHB068, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® JUNIOR, ORANGE, 40 mg/ml SUSPENSION ZUM EINNEHMEN, 100ml, Серія № AHB068, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>TYLOL®HOT DAY, 12 poset, Серія № 270630, NOBEL ILAC SANAYII VE TICARET A.S. Sancaklar 81100, DUZCE</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>TYLOL®HOT DAY, 12 poset, Серія № 270630, NOBEL ILAC SANAYII VE TICARET A.S. Sancaklar 81100, DUZCE</t>
+          <t>Tadalafil beta, 5 mg 84 Filmtabletten, Серія № 2405018050, betapharm Arzneimittel GmbH Kobelweg 95, 86156, Augsburg</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Tadalafil beta, 5 mg 84 Filmtabletten, Серія № 2405018050, betapharm Arzneimittel GmbH Kobelweg 95, 86156, Augsburg</t>
+          <t>Soldesam, 0,2% gocce orali, soluzione Flacone da 10 ml, Серія № 260128, laboratorio farmacologico milanese s.r.l. via monterosso, 273 21042, caronno pertusella (va)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Soldesam, 0,2% gocce orali, soluzione Flacone da 10 ml, Серія № 260128, laboratorio farmacologico milanese s.r.l. via monterosso, 273 21042, caronno pertusella (va)</t>
+          <t>Tolperison-HCI dura®, 50 mg Filmtabletten, 96 Filmtabletten, Серія № TN47017H, Mylan Germany GmbH Lutticher Stra?e 5 53842, Troisdorf</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Tolperison-HCI dura®, 50 mg Filmtabletten, 96 Filmtabletten, Серія № TN47017H, Mylan Germany GmbH Lutticher Stra?e 5 53842, Troisdorf</t>
+          <t>Escitalopram A?Z, 20 mg Filmtabletten, 100 Filmtabletten, Серія № 16515423, Merckle GmbH Ludwig-Merckle-Str. 3 89143, Blaubeuren</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Escitalopram A?Z, 20 mg Filmtabletten, 100 Filmtabletten, Серія № 16515423, Merckle GmbH Ludwig-Merckle-Str. 3 89143, Blaubeuren</t>
+          <t>Ezetimib Arasto, 10 mg Tabletten, 50 Tabletten, Серія № 26046T5, Laboratorios Medicamentos Internacionales S.A. Calle Solana 26 28850 Torrejon de Ardoz (Madrid), Spanien</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Ezetimib Arasto, 10 mg Tabletten, 50 Tabletten, Серія № 26046T5, Laboratorios Medicamentos Internacionales S.A. Calle Solana 26 28850 Torrejon de Ardoz (Madrid), Spanien</t>
+          <t>Sab simplex®, 69,19 mg/ml Suspension zum Einnehmen Simeticon, 30 ml, Серія № 01261, Delpharm Orleans 5, avenue de Concyr 45071 Orleans Cedex 2, Frankreich</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sab simplex®, 69,19 mg/ml Suspension zum Einnehmen Simeticon, 30 ml, Серія № 01261, Delpharm Orleans 5, avenue de Concyr 45071 Orleans Cedex 2, Frankreich</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953167, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953167, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D937842, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D937842, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953182, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953182, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Mounjaro® KwikPen®, 10 mg/Dosis, Injektionslosung in einem Fertigpen 3 Pens (jeder Pen gibt 4 Dosen ad), Серія № D871349D, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/Dosis, Injektionslosung in einem Fertigpen 3 Pens (jeder Pen gibt 4 Dosen ad), Серія № D871349D, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Espumisan®, Emulsion 40 mg/ml, 32 ml Emulsion zum Einnehmen, Серія № 51001A, BERLIN-CHEMIE AG Glienicker Weg 125, 12489 Berlin, Deutschland</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Espumisan®, Emulsion 40 mg/ml, 32 ml Emulsion zum Einnehmen, Серія № 51001A, BERLIN-CHEMIE AG Glienicker Weg 125, 12489 Berlin, Deutschland</t>
+          <t>Ben-u-ron® Saft, 40 mg/ml Sirup, 100 ml Sirup Zum Einnehmen, Серія № 306L241, Medinfar Manufacturing S.A. Parque Industrial Armando Martins Tavares Rua Outeiro da Armada No 5 Condeixa-а-Nova 3150-194 Sebal, Portugal</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Ben-u-ron® Saft, 40 mg/ml Sirup, 100 ml Sirup Zum Einnehmen, Серія № 306L241, Medinfar Manufacturing S.A. Parque Industrial Armando Martins Tavares Rua Outeiro da Armada No 5 Condeixa-а-Nova 3150-194 Sebal, Portugal</t>
+          <t>Lymphomyosot®N, 100 ml Mischung, Серія № 09982, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 100 ml Mischung, Серія № 09982, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Femoston® conti, 1mg/5mg Filmtabletten, 84 (3x28) Filmtabletten Zum Einnehmen, Серія № 375648, Abbott Biologicals B.V. C.J. van Houtenlaan 36 1381 CP Weesp, Niederlande</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Femoston® conti, 1mg/5mg Filmtabletten, 84 (3x28) Filmtabletten Zum Einnehmen, Серія № 375648, Abbott Biologicals B.V. C.J. van Houtenlaan 36 1381 CP Weesp, Niederlande</t>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 08900, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 08900, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 10944, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 10944, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5V443, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5V443, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T599, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 258-001.2/002.0/17-26 від 18.05.2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>18.05.2026</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T599, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5073,17 +5073,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>№ 258-001.2/002.0/17-26 від 18.05.2026</t>
+          <t>№ 259-001.2/002.0/17-26 від 21.05.2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>21.05.2026</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>ВАЛОКОРМІД, краплі оральні, по 25 мл у флаконах;, Серія № 11225, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5101,17 +5101,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>№ 259-001.2/002.0/17-26 від 21.05.2026</t>
+          <t>№ 260-001.2/002.0/17-26 від 22.05.2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>21.05.2026</t>
+          <t>22.05.2026</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>ВАЛОКОРМІД, краплі оральні, по 25 мл у флаконах;, Серія № 11225, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
+          <t>GENTEAL GEL, гель для очей, Серія № 2X11, EXCELVISION 27 RUE DE LA LOMBARDIER ANNONAY, 07100, FRENCH REPUBLIC, Франція</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>№ 260-001.2/002.0/17-26 від 22.05.2026</t>
+          <t>№ 261-001.2/002.0/17-26 від 22.05.2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>GENTEAL GEL, гель для очей, Серія № 2X11, EXCELVISION 27 RUE DE LA LOMBARDIER ANNONAY, 07100, FRENCH REPUBLIC, Франція</t>
+          <t>HEROGEL, суспензія для перорального застосування, ПЕТ-пляшка 240 мл, Серія № 83300804, Heromycin pharma Co., Ltd., -</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5157,17 +5157,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>№ 261-001.2/002.0/17-26 від 22.05.2026</t>
+          <t>№ 262-001.2/002.0/17-26 від 25.05.2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>22.05.2026</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>HEROGEL, суспензія для перорального застосування, ПЕТ-пляшка 240 мл, Серія № 83300804, Heromycin pharma Co., Ltd., -</t>
+          <t>ЕЗОЛОНГ®-20, таблетки, вкриті плівковою оболонкою, по 20 мг; по 7 таблеток у блістері; по 2 блістери у картонній коробці, Серія № ЕЕР25008А1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5185,17 +5185,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>№ 262-001.2/002.0/17-26 від 25.05.2026</t>
+          <t>№ 263-001.2/002.0/17-26 від 26.05.2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>25.05.2026</t>
+          <t>26.05.2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>ЕЗОЛОНГ®-20, таблетки, вкриті плівковою оболонкою, по 20 мг; по 7 таблеток у блістері; по 2 блістери у картонній коробці, Серія № ЕЕР25008А1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг, по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці;, Серія № ЕСМ25001В1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>№ 263-001.2/002.0/17-26 від 26.05.2026</t>
+          <t>№ 264-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>26.05.2026</t>
+          <t>27.05.2026</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг, по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці;, Серія № ЕСМ25001В1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>MONSEL`S SOLUTION, розчин, Серія № 640911253, Premier Medical Products, -</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>№ 264-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 265-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>MONSEL`S SOLUTION, розчин, Серія № 640911253, Premier Medical Products, -</t>
+          <t>APALIN 250 mg Injection, 125 mg/1 mL, розчин для ін`єкцій по 2 мл в ампулі; по 10 ампул у картонній пачці, Серія № 242837T, Duopharma (M) Sdn. Bhd., Малайзія</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>№ 265-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 266-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>APALIN 250 mg Injection, 125 mg/1 mL, розчин для ін`єкцій по 2 мл в ампулі; по 10 ампул у картонній пачці, Серія № 242837T, Duopharma (M) Sdn. Bhd., Малайзія</t>
+          <t>AMPICILLIN SODIUM, порошок для ін'єкцій, Серія № 315089, TP Drug Laboratories (1969) Co., Ltd (Praram 2 Branch), -</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>№ 266-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 267-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>AMPICILLIN SODIUM, порошок для ін'єкцій, Серія № 315089, TP Drug Laboratories (1969) Co., Ltd (Praram 2 Branch), -</t>
+          <t>FLEBOGAMMA DIF 5%, 50 mg/ml, розчин для інфузій, 400 мл, Серія № G04K181561, Instituto Grifols, S.A facility in Parets del Valles, Barcelona, Іспанія</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>№ 267-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 268-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>FLEBOGAMMA DIF 5%, 50 mg/ml, розчин для інфузій, 400 мл, Серія № G04K181561, Instituto Grifols, S.A facility in Parets del Valles, Barcelona, Іспанія</t>
+          <t>DURATESTON, 30  mg, 60  mg, 100 mg, cтерилізовані парентеральні розчини малого об'єму, Серія № 945858, ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>№ 268-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DURATESTON, 30  mg, 60  mg, 100 mg, cтерилізовані парентеральні розчини малого об'єму, Серія № 945858, ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
+          <t>АА PHARMA HYDROXYZINE CAPSULE, 10 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW6213A, AW6448A, AW8160A, AW8161A, AW8177A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>АА PHARMA HYDROXYZINE CAPSULE, 10 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW6213A, AW6448A, AW8160A, AW8161A, AW8177A, Catalent Ontario Limited, Канада</t>
+          <t>PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
+          <t>АА PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 270-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>АА PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
+          <t>GLUMET XR 500 mg, таблетки № 10 у блістері, у картонній коробці № 100, Серія № 5028486, 5032332, 5032334, 2034104, 5034103, 5034100, 5036722, 5036724, 5036723, 5037167, 5036983, 5036984, 5038424, 5039549, 5040444, Pharmaniaga Manufacturing Berhad, Selangor, Малайзія</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>№ 270-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 271-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>GLUMET XR 500 mg, таблетки № 10 у блістері, у картонній коробці № 100, Серія № 5028486, 5032332, 5032334, 2034104, 5034103, 5034100, 5036722, 5036724, 5036723, 5037167, 5036983, 5036984, 5038424, 5039549, 5040444, Pharmaniaga Manufacturing Berhad, Selangor, Малайзія</t>
+          <t>PALIFREN LONG 150 mg ( Paliperidonum), пролонгована суспензія для ін’єкцій у попередньо наповненому шприці, Серія № 4201120, 4300099, 4201591, PHARMATHEN INTERNATIONAL S.A Rodopi, Evrou, Греція</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>№ 271-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 272-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>PALIFREN LONG 150 mg ( Paliperidonum), пролонгована суспензія для ін’єкцій у попередньо наповненому шприці, Серія № 4201120, 4300099, 4201591, PHARMATHEN INTERNATIONAL S.A Rodopi, Evrou, Греція</t>
+          <t>FOSFATO DISSODICO DE DEXAMETASONA, 4 MG/ML, парентеральні розчини малого об’єму, стерилізовані термінальним методом, № 50, Серія № 25091566, HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, Бразилія</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>№ 272-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 273-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>FOSFATO DISSODICO DE DEXAMETASONA, 4 MG/ML, парентеральні розчини малого об’єму, стерилізовані термінальним методом, № 50, Серія № 25091566, HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, Бразилія</t>
+          <t>SPHERICAL ADSORPTIVE CARBON (Black Tablets), № 336, Серія № TK24804, TK24Y18, TK24Y19, TK25115, TK25117, TK25209, TK25306, TK25307, TK25308, TK25908, TT24Y05, TT24Z13, TP24601, TP24607, TP25222, TP25804, KUREHA Corporation, -</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5542,34 +5542,6 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73" ht="40" customHeight="1">
-      <c r="A73" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>№ 273-001.2/002.0/17-26 від 27.05.2026</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>27.05.2026</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>SPHERICAL ADSORPTIVE CARBON (Black Tablets), № 336, Серія № TK24804, TK24Y18, TK24Y19, TK25115, TK25117, TK25209, TK25306, TK25307, TK25308, TK25908, TT24Y05, TT24Z13, TP24601, TP24607, TP25222, TP25804, KUREHA Corporation, -</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8990,7 +8962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10571,6 +10543,62 @@
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
     </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>№ 392-001.001/002.0/17-26 від 24.08.2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>NEGAZOLE 250MG (METRONIDAZOLE), таблетки, вкриті плівковою оболонкою, у блістерах, Серія № 06056, 06764, 09307, Gulf Pharmaceutical Industries (Julphar), -</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>№ 393-001.001/002.0/17-26 від 24.08.2026</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>СОФОРИ ЯПОНСЬКОЇ НАСТОЙКА, настойка, по 40 мл у флаконах полімерних, Серія № 040424, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8962,7 +8962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10599,6 +10599,34 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
     </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>№ 396-001.001/002.0/17-26 від 25.08.2026</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>ЦИТРАМОН В, таблетки; по 10 таблеток у блістерах; по 10 блістерів у пачці з картону;, Серія № 10426, ПАТ "Монфарм", Україна</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -3486,7 +3486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>№ 243-001.2/002.0/17-26 від 14.05.2026</t>
+          <t>№ 245-001.2/002.0/17-26 від 14.05.2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг; по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці, Серія № ECM25002B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>№ 245-001.2/002.0/17-26 від 14.05.2026</t>
+          <t>№ 246-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>14.05.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
+          <t>Baclofen-neuraxpharm®, 25mg, Tabletten, 100 Tabletten, Серія № 230012, NEURAXPHARM Arzneimittel GmbH Elisabeth-Selbert-Str. 23 40764, Langenfeld</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>№ 246-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 247-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Baclofen-neuraxpharm®, 25mg, Tabletten, 100 Tabletten, Серія № 230012, NEURAXPHARM Arzneimittel GmbH Elisabeth-Selbert-Str. 23 40764, Langenfeld</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 42726A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 42726A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 20914A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 20914A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 13850A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>№ 247-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 248-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Opipram®, 50mg Filmtabletten, 100 Filmtabletten, Серія № 13850A, KrewelMeuselbach KM Krewel Meuselbach GmbH Krewelstr. 2, 53783, Eitorf</t>
+          <t>Naratriptan – 1A Pharma®, bei Migrane 2,5 mg Filmtabletten, 2 Filmtabletten № 1, Серія № PT5595, Lek S.A. Ul. Podlipie 16 Strykow 95-010, Polen</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>№ 248-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 249-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Naratriptan – 1A Pharma®, bei Migrane 2,5 mg Filmtabletten, 2 Filmtabletten № 1, Серія № PT5595, Lek S.A. Ul. Podlipie 16 Strykow 95-010, Polen</t>
+          <t>Duloxetin Glenmark, 30 mg magensaftresistente Hartkapseln, 28 magensaftresistente Hartkapseln, Серія № 40784, Towa Pharmaceutical Europe, S.L. C/ de Sant Marti, 75-97 Martorelles, 08107 Barcelona, Spanien</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>№ 249-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Duloxetin Glenmark, 30 mg magensaftresistente Hartkapseln, 28 magensaftresistente Hartkapseln, Серія № 40784, Towa Pharmaceutical Europe, S.L. C/ de Sant Marti, 75-97 Martorelles, 08107 Barcelona, Spanien</t>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 60 Film Kapli Tablet, Серія № 25371012, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 60 Film Kapli Tablet, Серія № 25371012, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 3 Film Kapli Tablet, Серія № 25371015, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 400 mg Film Kapli Tablet, 3 Film Kapli Tablet, Серія № 25371015, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>ANDAZOL®, 200mg/10ml Suspansiyon, % 2 suspansiyon 60 ml, Серія № 25020011, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>№ 250-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ANDAZOL®, 200mg/10ml Suspansiyon, % 2 suspansiyon 60 ml, Серія № 25020011, Biofarma Ilac San. ve Tic. A.S. Akp?nar Mah. Osmangazi Cad. No: 156 Sancaktepe /, ISTANBUL</t>
+          <t>NUROFEN® JUNIOR, ERDBEER, 40 mg/ml SUSPENSION ZUM EINNEHMEN 100ml, Серія № AHC903, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® JUNIOR, ERDBEER, 40 mg/ml SUSPENSION ZUM EINNEHMEN 100ml, Серія № AHC903, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® IMMEDIA, 400 mg Filmtabletten, 12 Filmtabletten, Серія № TE404, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® IMMEDIA, 400 mg Filmtabletten, 12 Filmtabletten, Серія № TE404, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN®, 400MG WEICHKAPSELN, 20 Weichkapseln, Серія № TY059, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN®, 400MG WEICHKAPSELN, 20 Weichkapseln, Серія № TY059, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® Immedia, 200 mg, 10 Weichkapseln, Серія № TK473, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® Immedia, 200 mg, 10 Weichkapseln, Серія № TK473, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>NUROFEN® JUNIOR, ORANGE, 40 mg/ml SUSPENSION ZUM EINNEHMEN, 100ml, Серія № AHB068, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>№ 251-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>NUROFEN® JUNIOR, ORANGE, 40 mg/ml SUSPENSION ZUM EINNEHMEN, 100ml, Серія № AHB068, RB NL Brands B.V. Schiphol Boulevard 207 1118 BH Schiphol, Niederlande</t>
+          <t>TYLOL®HOT DAY, 12 poset, Серія № 270630, NOBEL ILAC SANAYII VE TICARET A.S. Sancaklar 81100, DUZCE</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>TYLOL®HOT DAY, 12 poset, Серія № 270630, NOBEL ILAC SANAYII VE TICARET A.S. Sancaklar 81100, DUZCE</t>
+          <t>Tadalafil beta, 5 mg 84 Filmtabletten, Серія № 2405018050, betapharm Arzneimittel GmbH Kobelweg 95, 86156, Augsburg</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tadalafil beta, 5 mg 84 Filmtabletten, Серія № 2405018050, betapharm Arzneimittel GmbH Kobelweg 95, 86156, Augsburg</t>
+          <t>Soldesam, 0,2% gocce orali, soluzione Flacone da 10 ml, Серія № 260128, laboratorio farmacologico milanese s.r.l. via monterosso, 273 21042, caronno pertusella (va)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>№ 252-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Soldesam, 0,2% gocce orali, soluzione Flacone da 10 ml, Серія № 260128, laboratorio farmacologico milanese s.r.l. via monterosso, 273 21042, caronno pertusella (va)</t>
+          <t>Tolperison-HCI dura®, 50 mg Filmtabletten, 96 Filmtabletten, Серія № TN47017H, Mylan Germany GmbH Lutticher Stra?e 5 53842, Troisdorf</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Tolperison-HCI dura®, 50 mg Filmtabletten, 96 Filmtabletten, Серія № TN47017H, Mylan Germany GmbH Lutticher Stra?e 5 53842, Troisdorf</t>
+          <t>Escitalopram A?Z, 20 mg Filmtabletten, 100 Filmtabletten, Серія № 16515423, Merckle GmbH Ludwig-Merckle-Str. 3 89143, Blaubeuren</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Escitalopram A?Z, 20 mg Filmtabletten, 100 Filmtabletten, Серія № 16515423, Merckle GmbH Ludwig-Merckle-Str. 3 89143, Blaubeuren</t>
+          <t>Ezetimib Arasto, 10 mg Tabletten, 50 Tabletten, Серія № 26046T5, Laboratorios Medicamentos Internacionales S.A. Calle Solana 26 28850 Torrejon de Ardoz (Madrid), Spanien</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Ezetimib Arasto, 10 mg Tabletten, 50 Tabletten, Серія № 26046T5, Laboratorios Medicamentos Internacionales S.A. Calle Solana 26 28850 Torrejon de Ardoz (Madrid), Spanien</t>
+          <t>Sab simplex®, 69,19 mg/ml Suspension zum Einnehmen Simeticon, 30 ml, Серія № 01261, Delpharm Orleans 5, avenue de Concyr 45071 Orleans Cedex 2, Frankreich</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>№ 253-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Sab simplex®, 69,19 mg/ml Suspension zum Einnehmen Simeticon, 30 ml, Серія № 01261, Delpharm Orleans 5, avenue de Concyr 45071 Orleans Cedex 2, Frankreich</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953167, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953167, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D937842, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D937842, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953182, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/dosa, soluzione iniettabile in penna preriempita 1 penna (4 dosi), Серія № D953182, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Mounjaro® KwikPen®, 10 mg/Dosis, Injektionslosung in einem Fertigpen 3 Pens (jeder Pen gibt 4 Dosen ad), Серія № D871349D, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>№ 254-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Mounjaro® KwikPen®, 10 mg/Dosis, Injektionslosung in einem Fertigpen 3 Pens (jeder Pen gibt 4 Dosen ad), Серія № D871349D, Eli Lilly Italia S.p.A., Via Gramsci 731/733 50019, Sesto Fiorentino Firenze (FI), Italia</t>
+          <t>Espumisan®, Emulsion 40 mg/ml, 32 ml Emulsion zum Einnehmen, Серія № 51001A, BERLIN-CHEMIE AG Glienicker Weg 125, 12489 Berlin, Deutschland</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Espumisan®, Emulsion 40 mg/ml, 32 ml Emulsion zum Einnehmen, Серія № 51001A, BERLIN-CHEMIE AG Glienicker Weg 125, 12489 Berlin, Deutschland</t>
+          <t>Ben-u-ron® Saft, 40 mg/ml Sirup, 100 ml Sirup Zum Einnehmen, Серія № 306L241, Medinfar Manufacturing S.A. Parque Industrial Armando Martins Tavares Rua Outeiro da Armada No 5 Condeixa-а-Nova 3150-194 Sebal, Portugal</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Ben-u-ron® Saft, 40 mg/ml Sirup, 100 ml Sirup Zum Einnehmen, Серія № 306L241, Medinfar Manufacturing S.A. Parque Industrial Armando Martins Tavares Rua Outeiro da Armada No 5 Condeixa-а-Nova 3150-194 Sebal, Portugal</t>
+          <t>Lymphomyosot®N, 100 ml Mischung, Серія № 09982, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>№ 255-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 100 ml Mischung, Серія № 09982, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Femoston® conti, 1mg/5mg Filmtabletten, 84 (3x28) Filmtabletten Zum Einnehmen, Серія № 375648, Abbott Biologicals B.V. C.J. van Houtenlaan 36 1381 CP Weesp, Niederlande</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Femoston® conti, 1mg/5mg Filmtabletten, 84 (3x28) Filmtabletten Zum Einnehmen, Серія № 375648, Abbott Biologicals B.V. C.J. van Houtenlaan 36 1381 CP Weesp, Niederlande</t>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 08900, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 08900, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 10944, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>№ 256-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Lymphomyosot®N, 30 ml Mischung, Серія № 10944, Biologische Heilmittel Heel GmbH Dr.-Reckeweg-Str. 2-4 76532, Baden-Baden</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5V443, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5V443, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T599, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -5017,17 +5017,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>№ 257-001.2/002.0/17-26 від 15.05.2026</t>
+          <t>№ 258-001.2/002.0/17-26 від 18.05.2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>18.05.2026</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T599, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>№ 258-001.2/002.0/17-26 від 18.05.2026</t>
+          <t>№ 259-001.2/002.0/17-26 від 21.05.2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>21.05.2026</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Ozempic®, 1mg, Injektionslosung im Fertigpen, 1x3ml Pen und Einweg-Nadeln (8 Dosen), Серія № RP5T552, Novo Nordisk A/S Novo Alle, DK-2880 Bagsv?rd, Danemark</t>
+          <t>ВАЛОКОРМІД, краплі оральні, по 25 мл у флаконах;, Серія № 11225, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5073,17 +5073,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>№ 259-001.2/002.0/17-26 від 21.05.2026</t>
+          <t>№ 260-001.2/002.0/17-26 від 22.05.2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>21.05.2026</t>
+          <t>22.05.2026</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>ВАЛОКОРМІД, краплі оральні, по 25 мл у флаконах;, Серія № 11225, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
+          <t>GENTEAL GEL, гель для очей, Серія № 2X11, EXCELVISION 27 RUE DE LA LOMBARDIER ANNONAY, 07100, FRENCH REPUBLIC, Франція</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>№ 260-001.2/002.0/17-26 від 22.05.2026</t>
+          <t>№ 261-001.2/002.0/17-26 від 22.05.2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>GENTEAL GEL, гель для очей, Серія № 2X11, EXCELVISION 27 RUE DE LA LOMBARDIER ANNONAY, 07100, FRENCH REPUBLIC, Франція</t>
+          <t>HEROGEL, суспензія для перорального застосування, ПЕТ-пляшка 240 мл, Серія № 83300804, Heromycin pharma Co., Ltd., -</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -5129,17 +5129,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>№ 261-001.2/002.0/17-26 від 22.05.2026</t>
+          <t>№ 262-001.2/002.0/17-26 від 25.05.2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>22.05.2026</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>HEROGEL, суспензія для перорального застосування, ПЕТ-пляшка 240 мл, Серія № 83300804, Heromycin pharma Co., Ltd., -</t>
+          <t>ЕЗОЛОНГ®-20, таблетки, вкриті плівковою оболонкою, по 20 мг; по 7 таблеток у блістері; по 2 блістери у картонній коробці, Серія № ЕЕР25008А1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5157,17 +5157,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>№ 262-001.2/002.0/17-26 від 25.05.2026</t>
+          <t>№ 264-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>25.05.2026</t>
+          <t>27.05.2026</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>ЕЗОЛОНГ®-20, таблетки, вкриті плівковою оболонкою, по 20 мг; по 7 таблеток у блістері; по 2 блістери у картонній коробці, Серія № ЕЕР25008А1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>MONSEL`S SOLUTION, розчин, Серія № 640911253, Premier Medical Products, -</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5185,17 +5185,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>№ 263-001.2/002.0/17-26 від 26.05.2026</t>
+          <t>№ 265-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>26.05.2026</t>
+          <t>27.05.2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>КЛОТРИМАЗОЛ, таблетки вагінальні по 100 мг, по 6 таблеток у блістері; по 1 блістеру з аплікатором у картонній пачці;, Серія № ЕСМ25001В1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>APALIN 250 mg Injection, 125 mg/1 mL, розчин для ін`єкцій по 2 мл в ампулі; по 10 ампул у картонній пачці, Серія № 242837T, Duopharma (M) Sdn. Bhd., Малайзія</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>№ 264-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 266-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>MONSEL`S SOLUTION, розчин, Серія № 640911253, Premier Medical Products, -</t>
+          <t>AMPICILLIN SODIUM, порошок для ін'єкцій, Серія № 315089, TP Drug Laboratories (1969) Co., Ltd (Praram 2 Branch), -</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>№ 265-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 267-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>APALIN 250 mg Injection, 125 mg/1 mL, розчин для ін`єкцій по 2 мл в ампулі; по 10 ампул у картонній пачці, Серія № 242837T, Duopharma (M) Sdn. Bhd., Малайзія</t>
+          <t>FLEBOGAMMA DIF 5%, 50 mg/ml, розчин для інфузій, 400 мл, Серія № G04K181561, Instituto Grifols, S.A facility in Parets del Valles, Barcelona, Іспанія</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>№ 266-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 268-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>AMPICILLIN SODIUM, порошок для ін'єкцій, Серія № 315089, TP Drug Laboratories (1969) Co., Ltd (Praram 2 Branch), -</t>
+          <t>DURATESTON, 30  mg, 60  mg, 100 mg, cтерилізовані парентеральні розчини малого об'єму, Серія № 945858, ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>№ 267-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>FLEBOGAMMA DIF 5%, 50 mg/ml, розчин для інфузій, 400 мл, Серія № G04K181561, Instituto Grifols, S.A facility in Parets del Valles, Barcelona, Іспанія</t>
+          <t>АА PHARMA HYDROXYZINE CAPSULE, 10 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW6213A, AW6448A, AW8160A, AW8161A, AW8177A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>№ 268-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>DURATESTON, 30  mg, 60  mg, 100 mg, cтерилізовані парентеральні розчини малого об'єму, Серія № 945858, ASPEN PHARMA INDUSTRIA FARMACEUTICA LTDA, Бразилія</t>
+          <t>PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>АА PHARMA HYDROXYZINE CAPSULE, 10 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW6213A, AW6448A, AW8160A, AW8161A, AW8177A, Catalent Ontario Limited, Канада</t>
+          <t>АА PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 270-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
+          <t>GLUMET XR 500 mg, таблетки № 10 у блістері, у картонній коробці № 100, Серія № 5028486, 5032332, 5032334, 2034104, 5034103, 5034100, 5036722, 5036724, 5036723, 5037167, 5036983, 5036984, 5038424, 5039549, 5040444, Pharmaniaga Manufacturing Berhad, Selangor, Малайзія</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>№ 269-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 271-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>АА PHARMA HYDROXYZINE CAPSULE, 25 mg, капсули, наповнені рідиною, флакон № 100, Серія № AW5757A, AW5758A, AW6084A, AW6875A, AW7380A, AW7456A, AW7457A, AW8338A, AW8516A, AW8644A, AW8645A, AW8646A, AW8647A, Catalent Ontario Limited, Канада</t>
+          <t>PALIFREN LONG 150 mg ( Paliperidonum), пролонгована суспензія для ін’єкцій у попередньо наповненому шприці, Серія № 4201120, 4300099, 4201591, PHARMATHEN INTERNATIONAL S.A Rodopi, Evrou, Греція</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>№ 270-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 272-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>GLUMET XR 500 mg, таблетки № 10 у блістері, у картонній коробці № 100, Серія № 5028486, 5032332, 5032334, 2034104, 5034103, 5034100, 5036722, 5036724, 5036723, 5037167, 5036983, 5036984, 5038424, 5039549, 5040444, Pharmaniaga Manufacturing Berhad, Selangor, Малайзія</t>
+          <t>FOSFATO DISSODICO DE DEXAMETASONA, 4 MG/ML, парентеральні розчини малого об’єму, стерилізовані термінальним методом, № 50, Серія № 25091566, HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, Бразилія</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>№ 271-001.2/002.0/17-26 від 27.05.2026</t>
+          <t>№ 273-001.2/002.0/17-26 від 27.05.2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>PALIFREN LONG 150 mg ( Paliperidonum), пролонгована суспензія для ін’єкцій у попередньо наповненому шприці, Серія № 4201120, 4300099, 4201591, PHARMATHEN INTERNATIONAL S.A Rodopi, Evrou, Греція</t>
+          <t>SPHERICAL ADSORPTIVE CARBON (Black Tablets), № 336, Серія № TK24804, TK24Y18, TK24Y19, TK25115, TK25117, TK25209, TK25306, TK25307, TK25308, TK25908, TT24Y05, TT24Z13, TP24601, TP24607, TP25222, TP25804, KUREHA Corporation, -</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5486,62 +5486,6 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71" ht="40" customHeight="1">
-      <c r="A71" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>№ 272-001.2/002.0/17-26 від 27.05.2026</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>27.05.2026</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>FOSFATO DISSODICO DE DEXAMETASONA, 4 MG/ML, парентеральні розчини малого об’єму, стерилізовані термінальним методом, № 50, Серія № 25091566, HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, Бразилія</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72" ht="40" customHeight="1">
-      <c r="A72" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>№ 273-001.2/002.0/17-26 від 27.05.2026</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>27.05.2026</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>SPHERICAL ADSORPTIVE CARBON (Black Tablets), № 336, Серія № TK24804, TK24Y18, TK24Y19, TK25115, TK25117, TK25209, TK25306, TK25307, TK25308, TK25908, TT24Y05, TT24Z13, TP24601, TP24607, TP25222, TP25804, KUREHA Corporation, -</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8962,7 +8906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10627,6 +10571,90 @@
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr"/>
     </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>№ 399-001.001/002.0/17-26 від 25.08.2026</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>SOLTROPIN (Mupirocinum) 20 mg/g, мазь 15 г у тубі, Серія № S082414.1, INFECTOPHARM Arzneimittel und Consilium GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>№ 400-001.001/002.0/17-26 від 25.08.2026</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>ARANESP 10 mcg/4 ml (DARBEPOETIN ALFA), розчин для ін'єкцій у попередньо наповненому шприці, Серія № 1201165A, 1202944B, Amgen Manufacturing Limited, -</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>№ 400-001.001/002.0/17-26 від 25.08.2026</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>ARANESP 500 mcg/1 ml (DARBEPOETIN ALFA), розчин для ін'єкцій у попередньо наповненому шприці, Серія № 1189992A, 1190934A, Amgen Manufacturing Limited, -</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8906,7 +8906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10655,6 +10655,34 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
     </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>№ 402-001.001/002.0/17-26 від 26.08.2026</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 2 % по 25 г у тубах ламінатних в пачці, Серія № 030724, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8906,7 +8906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10683,6 +10683,146 @@
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
     </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>№ 403-001.001/002.0/17-26 від 26.08.2026</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>МЕЗИМ® КАПСУЛИ 10000, капсули тверді з кишковорозчинними міні-таблетками; по 20 капсул у банці, Серія № F160456 (cерія "in bulk" - 51225В), Адер Фармасьютіклс СРЛ, Італія, Італія</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>№ 404-001.001/002.0/17-26 від 26.08.2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>ТОБРАДЕКС®/TOBRADEX EYE OINTMENT (Tobramycin/Dexamethasone), мазь очна; по 3,5 г у тубі, Серія № VLM44A, Новартіс Мануфактурінг НВ, Бельгія</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>№ 405-001.001/002.0/17-26 від 26.08.2026</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>WARFANT 3 mg (WARFARIN SODIUM), таблетки № 100 у поліпропіленовому контейнері, Серія № 25002, Famar Italia S.p.A., Італiя</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>№ 406-001.001/002.0/17-26 від 26.08.2026</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>TEVA-PREGABALIN Capsules 150 mg (Pregabalin), капсули тверді по 150 мг, Серія № 100070495, 100068913, Teva Canada Ltd, Канада</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>№ 407-001.001/002.0/17-26 від 26.08.2026</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>IVF-M HP 75IU (HIGHLY PURIFIED HUMAN MENOPAUSAL GONADOTROPIN), ліофілізований порошок для розчину для ін'єкцій, Серія № HMG24706, HMG24707, HMG25701, HMG25702, HMG25704, LG CHEM, LTD., Корея</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8906,7 +8906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10823,6 +10823,202 @@
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr"/>
     </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>№ 408-001.001/002.0/17-26 від 27.08.2026</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT® 500 U (Botulinum toxin type A), ліофілізований порошок, Серія № P22686, з маркуванням Ipsen Farmaceutica Ltda., -</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>№ 409-001.001/002.0/17-26 від 27.08.2026</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>TRODELVY (Sacituzumab govitecan), асептично оброблені парентеральні розчини малого об'єму, Серія № 10008808, GILEAD SCIENCES INC (1800 WHEELER AVE.,LA VERNE, Каліфорнія</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>№ 410-001.001/002.0/17-26 від 27.08.2026</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>ПРОТЕКОН ФАСТ®, таблетки, вкриті плівковою оболонкою,  по 60 таблеток у контейнері; по 1 контейнеру у пачці з картону, Серія № EGD26001A1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>№ 411-001.001/002.0/17-26 від 27.08.2026</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>KEYTRUDA (Pembrolizumab) 25 mg/ml, 100 мл у флаконі, Серія № Z016478, Z016479, з маркуванням виробника Merck Sharp &amp; Dohme B.V., -</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>№ 412-001.001/002.0/17-26 від 27.08.2026</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>MOUNJARO (Tirzepatide), 15 mg/0.5 mL, розчин для ін'єкцій, флакон з одноразовою дозою, Серія № 2032316, з маркуванням виробника BSP Pharmaceuticals S.p.A., Latina Scalo, Італiя</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>№ 412-001.001/002.0/17-26 від 27.08.2026</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>MOUNJARO (Tirzepatide), 5 mg/0.5 mL, розчин для ін'єкцій, флакон з одноразовою дозою, Серія № 2032307, BSP Pharmaceuticals S.p.A., Latina Scalo, Італiя</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>№ 413-001.001/002.0/17-26 від 27.08.2026</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>MOUNJARO (tirzepatide), асептичний парентеральний розчин малого об’єму, Серія № 955010, ELI LILLY AND COMPANY, -</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8906,7 +8906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11019,6 +11019,34 @@
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
     </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>№ 414-001.001/002.0/17-26 від 28.08.2026</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Пантенол, мазь, 50 мг/г по 30 г у тубі,по 1 тубі в картонній упаковці, Серія № 15X59A, Хемофарм, АД, Сербія</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -8906,7 +8906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11047,6 +11047,90 @@
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr"/>
     </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>№ 415-001.001/002.0/17-26 від 31.08.2026</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники, по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ST420, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>№ 416-001.001/002.0/17-26 від 31.08.2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>НОРМОЛАКТ, сироп, 670 мг/мл по 100 мл у флаконі полімерному; по 1 флакону разом із дозувальною ложкою в пачці, Серія № 1360824, ПАТ "Науково-виробничий центр "Борщагівський хіміко-фармацевтичний завод", Україна</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>№ 417-001.001/002.0/17-26 від 31.08.2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>ЕНТОБАН, сироп; по 120 мл у флаконі; по 1 флакону у картонній коробці, Серія № 1825003, Хербіон Пакистан Прайвет Лімітед, Пакистан</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Червень 2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Липень 2026" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Серпень 2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Вересень 2026" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11134,4 +11135,336 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№ з/п</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Дата і номер розпорядження/ рішення/припису</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Дата одержання розпорядження/ рішення/припису</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Назва лікарських засобів та перелік серій лікарських засобів, зазначених у розпорядженні/ рішенні/приписі</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Результати перевірки щодо наявності зазначених лікарських засобів</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Вжиті заходи у разі виявлення зазначених лікарських засобів</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Дата і номер листа-повідомлення територіальному органу</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Підпис уповноваженої особи</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>№ 419-001.001/002.0/17-26 від 09.09.2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ІБУПРОФЕН Б.БРАУН, розчин для інфузій, 400 мг/100 мл по 100 мл у поліетиленових флаконах, по 100 мл у поліетиленових флаконах, по 10 або 20 флаконів у картонній коробці, Серія № всі серії, Б. Браун Медікал СА, Іспанія</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>№ 420-001.001/002.0/17-26 від 09.09.2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>DUTILOX (Duloxetinum), кишковорозчинні капсули, тверді, № 30, № 60, Серія № всі серії, TOWA Pharmaceutical Europe S.L.C, Іспанія</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>№ 421-001.001/002.0/17-26 від 09.09.2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>FINGOLIMOD ZENTIVA (Fingolimodum) 0,5 mg, капсули в блістері № 28, Серія № 4L01372M (bulk: 4L01372), LABORMED-PHARMA S.A., Румунія</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>№ 422-001.001/002.0/17-26 від 09.09.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>CUREOUS Cannabis- flower BLB THC32, 150 g, Серія № B15F125, ECO GROW s.r.o., -</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>№ 423-001.001/002.0/17-26 від 09.09.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>АБІЗОЛ, розчин оральний 1 мг/мл, по 150 мл розчину у флаконі, по одному флакону з мірним стаканчиком та шприцом-дозатором у картонній упаковці, Серія № ECVG002A, НОБЕЛ ІЛАЧ САНАЇ ВЕ ТІДЖАРЕТ А.Ш., Туреччина</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>№ 424-001.001/002.0/17-26 від 09.09.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>БРУФЕН® РАПІД, капсули м'які по 400 мг, по 10 капсул у блістері, по 1 блістеру у картонній коробці, Серія № B4U00225, Гелтек Прайвет Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>№ 425-001.001/002.0/17-26 від 09.09.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>НЕЙРОДАР®, таблетки, вкриті оболонкою, по 500 мг, по 10 таблеток у блістері; по 1 блістеру в картонній упаковці; по 3  упаковки у картонній коробці, Серія № 1008952, Кусум Хелтхкер Пвт Лтд, Індія</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>№ 426-001.001/002.0/17-26 від 09.09.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>MONASAN INJECTION 1ml Ampoule (Fluphenazine Decanoate), 25 мг/мл в ампулі зі скла бурштинового кольору типу I, Серія № 250879, 251988, Duopharma (M) Sendirian Berhad, Малайзія</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11143,7 +11143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11464,6 +11464,118 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>№ 427-001.001/002.0/17-26 від 10.09.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>БОТОКС/BOTOX 100 units, БОТОКС/BOTOX 100 units, порошок для розчину для ін’єкцій у флаконі у картонній коробці, Серія № С3822 С3, з маркуванням Аллерган Фармасьютікалз, -</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>№ 428-001.001/002.0/17-26 від 10.09.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>КРЕСТОР, таблетки, вкриті плівковою оболонкою, по 20 мг; по 14 таблеток у блістері; по 2 блістери в картонній коробці, Серія № А26237002, А25237040, АстраЗенека ЮК Лімітед, Велика Британія, США/ Велика Британія</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>№ 429-001.001/002.0/17-26 від 10.09.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>DARZALEX (Daratumumab), 400 mg/20 ml, концентрат для розчину для інфузій, флакон 20 мл, Серія № SLF4S40, з маркуванням Janssen, -</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>№ 430-001.001/002.0/17-26 від 10.09.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>OZEMPIC 1MG 1PC. W. NF+ 4PCS. (Semaglutidum), розчин для ін'єкцій у попередньо заповненій шприц-ручці, Серія № RT6KL87, з маркуванням виробника Novo Nordisk A/S., -</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11143,7 +11143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11576,6 +11576,118 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
     </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>№ 431-001.001/002.0/17-26 від 11.09.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники, по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ST420, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>№ 432-001.001/002.0/17-26 від 11.09.2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>всі ЛЗ виробництва Xi’an Guokang Ruijin Pharmaceutical co. Ltd, -, Серія № всі серії, Xi’an Guokang Ruijin Pharmaceutical co. Ltd, Китай</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>№ 433-001.001/002.0/17-26 від 11.09.2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>№ 434-001.001/002.0/17-26 від 11.09.2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT® 500 U (Botulinum toxin type A), ліофілізований порошок, Серія № P08193, з маркуванням Ipsen Farmaceutica Ltda, -</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
